--- a/excel/Расчёты_сравнение_ЭТ_Д.xlsx
+++ b/excel/Расчёты_сравнение_ЭТ_Д.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="506">
   <si>
     <t xml:space="preserve">РАСЧЁТЫ К ОТЧЁТУ О НИР</t>
   </si>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">Изменяйте только ячейки с синим шрифтом на жёлтом фоне на листах «Исходные» и «Веса». Все остальные значения пересчитываются формулами</t>
   </si>
   <si>
-    <t xml:space="preserve">Ключевые рычаги</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_task (сменное задание; 0 — полная смена), T_year_h (годовая загрузка), c_D и c_el (цены), l_charge_km (удалённость зарядки), P_ch_ac (мощность зарядки), цены машин</t>
+    <t xml:space="preserve">Основные изменяемые параметры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S_task (сменное задание; 0 — полная смена), T_year_h (годовая загрузка), c_D и c_el (цены), l_charge_km (расстояние до места зарядки), P_ch_ac (мощность зарядки), цены машин</t>
   </si>
   <si>
     <t xml:space="preserve">Цвета</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">Лист «Проходы»</t>
   </si>
   <si>
-    <t xml:space="preserve">результаты учётных проходов (значения из журналов CAN 1 Гц и полевых журналов) и расчётные показатели проходов (формулы); буксование — по ГОСТ 7057: δ = 1 − N0/N (N — число оборотов двигателя хода на учётной делянке)</t>
+    <t xml:space="preserve">результаты учётных проходов (значения из журналов CAN 1 Гц и полевых журналов) и расчётные показатели проходов (формулы); буксование — по ГОСТ 7057: δ = 1 − N0/N (N — число оборотов тягового электродвигателя на учётной делянке)</t>
   </si>
   <si>
     <t xml:space="preserve">Лист «Опыт_режимы»</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">Лист «Энергетика»</t>
   </si>
   <si>
-    <t xml:space="preserve">мощности ЭТ и Д, буксование, запас мощности, допустимость режимов, часовой расход топлива Д (ASAE D497.7)</t>
+    <t xml:space="preserve">мощности ЭТ и Д, буксование, запас мощности, допустимость режимов, часовой расход топлива Д (ASABE D497.7)</t>
   </si>
   <si>
     <t xml:space="preserve">Лист «Смена»</t>
   </si>
   <si>
-    <t xml:space="preserve">модель смены: развороты, автономность, подзарядки (до трёх циклов), сменная выработка, энергия, полученная из сети, расход топлива на 1 га</t>
+    <t xml:space="preserve">модель смены: развороты, время работы без подзарядки, подзарядки (до трёх циклов), сменная выработка с ограничением сменным заданием, энергия, полученная из сети, расход топлива на 1 га</t>
   </si>
   <si>
     <t xml:space="preserve">Лист «Экономика»</t>
   </si>
   <si>
-    <t xml:space="preserve">удельные прямые и совокупные затраты (ГОСТ 34393-2018, ASAE D497.7)</t>
+    <t xml:space="preserve">удельные прямые и совокупные затраты (ГОСТ 34393-2018, ASABE D497.7)</t>
   </si>
   <si>
     <t xml:space="preserve">Лист «Показатели»</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">Лист «Веса»</t>
   </si>
   <si>
-    <t xml:space="preserve">матрицы парных сравнений МАИ (изменяемые), веса, согласованность; итоговые веса</t>
+    <t xml:space="preserve">матрицы парных сравнений МАИ (изменяемые), веса, согласованность; итоговые веса: вес группы по МАИ × локальный вес показателя (среднее локальных весов МАИ и энтропийных, нормированных в пределах группы)</t>
   </si>
   <si>
     <t xml:space="preserve">Лист «Энтропия»</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">Лист «Устойчивость»</t>
   </si>
   <si>
-    <t xml:space="preserve">результаты Монте-Карло (1000 испытаний) и чувствительности — значения из программного комплекса Python (требуют многократного пересчёта)</t>
+    <t xml:space="preserve">результаты расчёта методом Монте-Карло (1000 реализаций) и чувствительности — значения из программного комплекса Python (требуют многократного пересчёта)</t>
   </si>
   <si>
     <t xml:space="preserve">Проверка</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">P_mot_1h</t>
   </si>
   <si>
-    <t xml:space="preserve">Часовая мощность двигателя хода</t>
+    <t xml:space="preserve">Часовая мощность тягового электродвигателя</t>
   </si>
   <si>
     <t xml:space="preserve">паспорт</t>
@@ -380,34 +380,31 @@
     <t xml:space="preserve">k_D</t>
   </si>
   <si>
-    <t xml:space="preserve">Поправка расхода топлива к ASAE D497.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">допущение (1,0 — в пользу Д)</t>
+    <t xml:space="preserve">Поправочный коэффициент к модели расхода топлива ASABE D497.7</t>
   </si>
   <si>
     <t xml:space="preserve">sfc_a</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAE D497.7: коэффициент a</t>
+    <t xml:space="preserve">ASABE D497.7: коэффициент a</t>
   </si>
   <si>
     <t xml:space="preserve">л/(кВт·ч)</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAE D497.7</t>
+    <t xml:space="preserve">ASABE D497.7</t>
   </si>
   <si>
     <t xml:space="preserve">sfc_b</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAE D497.7: коэффициент b</t>
+    <t xml:space="preserve">ASABE D497.7: коэффициент b</t>
   </si>
   <si>
     <t xml:space="preserve">LHV_D</t>
   </si>
   <si>
-    <t xml:space="preserve">Теплота сгорания ДТ</t>
+    <t xml:space="preserve">Низшая теплота сгорания ДТ</t>
   </si>
   <si>
     <t xml:space="preserve">МДж/л</t>
@@ -419,7 +416,7 @@
     <t xml:space="preserve">tank_D</t>
   </si>
   <si>
-    <t xml:space="preserve">Топливный бак Д</t>
+    <t xml:space="preserve">Вместимость топливного бака Д</t>
   </si>
   <si>
     <t xml:space="preserve">л</t>
@@ -482,7 +479,7 @@
     <t xml:space="preserve">l_charge_km</t>
   </si>
   <si>
-    <t xml:space="preserve">Удалённость места зарядки</t>
+    <t xml:space="preserve">Расстояние от поля до места зарядки (заправки)</t>
   </si>
   <si>
     <t xml:space="preserve">км</t>
@@ -629,13 +626,13 @@
     <t xml:space="preserve">ASAE_RF1</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAE D497.7: RF1 (колёсные тракторы)</t>
+    <t xml:space="preserve">ASABE D497.7: RF1 (колёсные тракторы)</t>
   </si>
   <si>
     <t xml:space="preserve">ASAE_RF2</t>
   </si>
   <si>
-    <t xml:space="preserve">ASAE D497.7: RF2</t>
+    <t xml:space="preserve">ASABE D497.7: RF2</t>
   </si>
   <si>
     <t xml:space="preserve">k_RM_ET</t>
@@ -668,7 +665,7 @@
     <t xml:space="preserve">bat_cal_y</t>
   </si>
   <si>
-    <t xml:space="preserve">Календарный ресурс батареи</t>
+    <t xml:space="preserve">Календарный срок службы батареи</t>
   </si>
   <si>
     <t xml:space="preserve">EF_grid</t>
@@ -698,7 +695,7 @@
     <t xml:space="preserve">PEF_el</t>
   </si>
   <si>
-    <t xml:space="preserve">Коэффициент первичной энергии электроэнергии</t>
+    <t xml:space="preserve">Коэффициент пересчёта электроэнергии в первичную энергию</t>
   </si>
   <si>
     <t xml:space="preserve">Директива 2012/27/ЕС</t>
@@ -707,7 +704,7 @@
     <t xml:space="preserve">PEF_D</t>
   </si>
   <si>
-    <t xml:space="preserve">Коэффициент первичной энергии ДТ</t>
+    <t xml:space="preserve">Коэффициент пересчёта ДТ в первичную энергию</t>
   </si>
   <si>
     <t xml:space="preserve">JEC WTW v5</t>
@@ -725,7 +722,7 @@
     <t xml:space="preserve">S_task</t>
   </si>
   <si>
-    <t xml:space="preserve">Сменное задание (0 — полная смена: задание = выработке Д)</t>
+    <t xml:space="preserve">Сменное задание (0 — сценарий 1: задание равно сменной выработке Д)</t>
   </si>
   <si>
     <t xml:space="preserve">га/смену</t>
@@ -737,7 +734,7 @@
     <t xml:space="preserve">alpha_w</t>
   </si>
   <si>
-    <t xml:space="preserve">Доля экспертных весов в итоговых</t>
+    <t xml:space="preserve">Доля локальных весов МАИ в локальных весах показателей</t>
   </si>
   <si>
     <t xml:space="preserve">методика (0,5)</t>
@@ -1166,7 +1163,7 @@
     <t xml:space="preserve">Запас мощности Д</t>
   </si>
   <si>
-    <t xml:space="preserve">Допустим ЭТ</t>
+    <t xml:space="preserve">Допустим ЭТ по критерию (3.7)</t>
   </si>
   <si>
     <t xml:space="preserve">Допустим Д</t>
@@ -1250,6 +1247,9 @@
     <t xml:space="preserve">A_бак, га</t>
   </si>
   <si>
+    <t xml:space="preserve">Дозаправок при полной смене</t>
+  </si>
+  <si>
     <t xml:space="preserve">Труд ЭТ, тг/га</t>
   </si>
   <si>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">CI</t>
   </si>
   <si>
-    <t xml:space="preserve">CR (RI = 1,12)</t>
+    <t xml:space="preserve">ОС (СИ = 1,12)</t>
   </si>
   <si>
     <t xml:space="preserve">Локальные матрицы (внутри групп)</t>
@@ -1400,16 +1400,25 @@
     <t xml:space="preserve">Код</t>
   </si>
   <si>
-    <t xml:space="preserve">w МАИ</t>
+    <t xml:space="preserve">Вес группы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лок. вес МАИ</t>
   </si>
   <si>
     <t xml:space="preserve">w энтроп.</t>
   </si>
   <si>
+    <t xml:space="preserve">Лок. вес энтроп.</t>
+  </si>
+  <si>
     <t xml:space="preserve">w итог</t>
   </si>
   <si>
-    <t xml:space="preserve">Допустим ЭТ и Д</t>
+    <t xml:space="preserve">Σ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выполнен ЭТ (опыт) и допустим Д</t>
   </si>
   <si>
     <t xml:space="preserve">S_зад, га</t>
@@ -1592,6 +1601,12 @@
     <t xml:space="preserve">Энтропийный вес</t>
   </si>
   <si>
+    <t xml:space="preserve">Энтропийный вес, сценарий 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Строка 40 — веса по матрице при текущем S_task; в расчёте весов используется строка 40 при S_task = 0 и строка 41 (значения сценария 1) при S_task &gt; 0, как в отчёте (подраздел 4.8)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сценарий</t>
   </si>
   <si>
@@ -1610,7 +1625,7 @@
     <t xml:space="preserve">P(C_сов ЭТ &lt; Д)</t>
   </si>
   <si>
-    <t xml:space="preserve">Значения получены программой src/analysis.py (1000 испытаний Монте-Карло: параметры — равномерно в диапазонах листа «Исходные», веса — распределение Дирихле с параметром 50·w). S1 — полная смена, S2 — задание 0,5 га.</t>
+    <t xml:space="preserve">Значения получены программой src/analysis.py (1000 реализаций метода Монте-Карло: параметры — равномерно в диапазонах листа «Исходные», веса — распределение Дирихле с параметром 50·w). S1 — полная смена, S2 — задание 0,5 га.</t>
   </si>
   <si>
     <t xml:space="preserve">S1</t>
@@ -2151,43 +2166,46 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>0.0192507100427242</c:v>
+                  <c:v>-0.0494890023747866</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-0.0210412573619323</c:v>
+                  <c:v>-0.0914225973233612</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-0.036728954152645</c:v>
+                  <c:v>-0.106085232829538</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-0.0177951833990991</c:v>
+                  <c:v>-0.0882632886901545</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-0.0361885484169353</c:v>
+                  <c:v>-0.105373544045986</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-0.0659112675695613</c:v>
+                  <c:v>-0.13356304235639</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.00195927823069966</c:v>
+                  <c:v>-0.0648462670606879</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-0.0408065793542917</c:v>
+                  <c:v>-0.108944935976843</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-0.0552696720316653</c:v>
+                  <c:v>-0.122451861204219</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-0.0414085438954833</c:v>
+                  <c:v>-0.109404523534765</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-0.0669547731598334</c:v>
+                  <c:v>-0.133311906382679</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-0.106706428741133</c:v>
+                  <c:v>-0.171225767807035</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-0.0594334322477936</c:v>
+                  <c:v>-0.126116139605442</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.202038431135661</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2195,11 +2213,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="76014858"/>
-        <c:axId val="70081143"/>
+        <c:axId val="25948836"/>
+        <c:axId val="64110380"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="76014858"/>
+        <c:axId val="25948836"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2231,7 +2249,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70081143"/>
+        <c:crossAx val="64110380"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2239,7 +2257,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70081143"/>
+        <c:axId val="64110380"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2315,7 +2333,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76014858"/>
+        <c:crossAx val="25948836"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2674,7 +2692,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -2732,106 +2750,106 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="U1" s="4" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="V1" s="4" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AA1" s="4" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AB1" s="4" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AC1" s="4" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AD1" s="4" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AE1" s="4" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AF1" s="4" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG1" s="4" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AH1" s="4" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2840,7 +2858,7 @@
         <v>культиватор 0.08×3.6</v>
       </c>
       <c r="B2" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q2,Энергетика!R2)</f>
+        <f aca="false">Энергетика!R2</f>
         <v>1</v>
       </c>
       <c r="C2" s="12" t="n">
@@ -2968,8 +2986,8 @@
         <v>-0.691961444314116</v>
       </c>
       <c r="AH2" s="24" t="n">
-        <f aca="false">IF(B2,Веса!$E$39*X2+Веса!$E$40*Y2+Веса!$E$41*Z2+Веса!$E$42*AA2+Веса!$E$43*AB2+Веса!$E$44*AC2+Веса!$E$45*AD2+Веса!$E$46*AE2+Веса!$E$47*AF2+Веса!$E$48*AG2,"")</f>
-        <v>0.0192507100427242</v>
+        <f aca="false">IF(B2,Веса!$H$39*X2+Веса!$H$40*Y2+Веса!$H$41*Z2+Веса!$H$42*AA2+Веса!$H$43*AB2+Веса!$H$44*AC2+Веса!$H$45*AD2+Веса!$H$46*AE2+Веса!$H$47*AF2+Веса!$H$48*AG2,"")</f>
+        <v>-0.0494890023747866</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2978,7 +2996,7 @@
         <v>культиватор 0.08×4.5</v>
       </c>
       <c r="B3" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q3,Энергетика!R3)</f>
+        <f aca="false">Энергетика!R3</f>
         <v>1</v>
       </c>
       <c r="C3" s="12" t="n">
@@ -3106,8 +3124,8 @@
         <v>-0.73465561459756</v>
       </c>
       <c r="AH3" s="24" t="n">
-        <f aca="false">IF(B3,Веса!$E$39*X3+Веса!$E$40*Y3+Веса!$E$41*Z3+Веса!$E$42*AA3+Веса!$E$43*AB3+Веса!$E$44*AC3+Веса!$E$45*AD3+Веса!$E$46*AE3+Веса!$E$47*AF3+Веса!$E$48*AG3,"")</f>
-        <v>-0.0210412573619323</v>
+        <f aca="false">IF(B3,Веса!$H$39*X3+Веса!$H$40*Y3+Веса!$H$41*Z3+Веса!$H$42*AA3+Веса!$H$43*AB3+Веса!$H$44*AC3+Веса!$H$45*AD3+Веса!$H$46*AE3+Веса!$H$47*AF3+Веса!$H$48*AG3,"")</f>
+        <v>-0.0914225973233612</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3116,7 +3134,7 @@
         <v>культиватор 0.08×5.4</v>
       </c>
       <c r="B4" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q4,Энергетика!R4)</f>
+        <f aca="false">Энергетика!R4</f>
         <v>1</v>
       </c>
       <c r="C4" s="12" t="n">
@@ -3244,8 +3262,8 @@
         <v>-0.755919660881893</v>
       </c>
       <c r="AH4" s="24" t="n">
-        <f aca="false">IF(B4,Веса!$E$39*X4+Веса!$E$40*Y4+Веса!$E$41*Z4+Веса!$E$42*AA4+Веса!$E$43*AB4+Веса!$E$44*AC4+Веса!$E$45*AD4+Веса!$E$46*AE4+Веса!$E$47*AF4+Веса!$E$48*AG4,"")</f>
-        <v>-0.036728954152645</v>
+        <f aca="false">IF(B4,Веса!$H$39*X4+Веса!$H$40*Y4+Веса!$H$41*Z4+Веса!$H$42*AA4+Веса!$H$43*AB4+Веса!$H$44*AC4+Веса!$H$45*AD4+Веса!$H$46*AE4+Веса!$H$47*AF4+Веса!$H$48*AG4,"")</f>
+        <v>-0.106085232829538</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3254,7 +3272,7 @@
         <v>культиватор 0.11×3.6</v>
       </c>
       <c r="B5" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q5,Энергетика!R5)</f>
+        <f aca="false">Энергетика!R5</f>
         <v>1</v>
       </c>
       <c r="C5" s="12" t="n">
@@ -3382,8 +3400,8 @@
         <v>-0.735432770497128</v>
       </c>
       <c r="AH5" s="24" t="n">
-        <f aca="false">IF(B5,Веса!$E$39*X5+Веса!$E$40*Y5+Веса!$E$41*Z5+Веса!$E$42*AA5+Веса!$E$43*AB5+Веса!$E$44*AC5+Веса!$E$45*AD5+Веса!$E$46*AE5+Веса!$E$47*AF5+Веса!$E$48*AG5,"")</f>
-        <v>-0.0177951833990991</v>
+        <f aca="false">IF(B5,Веса!$H$39*X5+Веса!$H$40*Y5+Веса!$H$41*Z5+Веса!$H$42*AA5+Веса!$H$43*AB5+Веса!$H$44*AC5+Веса!$H$45*AD5+Веса!$H$46*AE5+Веса!$H$47*AF5+Веса!$H$48*AG5,"")</f>
+        <v>-0.0882632886901545</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3392,7 +3410,7 @@
         <v>культиватор 0.11×4.5</v>
       </c>
       <c r="B6" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q6,Энергетика!R6)</f>
+        <f aca="false">Энергетика!R6</f>
         <v>1</v>
       </c>
       <c r="C6" s="12" t="n">
@@ -3520,8 +3538,8 @@
         <v>-0.760223555416672</v>
       </c>
       <c r="AH6" s="24" t="n">
-        <f aca="false">IF(B6,Веса!$E$39*X6+Веса!$E$40*Y6+Веса!$E$41*Z6+Веса!$E$42*AA6+Веса!$E$43*AB6+Веса!$E$44*AC6+Веса!$E$45*AD6+Веса!$E$46*AE6+Веса!$E$47*AF6+Веса!$E$48*AG6,"")</f>
-        <v>-0.0361885484169353</v>
+        <f aca="false">IF(B6,Веса!$H$39*X6+Веса!$H$40*Y6+Веса!$H$41*Z6+Веса!$H$42*AA6+Веса!$H$43*AB6+Веса!$H$44*AC6+Веса!$H$45*AD6+Веса!$H$46*AE6+Веса!$H$47*AF6+Веса!$H$48*AG6,"")</f>
+        <v>-0.105373544045986</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3530,7 +3548,7 @@
         <v>культиватор 0.11×5.4</v>
       </c>
       <c r="B7" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q7,Энергетика!R7)</f>
+        <f aca="false">Энергетика!R7</f>
         <v>1</v>
       </c>
       <c r="C7" s="12" t="n">
@@ -3658,8 +3676,8 @@
         <v>-0.777170113402031</v>
       </c>
       <c r="AH7" s="24" t="n">
-        <f aca="false">IF(B7,Веса!$E$39*X7+Веса!$E$40*Y7+Веса!$E$41*Z7+Веса!$E$42*AA7+Веса!$E$43*AB7+Веса!$E$44*AC7+Веса!$E$45*AD7+Веса!$E$46*AE7+Веса!$E$47*AF7+Веса!$E$48*AG7,"")</f>
-        <v>-0.0659112675695613</v>
+        <f aca="false">IF(B7,Веса!$H$39*X7+Веса!$H$40*Y7+Веса!$H$41*Z7+Веса!$H$42*AA7+Веса!$H$43*AB7+Веса!$H$44*AC7+Веса!$H$45*AD7+Веса!$H$46*AE7+Веса!$H$47*AF7+Веса!$H$48*AG7,"")</f>
+        <v>-0.13356304235639</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3668,7 +3686,7 @@
         <v>культиватор 0.14×3.6</v>
       </c>
       <c r="B8" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q8,Энергетика!R8)</f>
+        <f aca="false">Энергетика!R8</f>
         <v>0</v>
       </c>
       <c r="C8" s="12" t="n">
@@ -3796,7 +3814,7 @@
         <v>-0.75669894791523</v>
       </c>
       <c r="AH8" s="24" t="str">
-        <f aca="false">IF(B8,Веса!$E$39*X8+Веса!$E$40*Y8+Веса!$E$41*Z8+Веса!$E$42*AA8+Веса!$E$43*AB8+Веса!$E$44*AC8+Веса!$E$45*AD8+Веса!$E$46*AE8+Веса!$E$47*AF8+Веса!$E$48*AG8,"")</f>
+        <f aca="false">IF(B8,Веса!$H$39*X8+Веса!$H$40*Y8+Веса!$H$41*Z8+Веса!$H$42*AA8+Веса!$H$43*AB8+Веса!$H$44*AC8+Веса!$H$45*AD8+Веса!$H$46*AE8+Веса!$H$47*AF8+Веса!$H$48*AG8,"")</f>
         <v/>
       </c>
     </row>
@@ -3806,7 +3824,7 @@
         <v>культиватор 0.14×4.5</v>
       </c>
       <c r="B9" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q9,Энергетика!R9)</f>
+        <f aca="false">Энергетика!R9</f>
         <v>0</v>
       </c>
       <c r="C9" s="12" t="n">
@@ -3934,7 +3952,7 @@
         <v>-0.776775902419084</v>
       </c>
       <c r="AH9" s="24" t="str">
-        <f aca="false">IF(B9,Веса!$E$39*X9+Веса!$E$40*Y9+Веса!$E$41*Z9+Веса!$E$42*AA9+Веса!$E$43*AB9+Веса!$E$44*AC9+Веса!$E$45*AD9+Веса!$E$46*AE9+Веса!$E$47*AF9+Веса!$E$48*AG9,"")</f>
+        <f aca="false">IF(B9,Веса!$H$39*X9+Веса!$H$40*Y9+Веса!$H$41*Z9+Веса!$H$42*AA9+Веса!$H$43*AB9+Веса!$H$44*AC9+Веса!$H$45*AD9+Веса!$H$46*AE9+Веса!$H$47*AF9+Веса!$H$48*AG9,"")</f>
         <v/>
       </c>
     </row>
@@ -3944,7 +3962,7 @@
         <v>фреза 0.08×1.8</v>
       </c>
       <c r="B10" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q10,Энергетика!R10)</f>
+        <f aca="false">Энергетика!R10</f>
         <v>1</v>
       </c>
       <c r="C10" s="12" t="n">
@@ -4072,8 +4090,8 @@
         <v>-0.69519164773615</v>
       </c>
       <c r="AH10" s="24" t="n">
-        <f aca="false">IF(B10,Веса!$E$39*X10+Веса!$E$40*Y10+Веса!$E$41*Z10+Веса!$E$42*AA10+Веса!$E$43*AB10+Веса!$E$44*AC10+Веса!$E$45*AD10+Веса!$E$46*AE10+Веса!$E$47*AF10+Веса!$E$48*AG10,"")</f>
-        <v>0.00195927823069966</v>
+        <f aca="false">IF(B10,Веса!$H$39*X10+Веса!$H$40*Y10+Веса!$H$41*Z10+Веса!$H$42*AA10+Веса!$H$43*AB10+Веса!$H$44*AC10+Веса!$H$45*AD10+Веса!$H$46*AE10+Веса!$H$47*AF10+Веса!$H$48*AG10,"")</f>
+        <v>-0.0648462670606879</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4082,7 +4100,7 @@
         <v>фреза 0.08×2.7</v>
       </c>
       <c r="B11" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q11,Энергетика!R11)</f>
+        <f aca="false">Энергетика!R11</f>
         <v>1</v>
       </c>
       <c r="C11" s="12" t="n">
@@ -4210,8 +4228,8 @@
         <v>-0.740455342431983</v>
       </c>
       <c r="AH11" s="24" t="n">
-        <f aca="false">IF(B11,Веса!$E$39*X11+Веса!$E$40*Y11+Веса!$E$41*Z11+Веса!$E$42*AA11+Веса!$E$43*AB11+Веса!$E$44*AC11+Веса!$E$45*AD11+Веса!$E$46*AE11+Веса!$E$47*AF11+Веса!$E$48*AG11,"")</f>
-        <v>-0.0408065793542917</v>
+        <f aca="false">IF(B11,Веса!$H$39*X11+Веса!$H$40*Y11+Веса!$H$41*Z11+Веса!$H$42*AA11+Веса!$H$43*AB11+Веса!$H$44*AC11+Веса!$H$45*AD11+Веса!$H$46*AE11+Веса!$H$47*AF11+Веса!$H$48*AG11,"")</f>
+        <v>-0.108944935976843</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4220,7 +4238,7 @@
         <v>фреза 0.08×3.6</v>
       </c>
       <c r="B12" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q12,Энергетика!R12)</f>
+        <f aca="false">Энергетика!R12</f>
         <v>1</v>
       </c>
       <c r="C12" s="12" t="n">
@@ -4348,8 +4366,8 @@
         <v>-0.758927322986181</v>
       </c>
       <c r="AH12" s="24" t="n">
-        <f aca="false">IF(B12,Веса!$E$39*X12+Веса!$E$40*Y12+Веса!$E$41*Z12+Веса!$E$42*AA12+Веса!$E$43*AB12+Веса!$E$44*AC12+Веса!$E$45*AD12+Веса!$E$46*AE12+Веса!$E$47*AF12+Веса!$E$48*AG12,"")</f>
-        <v>-0.0552696720316653</v>
+        <f aca="false">IF(B12,Веса!$H$39*X12+Веса!$H$40*Y12+Веса!$H$41*Z12+Веса!$H$42*AA12+Веса!$H$43*AB12+Веса!$H$44*AC12+Веса!$H$45*AD12+Веса!$H$46*AE12+Веса!$H$47*AF12+Веса!$H$48*AG12,"")</f>
+        <v>-0.122451861204219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4358,7 +4376,7 @@
         <v>фреза 0.12×1.8</v>
       </c>
       <c r="B13" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q13,Энергетика!R13)</f>
+        <f aca="false">Энергетика!R13</f>
         <v>1</v>
       </c>
       <c r="C13" s="12" t="n">
@@ -4486,8 +4504,8 @@
         <v>-0.742779517151242</v>
       </c>
       <c r="AH13" s="24" t="n">
-        <f aca="false">IF(B13,Веса!$E$39*X13+Веса!$E$40*Y13+Веса!$E$41*Z13+Веса!$E$42*AA13+Веса!$E$43*AB13+Веса!$E$44*AC13+Веса!$E$45*AD13+Веса!$E$46*AE13+Веса!$E$47*AF13+Веса!$E$48*AG13,"")</f>
-        <v>-0.0414085438954833</v>
+        <f aca="false">IF(B13,Веса!$H$39*X13+Веса!$H$40*Y13+Веса!$H$41*Z13+Веса!$H$42*AA13+Веса!$H$43*AB13+Веса!$H$44*AC13+Веса!$H$45*AD13+Веса!$H$46*AE13+Веса!$H$47*AF13+Веса!$H$48*AG13,"")</f>
+        <v>-0.109404523534765</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,7 +4514,7 @@
         <v>фреза 0.12×2.7</v>
       </c>
       <c r="B14" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q14,Энергетика!R14)</f>
+        <f aca="false">Энергетика!R14</f>
         <v>1</v>
       </c>
       <c r="C14" s="12" t="n">
@@ -4624,8 +4642,8 @@
         <v>-0.770974359546012</v>
       </c>
       <c r="AH14" s="24" t="n">
-        <f aca="false">IF(B14,Веса!$E$39*X14+Веса!$E$40*Y14+Веса!$E$41*Z14+Веса!$E$42*AA14+Веса!$E$43*AB14+Веса!$E$44*AC14+Веса!$E$45*AD14+Веса!$E$46*AE14+Веса!$E$47*AF14+Веса!$E$48*AG14,"")</f>
-        <v>-0.0669547731598334</v>
+        <f aca="false">IF(B14,Веса!$H$39*X14+Веса!$H$40*Y14+Веса!$H$41*Z14+Веса!$H$42*AA14+Веса!$H$43*AB14+Веса!$H$44*AC14+Веса!$H$45*AD14+Веса!$H$46*AE14+Веса!$H$47*AF14+Веса!$H$48*AG14,"")</f>
+        <v>-0.133311906382679</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4634,7 +4652,7 @@
         <v>фреза 0.12×3.6</v>
       </c>
       <c r="B15" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q15,Энергетика!R15)</f>
+        <f aca="false">Энергетика!R15</f>
         <v>1</v>
       </c>
       <c r="C15" s="12" t="n">
@@ -4762,8 +4780,8 @@
         <v>-0.784676388620838</v>
       </c>
       <c r="AH15" s="24" t="n">
-        <f aca="false">IF(B15,Веса!$E$39*X15+Веса!$E$40*Y15+Веса!$E$41*Z15+Веса!$E$42*AA15+Веса!$E$43*AB15+Веса!$E$44*AC15+Веса!$E$45*AD15+Веса!$E$46*AE15+Веса!$E$47*AF15+Веса!$E$48*AG15,"")</f>
-        <v>-0.106706428741133</v>
+        <f aca="false">IF(B15,Веса!$H$39*X15+Веса!$H$40*Y15+Веса!$H$41*Z15+Веса!$H$42*AA15+Веса!$H$43*AB15+Веса!$H$44*AC15+Веса!$H$45*AD15+Веса!$H$46*AE15+Веса!$H$47*AF15+Веса!$H$48*AG15,"")</f>
+        <v>-0.171225767807035</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4772,7 +4790,7 @@
         <v>фреза 0.16×1.8</v>
       </c>
       <c r="B16" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q16,Энергетика!R16)</f>
+        <f aca="false">Энергетика!R16</f>
         <v>1</v>
       </c>
       <c r="C16" s="12" t="n">
@@ -4900,8 +4918,8 @@
         <v>-0.76588453059444</v>
       </c>
       <c r="AH16" s="24" t="n">
-        <f aca="false">IF(B16,Веса!$E$39*X16+Веса!$E$40*Y16+Веса!$E$41*Z16+Веса!$E$42*AA16+Веса!$E$43*AB16+Веса!$E$44*AC16+Веса!$E$45*AD16+Веса!$E$46*AE16+Веса!$E$47*AF16+Веса!$E$48*AG16,"")</f>
-        <v>-0.0594334322477936</v>
+        <f aca="false">IF(B16,Веса!$H$39*X16+Веса!$H$40*Y16+Веса!$H$41*Z16+Веса!$H$42*AA16+Веса!$H$43*AB16+Веса!$H$44*AC16+Веса!$H$45*AD16+Веса!$H$46*AE16+Веса!$H$47*AF16+Веса!$H$48*AG16,"")</f>
+        <v>-0.126116139605442</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4910,8 +4928,8 @@
         <v>фреза 0.16×2.7</v>
       </c>
       <c r="B17" s="19" t="b">
-        <f aca="false">AND(Энергетика!Q17,Энергетика!R17)</f>
-        <v>0</v>
+        <f aca="false">Энергетика!R17</f>
+        <v>1</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">IF(S_task&gt;0,S_task,Смена!V17)</f>
@@ -5037,9 +5055,9 @@
         <f aca="false">IF(MAX(ABS(M17),ABS(W17))=0,0,1*(M17-W17)/MAX(ABS(M17),ABS(W17)))</f>
         <v>-0.788746690376324</v>
       </c>
-      <c r="AH17" s="24" t="str">
-        <f aca="false">IF(B17,Веса!$E$39*X17+Веса!$E$40*Y17+Веса!$E$41*Z17+Веса!$E$42*AA17+Веса!$E$43*AB17+Веса!$E$44*AC17+Веса!$E$45*AD17+Веса!$E$46*AE17+Веса!$E$47*AF17+Веса!$E$48*AG17,"")</f>
-        <v/>
+      <c r="AH17" s="24" t="n">
+        <f aca="false">IF(B17,Веса!$H$39*X17+Веса!$H$40*Y17+Веса!$H$41*Z17+Веса!$H$42*AA17+Веса!$H$43*AB17+Веса!$H$44*AC17+Веса!$H$45*AD17+Веса!$H$46*AE17+Веса!$H$47*AF17+Веса!$H$48*AG17,"")</f>
+        <v>-0.202038431135661</v>
       </c>
     </row>
   </sheetData>
@@ -5059,7 +5077,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH40"/>
+  <dimension ref="A1:AH42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -5068,7 +5086,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>412</v>
@@ -5101,67 +5119,67 @@
         <v>423</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="O1" s="9" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="P1" s="9" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="S1" s="9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="V1" s="9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="W1" s="9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="Y1" s="9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="Z1" s="9" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AA1" s="9" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AB1" s="9" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AC1" s="9" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AD1" s="9" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AF1" s="9" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG1" s="9" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AH1" s="9" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,7 +5249,7 @@
       </c>
       <c r="R2" s="15" t="n">
         <f aca="false">IF($L2,IF(F$37&gt;F$36,(F2-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.914332387770158</v>
+        <v>0.920405034633866</v>
       </c>
       <c r="S2" s="15" t="n">
         <f aca="false">IF($L2,IF(G$37&gt;G$36,(G2-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5251,47 +5269,47 @@
       </c>
       <c r="W2" s="15" t="n">
         <f aca="false">IF($L2,IF(K$37&gt;K$36,(K2-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.185489932675376</v>
+        <v>0.193889637401974</v>
       </c>
       <c r="Y2" s="15" t="n">
         <f aca="false">IF($L2,N2/N$38*LN(N2/N$38),0)</f>
-        <v>-1.99114823882613E-006</v>
+        <v>-1.77902407273223E-006</v>
       </c>
       <c r="Z2" s="15" t="n">
         <f aca="false">IF($L2,O2/O$38*LN(O2/O$38),0)</f>
-        <v>-1.82668770990439E-006</v>
+        <v>-1.59577182820938E-006</v>
       </c>
       <c r="AA2" s="15" t="n">
         <f aca="false">IF($L2,P2/P$38*LN(P2/P$38),0)</f>
-        <v>-0.0167802378649551</v>
+        <v>-0.0157817544771977</v>
       </c>
       <c r="AB2" s="15" t="n">
         <f aca="false">IF($L2,Q2/Q$38*LN(Q2/Q$38),0)</f>
-        <v>-0.164646906168434</v>
+        <v>-0.1646468812552</v>
       </c>
       <c r="AC2" s="15" t="n">
         <f aca="false">IF($L2,R2/R$38*LN(R2/R$38),0)</f>
-        <v>-0.173866376566833</v>
+        <v>-0.167670653984531</v>
       </c>
       <c r="AD2" s="15" t="n">
         <f aca="false">IF($L2,S2/S$38*LN(S2/S$38),0)</f>
-        <v>-0.0612251424773831</v>
+        <v>-0.0564801031037027</v>
       </c>
       <c r="AE2" s="15" t="n">
         <f aca="false">IF($L2,T2/T$38*LN(T2/T$38),0)</f>
-        <v>-0.094610966935777</v>
+        <v>-0.087777369245093</v>
       </c>
       <c r="AF2" s="15" t="n">
         <f aca="false">IF($L2,U2/U$38*LN(U2/U$38),0)</f>
-        <v>-1.81424555084807E-006</v>
+        <v>-1.58224862559416E-006</v>
       </c>
       <c r="AG2" s="15" t="n">
         <f aca="false">IF($L2,V2/V$38*LN(V2/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH2" s="15" t="n">
         <f aca="false">IF($L2,W2/W$38*LN(W2/W$38),0)</f>
-        <v>-0.0650182320294946</v>
+        <v>-0.0641374909167349</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5361,7 +5379,7 @@
       </c>
       <c r="R3" s="15" t="n">
         <f aca="false">IF($L3,IF(F$37&gt;F$36,(F3-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.996398879741584</v>
+        <v>0.996654217183392</v>
       </c>
       <c r="S3" s="15" t="n">
         <f aca="false">IF($L3,IF(G$37&gt;G$36,(G3-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5385,43 +5403,43 @@
       </c>
       <c r="Y3" s="15" t="n">
         <f aca="false">IF($L3,N3/N$38*LN(N3/N$38),0)</f>
-        <v>-0.13295532505332</v>
+        <v>-0.122366301514831</v>
       </c>
       <c r="Z3" s="15" t="n">
         <f aca="false">IF($L3,O3/O$38*LN(O3/O$38),0)</f>
-        <v>-0.088725431526075</v>
+        <v>-0.0797756123747118</v>
       </c>
       <c r="AA3" s="15" t="n">
         <f aca="false">IF($L3,P3/P$38*LN(P3/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB3" s="15" t="n">
         <f aca="false">IF($L3,Q3/Q$38*LN(Q3/Q$38),0)</f>
-        <v>-0.182984568066369</v>
+        <v>-0.182984541298323</v>
       </c>
       <c r="AC3" s="15" t="n">
         <f aca="false">IF($L3,R3/R$38*LN(R3/R$38),0)</f>
-        <v>-0.183586924363748</v>
+        <v>-0.176443732859793</v>
       </c>
       <c r="AD3" s="15" t="n">
         <f aca="false">IF($L3,S3/S$38*LN(S3/S$38),0)</f>
-        <v>-0.0971295017657366</v>
+        <v>-0.0899735938468135</v>
       </c>
       <c r="AE3" s="15" t="n">
         <f aca="false">IF($L3,T3/T$38*LN(T3/T$38),0)</f>
-        <v>-0.0740767501318165</v>
+        <v>-0.0685700191307427</v>
       </c>
       <c r="AF3" s="15" t="n">
         <f aca="false">IF($L3,U3/U$38*LN(U3/U$38),0)</f>
-        <v>-0.0849222131748751</v>
+        <v>-0.0762101381199307</v>
       </c>
       <c r="AG3" s="15" t="n">
         <f aca="false">IF($L3,V3/V$38*LN(V3/V$38),0)</f>
-        <v>-0.160059234006008</v>
+        <v>-0.149608185151357</v>
       </c>
       <c r="AH3" s="15" t="n">
         <f aca="false">IF($L3,W3/W$38*LN(W3/W$38),0)</f>
-        <v>-0.208501502148063</v>
+        <v>-0.20085083148008</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5491,7 +5509,7 @@
       </c>
       <c r="R4" s="15" t="n">
         <f aca="false">IF($L4,IF(F$37&gt;F$36,(F4-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.691188311345422</v>
+        <v>0.713078597138776</v>
       </c>
       <c r="S4" s="15" t="n">
         <f aca="false">IF($L4,IF(G$37&gt;G$36,(G4-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5511,47 +5529,47 @@
       </c>
       <c r="W4" s="15" t="n">
         <f aca="false">IF($L4,IF(K$37&gt;K$36,(K4-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.115691659048657</v>
+        <v>0.124811163557492</v>
       </c>
       <c r="Y4" s="15" t="n">
         <f aca="false">IF($L4,N4/N$38*LN(N4/N$38),0)</f>
-        <v>-0.00681432920566137</v>
+        <v>-0.00614756750104227</v>
       </c>
       <c r="Z4" s="15" t="n">
         <f aca="false">IF($L4,O4/O$38*LN(O4/O$38),0)</f>
-        <v>-0.0140935664443076</v>
+        <v>-0.0124919285557414</v>
       </c>
       <c r="AA4" s="15" t="n">
         <f aca="false">IF($L4,P4/P$38*LN(P4/P$38),0)</f>
-        <v>-1.25249723726808E-006</v>
+        <v>-1.16853366939625E-006</v>
       </c>
       <c r="AB4" s="15" t="n">
         <f aca="false">IF($L4,Q4/Q$38*LN(Q4/Q$38),0)</f>
-        <v>-0.168676935740122</v>
+        <v>-0.168676910400089</v>
       </c>
       <c r="AC4" s="15" t="n">
         <f aca="false">IF($L4,R4/R$38*LN(R4/R$38),0)</f>
-        <v>-0.144722099226559</v>
+        <v>-0.141642513534169</v>
       </c>
       <c r="AD4" s="15" t="n">
         <f aca="false">IF($L4,S4/S$38*LN(S4/S$38),0)</f>
-        <v>-0.0368678603115918</v>
+        <v>-0.033900972945169</v>
       </c>
       <c r="AE4" s="15" t="n">
         <f aca="false">IF($L4,T4/T$38*LN(T4/T$38),0)</f>
-        <v>-0.06575472050579</v>
+        <v>-0.0608083056315504</v>
       </c>
       <c r="AF4" s="15" t="n">
         <f aca="false">IF($L4,U4/U$38*LN(U4/U$38),0)</f>
-        <v>-0.014603001657097</v>
+        <v>-0.012926276289238</v>
       </c>
       <c r="AG4" s="15" t="n">
         <f aca="false">IF($L4,V4/V$38*LN(V4/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH4" s="15" t="n">
         <f aca="false">IF($L4,W4/W$38*LN(W4/W$38),0)</f>
-        <v>-0.0451563073680582</v>
+        <v>-0.0456416043846974</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5621,7 +5639,7 @@
       </c>
       <c r="R5" s="15" t="n">
         <f aca="false">IF($L5,IF(F$37&gt;F$36,(F5-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.794067020770589</v>
+        <v>0.80866471647906</v>
       </c>
       <c r="S5" s="15" t="n">
         <f aca="false">IF($L5,IF(G$37&gt;G$36,(G5-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5641,47 +5659,47 @@
       </c>
       <c r="W5" s="15" t="n">
         <f aca="false">IF($L5,IF(K$37&gt;K$36,(K5-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.926350430174263</v>
+        <v>0.927109957041729</v>
       </c>
       <c r="Y5" s="15" t="n">
         <f aca="false">IF($L5,N5/N$38*LN(N5/N$38),0)</f>
-        <v>-0.120887769177608</v>
+        <v>-0.111090978967389</v>
       </c>
       <c r="Z5" s="15" t="n">
         <f aca="false">IF($L5,O5/O$38*LN(O5/O$38),0)</f>
-        <v>-0.0718856298144445</v>
+        <v>-0.0644656191908916</v>
       </c>
       <c r="AA5" s="15" t="n">
         <f aca="false">IF($L5,P5/P$38*LN(P5/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB5" s="15" t="n">
         <f aca="false">IF($L5,Q5/Q$38*LN(Q5/Q$38),0)</f>
-        <v>-0.18748999853378</v>
+        <v>-0.187489971345647</v>
       </c>
       <c r="AC5" s="15" t="n">
         <f aca="false">IF($L5,R5/R$38*LN(R5/R$38),0)</f>
-        <v>-0.15869201181754</v>
+        <v>-0.154066932199278</v>
       </c>
       <c r="AD5" s="15" t="n">
         <f aca="false">IF($L5,S5/S$38*LN(S5/S$38),0)</f>
-        <v>-0.0609623224652217</v>
+        <v>-0.0562358442605781</v>
       </c>
       <c r="AE5" s="15" t="n">
         <f aca="false">IF($L5,T5/T$38*LN(T5/T$38),0)</f>
-        <v>-0.0362217025575046</v>
+        <v>-0.0333705323299365</v>
       </c>
       <c r="AF5" s="15" t="n">
         <f aca="false">IF($L5,U5/U$38*LN(U5/U$38),0)</f>
-        <v>-0.0675708386297342</v>
+        <v>-0.0604718497281633</v>
       </c>
       <c r="AG5" s="15" t="n">
         <f aca="false">IF($L5,V5/V$38*LN(V5/V$38),0)</f>
-        <v>-0.150255194903306</v>
+        <v>-0.140290992733866</v>
       </c>
       <c r="AH5" s="15" t="n">
         <f aca="false">IF($L5,W5/W$38*LN(W5/W$38),0)</f>
-        <v>-0.199119345731267</v>
+        <v>-0.191768661898512</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5751,7 +5769,7 @@
       </c>
       <c r="R6" s="15" t="n">
         <f aca="false">IF($L6,IF(F$37&gt;F$36,(F6-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.452765268575861</v>
+        <v>0.491556247694626</v>
       </c>
       <c r="S6" s="15" t="n">
         <f aca="false">IF($L6,IF(G$37&gt;G$36,(G6-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5771,47 +5789,47 @@
       </c>
       <c r="W6" s="15" t="n">
         <f aca="false">IF($L6,IF(K$37&gt;K$36,(K6-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.0677235454814905</v>
+        <v>0.0773377246564164</v>
       </c>
       <c r="Y6" s="15" t="n">
         <f aca="false">IF($L6,N6/N$38*LN(N6/N$38),0)</f>
-        <v>-0.0076135626906121</v>
+        <v>-0.00687083794276808</v>
       </c>
       <c r="Z6" s="15" t="n">
         <f aca="false">IF($L6,O6/O$38*LN(O6/O$38),0)</f>
-        <v>-0.0157040517936754</v>
+        <v>-0.0139264626215068</v>
       </c>
       <c r="AA6" s="15" t="n">
         <f aca="false">IF($L6,P6/P$38*LN(P6/P$38),0)</f>
-        <v>-0.000608327829386177</v>
+        <v>-0.000569315071873518</v>
       </c>
       <c r="AB6" s="15" t="n">
         <f aca="false">IF($L6,Q6/Q$38*LN(Q6/Q$38),0)</f>
-        <v>-0.17357692121598</v>
+        <v>-0.17357689537128</v>
       </c>
       <c r="AC6" s="15" t="n">
         <f aca="false">IF($L6,R6/R$38*LN(R6/R$38),0)</f>
-        <v>-0.107961992370657</v>
+        <v>-0.109437314098661</v>
       </c>
       <c r="AD6" s="15" t="n">
         <f aca="false">IF($L6,S6/S$38*LN(S6/S$38),0)</f>
-        <v>-1.69961801354465E-006</v>
+        <v>-1.53993213600639E-006</v>
       </c>
       <c r="AE6" s="15" t="n">
         <f aca="false">IF($L6,T6/T$38*LN(T6/T$38),0)</f>
-        <v>-0.0346515143172814</v>
+        <v>-0.031916619088027</v>
       </c>
       <c r="AF6" s="15" t="n">
         <f aca="false">IF($L6,U6/U$38*LN(U6/U$38),0)</f>
-        <v>-0.0162691891302206</v>
+        <v>-0.0144086584432992</v>
       </c>
       <c r="AG6" s="15" t="n">
         <f aca="false">IF($L6,V6/V$38*LN(V6/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH6" s="15" t="n">
         <f aca="false">IF($L6,W6/W$38*LN(W6/W$38),0)</f>
-        <v>-0.0294906755909262</v>
+        <v>-0.0312132955062305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5881,7 +5899,7 @@
       </c>
       <c r="R7" s="15" t="n">
         <f aca="false">IF($L7,IF(F$37&gt;F$36,(F7-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.576980179257957</v>
+        <v>0.606966144870077</v>
       </c>
       <c r="S7" s="15" t="n">
         <f aca="false">IF($L7,IF(G$37&gt;G$36,(G7-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -5901,47 +5919,47 @@
       </c>
       <c r="W7" s="15" t="n">
         <f aca="false">IF($L7,IF(K$37&gt;K$36,(K7-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.825956379634775</v>
+        <v>0.827751227463084</v>
       </c>
       <c r="Y7" s="15" t="n">
         <f aca="false">IF($L7,N7/N$38*LN(N7/N$38),0)</f>
-        <v>-0.113222072276067</v>
+        <v>-0.103946547305135</v>
       </c>
       <c r="Z7" s="15" t="n">
         <f aca="false">IF($L7,O7/O$38*LN(O7/O$38),0)</f>
-        <v>-0.0608164442276998</v>
+        <v>-0.0544410570450318</v>
       </c>
       <c r="AA7" s="15" t="n">
         <f aca="false">IF($L7,P7/P$38*LN(P7/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB7" s="15" t="n">
         <f aca="false">IF($L7,Q7/Q$38*LN(Q7/Q$38),0)</f>
-        <v>-0.19297175762032</v>
+        <v>-0.192971729941251</v>
       </c>
       <c r="AC7" s="15" t="n">
         <f aca="false">IF($L7,R7/R$38*LN(R7/R$38),0)</f>
-        <v>-0.127969375174455</v>
+        <v>-0.126873627073621</v>
       </c>
       <c r="AD7" s="15" t="n">
         <f aca="false">IF($L7,S7/S$38*LN(S7/S$38),0)</f>
-        <v>-0.0314100353772235</v>
+        <v>-0.0288583848289632</v>
       </c>
       <c r="AE7" s="15" t="n">
         <f aca="false">IF($L7,T7/T$38*LN(T7/T$38),0)</f>
-        <v>-1.66972797761875E-006</v>
+        <v>-1.51640081233407E-006</v>
       </c>
       <c r="AF7" s="15" t="n">
         <f aca="false">IF($L7,U7/U$38*LN(U7/U$38),0)</f>
-        <v>-0.0561057787004976</v>
+        <v>-0.0501148943270826</v>
       </c>
       <c r="AG7" s="15" t="n">
         <f aca="false">IF($L7,V7/V$38*LN(V7/V$38),0)</f>
-        <v>-0.144092245219751</v>
+        <v>-0.134445609189706</v>
       </c>
       <c r="AH7" s="15" t="n">
         <f aca="false">IF($L7,W7/W$38*LN(W7/W$38),0)</f>
-        <v>-0.185526438669665</v>
+        <v>-0.178649391931411</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6011,7 +6029,7 @@
       </c>
       <c r="R8" s="15" t="n">
         <f aca="false">IF($L8,IF(F$37&gt;F$36,(F8-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.6837870023783</v>
+        <v>0.706201932315135</v>
       </c>
       <c r="S8" s="15" t="n">
         <f aca="false">IF($L8,IF(G$37&gt;G$36,(G8-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6031,47 +6049,47 @@
       </c>
       <c r="W8" s="15" t="n">
         <f aca="false">IF($L8,IF(K$37&gt;K$36,(K8-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.109241444196727</v>
+        <v>0.118427467016181</v>
       </c>
       <c r="Y8" s="15" t="n">
         <f aca="false">IF($L8,N8/N$38*LN(N8/N$38),0)</f>
-        <v>-0.0283429203311924</v>
+        <v>-0.0257126012221538</v>
       </c>
       <c r="Z8" s="15" t="n">
         <f aca="false">IF($L8,O8/O$38*LN(O8/O$38),0)</f>
-        <v>-0.0559009973091858</v>
+        <v>-0.0499994775193017</v>
       </c>
       <c r="AA8" s="15" t="n">
         <f aca="false">IF($L8,P8/P$38*LN(P8/P$38),0)</f>
-        <v>-0.000138925560628058</v>
+        <v>-0.000129873801537629</v>
       </c>
       <c r="AB8" s="15" t="n">
         <f aca="false">IF($L8,Q8/Q$38*LN(Q8/Q$38),0)</f>
-        <v>-0.212965733551187</v>
+        <v>-0.21296570428394</v>
       </c>
       <c r="AC8" s="15" t="n">
         <f aca="false">IF($L8,R8/R$38*LN(R8/R$38),0)</f>
-        <v>-0.143678242454519</v>
+        <v>-0.140718041917233</v>
       </c>
       <c r="AD8" s="15" t="n">
         <f aca="false">IF($L8,S8/S$38*LN(S8/S$38),0)</f>
-        <v>-0.0815254998084013</v>
+        <v>-0.0753868752082788</v>
       </c>
       <c r="AE8" s="15" t="n">
         <f aca="false">IF($L8,T8/T$38*LN(T8/T$38),0)</f>
-        <v>-0.10748192513611</v>
+        <v>-0.09985769413016</v>
       </c>
       <c r="AF8" s="15" t="n">
         <f aca="false">IF($L8,U8/U$38*LN(U8/U$38),0)</f>
-        <v>-0.0577611535943633</v>
+        <v>-0.0516081838674124</v>
       </c>
       <c r="AG8" s="15" t="n">
         <f aca="false">IF($L8,V8/V$38*LN(V8/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH8" s="15" t="n">
         <f aca="false">IF($L8,W8/W$38*LN(W8/W$38),0)</f>
-        <v>-0.0431669734031522</v>
+        <v>-0.0437996823399066</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6141,7 +6159,7 @@
       </c>
       <c r="R9" s="15" t="n">
         <f aca="false">IF($L9,IF(F$37&gt;F$36,(F9-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.771707260242427</v>
+        <v>0.78788993469761</v>
       </c>
       <c r="S9" s="15" t="n">
         <f aca="false">IF($L9,IF(G$37&gt;G$36,(G9-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6161,47 +6179,47 @@
       </c>
       <c r="W9" s="15" t="n">
         <f aca="false">IF($L9,IF(K$37&gt;K$36,(K9-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.90521153486818</v>
+        <v>0.906189058133658</v>
       </c>
       <c r="Y9" s="15" t="n">
         <f aca="false">IF($L9,N9/N$38*LN(N9/N$38),0)</f>
-        <v>-0.149059546226539</v>
+        <v>-0.137469947651451</v>
       </c>
       <c r="Z9" s="15" t="n">
         <f aca="false">IF($L9,O9/O$38*LN(O9/O$38),0)</f>
-        <v>-0.110392097876768</v>
+        <v>-0.099581008861886</v>
       </c>
       <c r="AA9" s="15" t="n">
         <f aca="false">IF($L9,P9/P$38*LN(P9/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB9" s="15" t="n">
         <f aca="false">IF($L9,Q9/Q$38*LN(Q9/Q$38),0)</f>
-        <v>-0.23719509908782</v>
+        <v>-0.237195068385808</v>
       </c>
       <c r="AC9" s="15" t="n">
         <f aca="false">IF($L9,R9/R$38*LN(R9/R$38),0)</f>
-        <v>-0.155738069186573</v>
+        <v>-0.151431759633679</v>
       </c>
       <c r="AD9" s="15" t="n">
         <f aca="false">IF($L9,S9/S$38*LN(S9/S$38),0)</f>
-        <v>-0.104496292249956</v>
+        <v>-0.0968766791064747</v>
       </c>
       <c r="AE9" s="15" t="n">
         <f aca="false">IF($L9,T9/T$38*LN(T9/T$38),0)</f>
-        <v>-0.0803922432252994</v>
+        <v>-0.0744689602083958</v>
       </c>
       <c r="AF9" s="15" t="n">
         <f aca="false">IF($L9,U9/U$38*LN(U9/U$38),0)</f>
-        <v>-0.107139979940136</v>
+        <v>-0.096475806277611</v>
       </c>
       <c r="AG9" s="15" t="n">
         <f aca="false">IF($L9,V9/V$38*LN(V9/V$38),0)</f>
-        <v>-0.173315496382223</v>
+        <v>-0.162243926536885</v>
       </c>
       <c r="AH9" s="15" t="n">
         <f aca="false">IF($L9,W9/W$38*LN(W9/W$38),0)</f>
-        <v>-0.196336996236006</v>
+        <v>-0.189079592114495</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6271,7 +6289,7 @@
       </c>
       <c r="R10" s="15" t="n">
         <f aca="false">IF($L10,IF(F$37&gt;F$36,(F10-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.391337643110703</v>
+        <v>0.43448293902551</v>
       </c>
       <c r="S10" s="15" t="n">
         <f aca="false">IF($L10,IF(G$37&gt;G$36,(G10-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6291,47 +6309,47 @@
       </c>
       <c r="W10" s="15" t="n">
         <f aca="false">IF($L10,IF(K$37&gt;K$36,(K10-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.0532448328743759</v>
+        <v>0.0630083248279734</v>
       </c>
       <c r="Y10" s="15" t="n">
         <f aca="false">IF($L10,N10/N$38*LN(N10/N$38),0)</f>
-        <v>-0.0287303763107537</v>
+        <v>-0.0260659981721968</v>
       </c>
       <c r="Z10" s="15" t="n">
         <f aca="false">IF($L10,O10/O$38*LN(O10/O$38),0)</f>
-        <v>-0.0566290502467162</v>
+        <v>-0.0506569528755978</v>
       </c>
       <c r="AA10" s="15" t="n">
         <f aca="false">IF($L10,P10/P$38*LN(P10/P$38),0)</f>
-        <v>-0.000867807155289646</v>
+        <v>-0.000812417244137503</v>
       </c>
       <c r="AB10" s="15" t="n">
         <f aca="false">IF($L10,Q10/Q$38*LN(Q10/Q$38),0)</f>
-        <v>-0.218274483858432</v>
+        <v>-0.218274454227445</v>
       </c>
       <c r="AC10" s="15" t="n">
         <f aca="false">IF($L10,R10/R$38*LN(R10/R$38),0)</f>
-        <v>-0.0972352605067981</v>
+        <v>-0.100190168186479</v>
       </c>
       <c r="AD10" s="15" t="n">
         <f aca="false">IF($L10,S10/S$38*LN(S10/S$38),0)</f>
-        <v>-0.0452124540165071</v>
+        <v>-0.0416229426669906</v>
       </c>
       <c r="AE10" s="15" t="n">
         <f aca="false">IF($L10,T10/T$38*LN(T10/T$38),0)</f>
-        <v>-0.0709188602487245</v>
+        <v>-0.0656232186881384</v>
       </c>
       <c r="AF10" s="15" t="n">
         <f aca="false">IF($L10,U10/U$38*LN(U10/U$38),0)</f>
-        <v>-0.0585111975068402</v>
+        <v>-0.0522850212579357</v>
       </c>
       <c r="AG10" s="15" t="n">
         <f aca="false">IF($L10,V10/V$38*LN(V10/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH10" s="15" t="n">
         <f aca="false">IF($L10,W10/W$38*LN(W10/W$38),0)</f>
-        <v>-0.0242654300615069</v>
+        <v>-0.0264527107541021</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6401,7 +6419,7 @@
       </c>
       <c r="R11" s="15" t="n">
         <f aca="false">IF($L11,IF(F$37&gt;F$36,(F11-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.500818462126149</v>
+        <v>0.536203175314968</v>
       </c>
       <c r="S11" s="15" t="n">
         <f aca="false">IF($L11,IF(G$37&gt;G$36,(G11-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6421,47 +6439,47 @@
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">IF($L11,IF(K$37&gt;K$36,(K11-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.78357670453293</v>
+        <v>0.785808595848485</v>
       </c>
       <c r="Y11" s="15" t="n">
         <f aca="false">IF($L11,N11/N$38*LN(N11/N$38),0)</f>
-        <v>-0.138682837442359</v>
+        <v>-0.127730342612519</v>
       </c>
       <c r="Z11" s="15" t="n">
         <f aca="false">IF($L11,O11/O$38*LN(O11/O$38),0)</f>
-        <v>-0.0965219169450481</v>
+        <v>-0.0868882780631824</v>
       </c>
       <c r="AA11" s="15" t="n">
         <f aca="false">IF($L11,P11/P$38*LN(P11/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB11" s="15" t="n">
         <f aca="false">IF($L11,Q11/Q$38*LN(Q11/Q$38),0)</f>
-        <v>-0.243176749883541</v>
+        <v>-0.243176718923783</v>
       </c>
       <c r="AC11" s="15" t="n">
         <f aca="false">IF($L11,R11/R$38*LN(R11/R$38),0)</f>
-        <v>-0.115949028756361</v>
+        <v>-0.11637001379022</v>
       </c>
       <c r="AD11" s="15" t="n">
         <f aca="false">IF($L11,S11/S$38*LN(S11/S$38),0)</f>
-        <v>-0.070391999833935</v>
+        <v>-0.0650078876491034</v>
       </c>
       <c r="AE11" s="15" t="n">
         <f aca="false">IF($L11,T11/T$38*LN(T11/T$38),0)</f>
-        <v>-0.044710060947661</v>
+        <v>-0.0412391426296632</v>
       </c>
       <c r="AF11" s="15" t="n">
         <f aca="false">IF($L11,U11/U$38*LN(U11/U$38),0)</f>
-        <v>-0.0929284636625501</v>
+        <v>-0.0834980960113598</v>
       </c>
       <c r="AG11" s="15" t="n">
         <f aca="false">IF($L11,V11/V$38*LN(V11/V$38),0)</f>
-        <v>-0.164752505654664</v>
+        <v>-0.154076666152075</v>
       </c>
       <c r="AH11" s="15" t="n">
         <f aca="false">IF($L11,W11/W$38*LN(W11/W$38),0)</f>
-        <v>-0.179486340595867</v>
+        <v>-0.172833814635508</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6531,7 +6549,7 @@
       </c>
       <c r="R12" s="15" t="n">
         <f aca="false">IF($L12,IF(F$37&gt;F$36,(F12-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.0753253913710559</v>
+        <v>0.140871316401592</v>
       </c>
       <c r="S12" s="15" t="n">
         <f aca="false">IF($L12,IF(G$37&gt;G$36,(G12-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6551,47 +6569,47 @@
       </c>
       <c r="W12" s="15" t="n">
         <f aca="false">IF($L12,IF(K$37&gt;K$36,(K12-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.014592243294475</v>
+        <v>0.0247543428943209</v>
       </c>
       <c r="Y12" s="15" t="n">
         <f aca="false">IF($L12,N12/N$38*LN(N12/N$38),0)</f>
-        <v>-0.0302256552824623</v>
+        <v>-0.0274302009714468</v>
       </c>
       <c r="Z12" s="15" t="n">
         <f aca="false">IF($L12,O12/O$38*LN(O12/O$38),0)</f>
-        <v>-0.0594318148472806</v>
+        <v>-0.0531892859774906</v>
       </c>
       <c r="AA12" s="15" t="n">
         <f aca="false">IF($L12,P12/P$38*LN(P12/P$38),0)</f>
-        <v>-0.0015441645751677</v>
+        <v>-0.00144646337808612</v>
       </c>
       <c r="AB12" s="15" t="n">
         <f aca="false">IF($L12,Q12/Q$38*LN(Q12/Q$38),0)</f>
-        <v>-0.224741383232598</v>
+        <v>-0.22474135319448</v>
       </c>
       <c r="AC12" s="15" t="n">
         <f aca="false">IF($L12,R12/R$38*LN(R12/R$38),0)</f>
-        <v>-0.0272446462936226</v>
+        <v>-0.0427200653972034</v>
       </c>
       <c r="AD12" s="15" t="n">
         <f aca="false">IF($L12,S12/S$38*LN(S12/S$38),0)</f>
-        <v>-0.0141387898936304</v>
+        <v>-0.0129479400830281</v>
       </c>
       <c r="AE12" s="15" t="n">
         <f aca="false">IF($L12,T12/T$38*LN(T12/T$38),0)</f>
-        <v>-0.0434450268746466</v>
+        <v>-0.040065544111424</v>
       </c>
       <c r="AF12" s="15" t="n">
         <f aca="false">IF($L12,U12/U$38*LN(U12/U$38),0)</f>
-        <v>-0.0613981685595404</v>
+        <v>-0.054891570711705</v>
       </c>
       <c r="AG12" s="15" t="n">
         <f aca="false">IF($L12,V12/V$38*LN(V12/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH12" s="15" t="n">
         <f aca="false">IF($L12,W12/W$38*LN(W12/W$38),0)</f>
-        <v>-0.00824240459507273</v>
+        <v>-0.0122245122276038</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6661,7 +6679,7 @@
       </c>
       <c r="R13" s="15" t="n">
         <f aca="false">IF($L13,IF(F$37&gt;F$36,(F13-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.206153621684403</v>
+        <v>0.262425745939864</v>
       </c>
       <c r="S13" s="15" t="n">
         <f aca="false">IF($L13,IF(G$37&gt;G$36,(G13-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -6681,47 +6699,47 @@
       </c>
       <c r="W13" s="15" t="n">
         <f aca="false">IF($L13,IF(K$37&gt;K$36,(K13-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.683175614871874</v>
+        <v>0.686442899739725</v>
       </c>
       <c r="Y13" s="15" t="n">
         <f aca="false">IF($L13,N13/N$38*LN(N13/N$38),0)</f>
-        <v>-0.132640027553873</v>
+        <v>-0.122071251151882</v>
       </c>
       <c r="Z13" s="15" t="n">
         <f aca="false">IF($L13,O13/O$38*LN(O13/O$38),0)</f>
-        <v>-0.088292943889809</v>
+        <v>-0.0793815137916576</v>
       </c>
       <c r="AA13" s="15" t="n">
         <f aca="false">IF($L13,P13/P$38*LN(P13/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB13" s="15" t="n">
         <f aca="false">IF($L13,Q13/Q$38*LN(Q13/Q$38),0)</f>
-        <v>-0.250469373967409</v>
+        <v>-0.25046934275227</v>
       </c>
       <c r="AC13" s="15" t="n">
         <f aca="false">IF($L13,R13/R$38*LN(R13/R$38),0)</f>
-        <v>-0.0603022342317882</v>
+        <v>-0.0690500244876757</v>
       </c>
       <c r="AD13" s="15" t="n">
         <f aca="false">IF($L13,S13/S$38*LN(S13/S$38),0)</f>
-        <v>-0.0436270556438433</v>
+        <v>-0.0401547300046589</v>
       </c>
       <c r="AE13" s="15" t="n">
         <f aca="false">IF($L13,T13/T$38*LN(T13/T$38),0)</f>
-        <v>-0.0143398939813577</v>
+        <v>-0.0131603263751343</v>
       </c>
       <c r="AF13" s="15" t="n">
         <f aca="false">IF($L13,U13/U$38*LN(U13/U$38),0)</f>
-        <v>-0.0844776511719033</v>
+        <v>-0.0758059445285295</v>
       </c>
       <c r="AG13" s="15" t="n">
         <f aca="false">IF($L13,V13/V$38*LN(V13/V$38),0)</f>
-        <v>-0.159801591345966</v>
+        <v>-0.149363040333097</v>
       </c>
       <c r="AH13" s="15" t="n">
         <f aca="false">IF($L13,W13/W$38*LN(W13/W$38),0)</f>
-        <v>-0.164384981391074</v>
+        <v>-0.158329751095722</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7311,7 +7329,7 @@
       </c>
       <c r="R18" s="15" t="n">
         <f aca="false">IF($L18,IF(F$37&gt;F$36,(F18-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.929755305810106</v>
+        <v>0.93473469421629</v>
       </c>
       <c r="S18" s="15" t="n">
         <f aca="false">IF($L18,IF(G$37&gt;G$36,(G18-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -7331,47 +7349,47 @@
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">IF($L18,IF(K$37&gt;K$36,(K18-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.181687645049995</v>
+        <v>0.190126561144762</v>
       </c>
       <c r="Y18" s="15" t="n">
         <f aca="false">IF($L18,N18/N$38*LN(N18/N$38),0)</f>
-        <v>-0.0613211164698217</v>
+        <v>-0.0559202569716979</v>
       </c>
       <c r="Z18" s="15" t="n">
         <f aca="false">IF($L18,O18/O$38*LN(O18/O$38),0)</f>
-        <v>-0.115424520125221</v>
+        <v>-0.104198870124675</v>
       </c>
       <c r="AA18" s="15" t="n">
         <f aca="false">IF($L18,P18/P$38*LN(P18/P$38),0)</f>
-        <v>-0.0152159647852126</v>
+        <v>-0.0143070443083522</v>
       </c>
       <c r="AB18" s="15" t="n">
         <f aca="false">IF($L18,Q18/Q$38*LN(Q18/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC18" s="15" t="n">
         <f aca="false">IF($L18,R18/R$38*LN(R18/R$38),0)</f>
-        <v>-0.175730487960318</v>
+        <v>-0.169349512391634</v>
       </c>
       <c r="AD18" s="15" t="n">
         <f aca="false">IF($L18,S18/S$38*LN(S18/S$38),0)</f>
-        <v>-0.187042294079605</v>
+        <v>-0.175045653750992</v>
       </c>
       <c r="AE18" s="15" t="n">
         <f aca="false">IF($L18,T18/T$38*LN(T18/T$38),0)</f>
-        <v>-0.216949773996463</v>
+        <v>-0.204132932252402</v>
       </c>
       <c r="AF18" s="15" t="n">
         <f aca="false">IF($L18,U18/U$38*LN(U18/U$38),0)</f>
-        <v>-0.118923854683636</v>
+        <v>-0.1072776796149</v>
       </c>
       <c r="AG18" s="15" t="n">
         <f aca="false">IF($L18,V18/V$38*LN(V18/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH18" s="15" t="n">
         <f aca="false">IF($L18,W18/W$38*LN(W18/W$38),0)</f>
-        <v>-0.0640026627120233</v>
+        <v>-0.0631878544442841</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7465,43 +7483,43 @@
       </c>
       <c r="Y19" s="15" t="n">
         <f aca="false">IF($L19,N19/N$38*LN(N19/N$38),0)</f>
-        <v>-0.219350333094834</v>
+        <v>-0.204303602743046</v>
       </c>
       <c r="Z19" s="15" t="n">
         <f aca="false">IF($L19,O19/O$38*LN(O19/O$38),0)</f>
-        <v>-0.198973738473889</v>
+        <v>-0.18199988959069</v>
       </c>
       <c r="AA19" s="15" t="n">
         <f aca="false">IF($L19,P19/P$38*LN(P19/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB19" s="15" t="n">
         <f aca="false">IF($L19,Q19/Q$38*LN(Q19/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC19" s="15" t="n">
         <f aca="false">IF($L19,R19/R$38*LN(R19/R$38),0)</f>
-        <v>-0.184002653558498</v>
+        <v>-0.176819966926359</v>
       </c>
       <c r="AD19" s="15" t="n">
         <f aca="false">IF($L19,S19/S$38*LN(S19/S$38),0)</f>
-        <v>-0.221439151502464</v>
+        <v>-0.208172634467566</v>
       </c>
       <c r="AE19" s="15" t="n">
         <f aca="false">IF($L19,T19/T$38*LN(T19/T$38),0)</f>
-        <v>-0.197380825024281</v>
+        <v>-0.185251050590627</v>
       </c>
       <c r="AF19" s="15" t="n">
         <f aca="false">IF($L19,U19/U$38*LN(U19/U$38),0)</f>
-        <v>-0.197342097468032</v>
+        <v>-0.18025374521068</v>
       </c>
       <c r="AG19" s="15" t="n">
         <f aca="false">IF($L19,V19/V$38*LN(V19/V$38),0)</f>
-        <v>-0.232957516178811</v>
+        <v>-0.219742601541559</v>
       </c>
       <c r="AH19" s="15" t="n">
         <f aca="false">IF($L19,W19/W$38*LN(W19/W$38),0)</f>
-        <v>-0.208501502148063</v>
+        <v>-0.20085083148008</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7571,7 +7589,7 @@
       </c>
       <c r="R20" s="15" t="n">
         <f aca="false">IF($L20,IF(F$37&gt;F$36,(F20-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.664789450730131</v>
+        <v>0.688551028166343</v>
       </c>
       <c r="S20" s="15" t="n">
         <f aca="false">IF($L20,IF(G$37&gt;G$36,(G20-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -7591,47 +7609,47 @@
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">IF($L20,IF(K$37&gt;K$36,(K20-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.0997830292269462</v>
+        <v>0.109066592639911</v>
       </c>
       <c r="Y20" s="15" t="n">
         <f aca="false">IF($L20,N20/N$38*LN(N20/N$38),0)</f>
-        <v>-0.052853612496994</v>
+        <v>-0.048140497966586</v>
       </c>
       <c r="Z20" s="15" t="n">
         <f aca="false">IF($L20,O20/O$38*LN(O20/O$38),0)</f>
-        <v>-0.10059096754312</v>
+        <v>-0.0906066715653102</v>
       </c>
       <c r="AA20" s="15" t="n">
         <f aca="false">IF($L20,P20/P$38*LN(P20/P$38),0)</f>
-        <v>-0.000231661871580921</v>
+        <v>-0.000216641424484706</v>
       </c>
       <c r="AB20" s="15" t="n">
         <f aca="false">IF($L20,Q20/Q$38*LN(Q20/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC20" s="15" t="n">
         <f aca="false">IF($L20,R20/R$38*LN(R20/R$38),0)</f>
-        <v>-0.140973545365043</v>
+        <v>-0.138325247879635</v>
       </c>
       <c r="AD20" s="15" t="n">
         <f aca="false">IF($L20,S20/S$38*LN(S20/S$38),0)</f>
-        <v>-0.12888562027097</v>
+        <v>-0.119809630341091</v>
       </c>
       <c r="AE20" s="15" t="n">
         <f aca="false">IF($L20,T20/T$38*LN(T20/T$38),0)</f>
-        <v>-0.153336124275657</v>
+        <v>-0.143171571435005</v>
       </c>
       <c r="AF20" s="15" t="n">
         <f aca="false">IF($L20,U20/U$38*LN(U20/U$38),0)</f>
-        <v>-0.103712216313531</v>
+        <v>-0.0933407455956682</v>
       </c>
       <c r="AG20" s="15" t="n">
         <f aca="false">IF($L20,V20/V$38*LN(V20/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH20" s="15" t="n">
         <f aca="false">IF($L20,W20/W$38*LN(W20/W$38),0)</f>
-        <v>-0.040191221978363</v>
+        <v>-0.0410489957473623</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7701,7 +7719,7 @@
       </c>
       <c r="R21" s="15" t="n">
         <f aca="false">IF($L21,IF(F$37&gt;F$36,(F21-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.759989480688371</v>
+        <v>0.777002773679403</v>
       </c>
       <c r="S21" s="15" t="n">
         <f aca="false">IF($L21,IF(G$37&gt;G$36,(G21-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -7721,47 +7739,47 @@
       </c>
       <c r="W21" s="15" t="n">
         <f aca="false">IF($L21,IF(K$37&gt;K$36,(K21-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.889713589769299</v>
+        <v>0.890850936722781</v>
       </c>
       <c r="Y21" s="15" t="n">
         <f aca="false">IF($L21,N21/N$38*LN(N21/N$38),0)</f>
-        <v>-0.181916363238133</v>
+        <v>-0.168507409349113</v>
       </c>
       <c r="Z21" s="15" t="n">
         <f aca="false">IF($L21,O21/O$38*LN(O21/O$38),0)</f>
-        <v>-0.152721032043203</v>
+        <v>-0.138646807516624</v>
       </c>
       <c r="AA21" s="15" t="n">
         <f aca="false">IF($L21,P21/P$38*LN(P21/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB21" s="15" t="n">
         <f aca="false">IF($L21,Q21/Q$38*LN(Q21/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC21" s="15" t="n">
         <f aca="false">IF($L21,R21/R$38*LN(R21/R$38),0)</f>
-        <v>-0.154172338271518</v>
+        <v>-0.150036725831513</v>
       </c>
       <c r="AD21" s="15" t="n">
         <f aca="false">IF($L21,S21/S$38*LN(S21/S$38),0)</f>
-        <v>-0.151372317153322</v>
+        <v>-0.141067902190849</v>
       </c>
       <c r="AE21" s="15" t="n">
         <f aca="false">IF($L21,T21/T$38*LN(T21/T$38),0)</f>
-        <v>-0.12675410297155</v>
+        <v>-0.118007614504559</v>
       </c>
       <c r="AF21" s="15" t="n">
         <f aca="false">IF($L21,U21/U$38*LN(U21/U$38),0)</f>
-        <v>-0.150334935035047</v>
+        <v>-0.13626497349869</v>
       </c>
       <c r="AG21" s="15" t="n">
         <f aca="false">IF($L21,V21/V$38*LN(V21/V$38),0)</f>
-        <v>-0.200874826474067</v>
+        <v>-0.188667505813474</v>
       </c>
       <c r="AH21" s="15" t="n">
         <f aca="false">IF($L21,W21/W$38*LN(W21/W$38),0)</f>
-        <v>-0.194270736618917</v>
+        <v>-0.187083846707874</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7831,7 +7849,7 @@
       </c>
       <c r="R22" s="15" t="n">
         <f aca="false">IF($L22,IF(F$37&gt;F$36,(F22-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.450003163563979</v>
+        <v>0.488989935376253</v>
       </c>
       <c r="S22" s="15" t="n">
         <f aca="false">IF($L22,IF(G$37&gt;G$36,(G22-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -7851,47 +7869,47 @@
       </c>
       <c r="W22" s="15" t="n">
         <f aca="false">IF($L22,IF(K$37&gt;K$36,(K22-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.05914550532367</v>
+        <v>0.0688481461627146</v>
       </c>
       <c r="Y22" s="15" t="n">
         <f aca="false">IF($L22,N22/N$38*LN(N22/N$38),0)</f>
-        <v>-0.0415891534157879</v>
+        <v>-0.0378157039911593</v>
       </c>
       <c r="Z22" s="15" t="n">
         <f aca="false">IF($L22,O22/O$38*LN(O22/O$38),0)</f>
-        <v>-0.0803864677475006</v>
+        <v>-0.0721852283954921</v>
       </c>
       <c r="AA22" s="15" t="n">
         <f aca="false">IF($L22,P22/P$38*LN(P22/P$38),0)</f>
-        <v>-0.000748140317335659</v>
+        <v>-0.000700291074168319</v>
       </c>
       <c r="AB22" s="15" t="n">
         <f aca="false">IF($L22,Q22/Q$38*LN(Q22/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC22" s="15" t="n">
         <f aca="false">IF($L22,R22/R$38*LN(R22/R$38),0)</f>
-        <v>-0.10749258296143</v>
+        <v>-0.109031087815581</v>
       </c>
       <c r="AD22" s="15" t="n">
         <f aca="false">IF($L22,S22/S$38*LN(S22/S$38),0)</f>
-        <v>-0.0789669520913482</v>
+        <v>-0.0729996165482489</v>
       </c>
       <c r="AE22" s="15" t="n">
         <f aca="false">IF($L22,T22/T$38*LN(T22/T$38),0)</f>
-        <v>-0.103125139208667</v>
+        <v>-0.0957649281655761</v>
       </c>
       <c r="AF22" s="15" t="n">
         <f aca="false">IF($L22,U22/U$38*LN(U22/U$38),0)</f>
-        <v>-0.0829599126549707</v>
+        <v>-0.0744264061141054</v>
       </c>
       <c r="AG22" s="15" t="n">
         <f aca="false">IF($L22,V22/V$38*LN(V22/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH22" s="15" t="n">
         <f aca="false">IF($L22,W22/W$38*LN(W22/W$38),0)</f>
-        <v>-0.0264305541761504</v>
+        <v>-0.0284210540420518</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7961,7 +7979,7 @@
       </c>
       <c r="R23" s="15" t="n">
         <f aca="false">IF($L23,IF(F$37&gt;F$36,(F23-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.566642535402882</v>
+        <v>0.59736128819225</v>
       </c>
       <c r="S23" s="15" t="n">
         <f aca="false">IF($L23,IF(G$37&gt;G$36,(G23-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -7981,47 +7999,47 @@
       </c>
       <c r="W23" s="15" t="n">
         <f aca="false">IF($L23,IF(K$37&gt;K$36,(K23-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.802887923925915</v>
+        <v>0.804920666884476</v>
       </c>
       <c r="Y23" s="15" t="n">
         <f aca="false">IF($L23,N23/N$38*LN(N23/N$38),0)</f>
-        <v>-0.157101584723803</v>
+        <v>-0.145037945771691</v>
       </c>
       <c r="Z23" s="15" t="n">
         <f aca="false">IF($L23,O23/O$38*LN(O23/O$38),0)</f>
-        <v>-0.120951110964285</v>
+        <v>-0.109278137523616</v>
       </c>
       <c r="AA23" s="15" t="n">
         <f aca="false">IF($L23,P23/P$38*LN(P23/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB23" s="15" t="n">
         <f aca="false">IF($L23,Q23/Q$38*LN(Q23/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC23" s="15" t="n">
         <f aca="false">IF($L23,R23/R$38*LN(R23/R$38),0)</f>
-        <v>-0.126380511453156</v>
+        <v>-0.12548062435769</v>
       </c>
       <c r="AD23" s="15" t="n">
         <f aca="false">IF($L23,S23/S$38*LN(S23/S$38),0)</f>
-        <v>-0.102480570984853</v>
+        <v>-0.0949867673963865</v>
       </c>
       <c r="AE23" s="15" t="n">
         <f aca="false">IF($L23,T23/T$38*LN(T23/T$38),0)</f>
-        <v>-0.0774767718436377</v>
+        <v>-0.0717448554220742</v>
       </c>
       <c r="AF23" s="15" t="n">
         <f aca="false">IF($L23,U23/U$38*LN(U23/U$38),0)</f>
-        <v>-0.117936554105071</v>
+        <v>-0.106371192481718</v>
       </c>
       <c r="AG23" s="15" t="n">
         <f aca="false">IF($L23,V23/V$38*LN(V23/V$38),0)</f>
-        <v>-0.180001436686751</v>
+        <v>-0.168634353319555</v>
       </c>
       <c r="AH23" s="15" t="n">
         <f aca="false">IF($L23,W23/W$38*LN(W23/W$38),0)</f>
-        <v>-0.182261994801813</v>
+        <v>-0.175505247909142</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8091,7 +8109,7 @@
       </c>
       <c r="R24" s="15" t="n">
         <f aca="false">IF($L24,IF(F$37&gt;F$36,(F24-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.654574656114294</v>
+        <v>0.679060312520302</v>
       </c>
       <c r="S24" s="15" t="n">
         <f aca="false">IF($L24,IF(G$37&gt;G$36,(G24-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8111,47 +8129,47 @@
       </c>
       <c r="W24" s="15" t="n">
         <f aca="false">IF($L24,IF(K$37&gt;K$36,(K24-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.0926523415679968</v>
+        <v>0.102009440716983</v>
       </c>
       <c r="Y24" s="15" t="n">
         <f aca="false">IF($L24,N24/N$38*LN(N24/N$38),0)</f>
-        <v>-0.0960031677968267</v>
+        <v>-0.0879475485374226</v>
       </c>
       <c r="Z24" s="15" t="n">
         <f aca="false">IF($L24,O24/O$38*LN(O24/O$38),0)</f>
-        <v>-0.173093454418865</v>
+        <v>-0.157646178692506</v>
       </c>
       <c r="AA24" s="15" t="n">
         <f aca="false">IF($L24,P24/P$38*LN(P24/P$38),0)</f>
-        <v>-0.000338146538352914</v>
+        <v>-0.000316309251966338</v>
       </c>
       <c r="AB24" s="15" t="n">
         <f aca="false">IF($L24,Q24/Q$38*LN(Q24/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC24" s="15" t="n">
         <f aca="false">IF($L24,R24/R$38*LN(R24/R$38),0)</f>
-        <v>-0.139503901466956</v>
+        <v>-0.137026645880289</v>
       </c>
       <c r="AD24" s="15" t="n">
         <f aca="false">IF($L24,S24/S$38*LN(S24/S$38),0)</f>
-        <v>-0.207591954727656</v>
+        <v>-0.194787806684308</v>
       </c>
       <c r="AE24" s="15" t="n">
         <f aca="false">IF($L24,T24/T$38*LN(T24/T$38),0)</f>
-        <v>-0.230303723357244</v>
+        <v>-0.217098082011398</v>
       </c>
       <c r="AF24" s="15" t="n">
         <f aca="false">IF($L24,U24/U$38*LN(U24/U$38),0)</f>
-        <v>-0.177847602873819</v>
+        <v>-0.161912281909935</v>
       </c>
       <c r="AG24" s="15" t="n">
         <f aca="false">IF($L24,V24/V$38*LN(V24/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH24" s="15" t="n">
         <f aca="false">IF($L24,W24/W$38*LN(W24/W$38),0)</f>
-        <v>-0.037898168854952</v>
+        <v>-0.0389334374425572</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8221,7 +8239,7 @@
       </c>
       <c r="R25" s="15" t="n">
         <f aca="false">IF($L25,IF(F$37&gt;F$36,(F25-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.744096289534088</v>
+        <v>0.762236176442136</v>
       </c>
       <c r="S25" s="15" t="n">
         <f aca="false">IF($L25,IF(G$37&gt;G$36,(G25-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8241,47 +8259,47 @@
       </c>
       <c r="W25" s="15" t="n">
         <f aca="false">IF($L25,IF(K$37&gt;K$36,(K25-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.871630978945181</v>
+        <v>0.872954804140276</v>
       </c>
       <c r="Y25" s="15" t="n">
         <f aca="false">IF($L25,N25/N$38*LN(N25/N$38),0)</f>
-        <v>-0.241313663619512</v>
+        <v>-0.225579668411962</v>
       </c>
       <c r="Z25" s="15" t="n">
         <f aca="false">IF($L25,O25/O$38*LN(O25/O$38),0)</f>
-        <v>-0.225423745342577</v>
+        <v>-0.207188940392964</v>
       </c>
       <c r="AA25" s="15" t="n">
         <f aca="false">IF($L25,P25/P$38*LN(P25/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB25" s="15" t="n">
         <f aca="false">IF($L25,Q25/Q$38*LN(Q25/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC25" s="15" t="n">
         <f aca="false">IF($L25,R25/R$38*LN(R25/R$38),0)</f>
-        <v>-0.152028812801389</v>
+        <v>-0.148128845032478</v>
       </c>
       <c r="AD25" s="15" t="n">
         <f aca="false">IF($L25,S25/S$38*LN(S25/S$38),0)</f>
-        <v>-0.22984037796944</v>
+        <v>-0.216329565723992</v>
       </c>
       <c r="AE25" s="15" t="n">
         <f aca="false">IF($L25,T25/T$38*LN(T25/T$38),0)</f>
-        <v>-0.204614904220771</v>
+        <v>-0.192216065874097</v>
       </c>
       <c r="AF25" s="15" t="n">
         <f aca="false">IF($L25,U25/U$38*LN(U25/U$38),0)</f>
-        <v>-0.224163011123138</v>
+        <v>-0.20576060294861</v>
       </c>
       <c r="AG25" s="15" t="n">
         <f aca="false">IF($L25,V25/V$38*LN(V25/V$38),0)</f>
-        <v>-0.252068966138447</v>
+        <v>-0.238456870144653</v>
       </c>
       <c r="AH25" s="15" t="n">
         <f aca="false">IF($L25,W25/W$38*LN(W25/W$38),0)</f>
-        <v>-0.191831081304318</v>
+        <v>-0.184728792405486</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8351,7 +8369,7 @@
       </c>
       <c r="R26" s="15" t="n">
         <f aca="false">IF($L26,IF(F$37&gt;F$36,(F26-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.28965315212178</v>
+        <v>0.340006385567253</v>
       </c>
       <c r="S26" s="15" t="n">
         <f aca="false">IF($L26,IF(G$37&gt;G$36,(G26-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8371,47 +8389,47 @@
       </c>
       <c r="W26" s="15" t="n">
         <f aca="false">IF($L26,IF(K$37&gt;K$36,(K26-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.03013421855855</v>
+        <v>0.0401360404061056</v>
       </c>
       <c r="Y26" s="15" t="n">
         <f aca="false">IF($L26,N26/N$38*LN(N26/N$38),0)</f>
-        <v>-0.0812115485805352</v>
+        <v>-0.0742563177631561</v>
       </c>
       <c r="Z26" s="15" t="n">
         <f aca="false">IF($L26,O26/O$38*LN(O26/O$38),0)</f>
-        <v>-0.149104449869521</v>
+        <v>-0.135288233289337</v>
       </c>
       <c r="AA26" s="15" t="n">
         <f aca="false">IF($L26,P26/P$38*LN(P26/P$38),0)</f>
-        <v>-0.00123095841421431</v>
+        <v>-0.0011527921327292</v>
       </c>
       <c r="AB26" s="15" t="n">
         <f aca="false">IF($L26,Q26/Q$38*LN(Q26/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC26" s="15" t="n">
         <f aca="false">IF($L26,R26/R$38*LN(R26/R$38),0)</f>
-        <v>-0.0779584345852306</v>
+        <v>-0.0837823259722813</v>
       </c>
       <c r="AD26" s="15" t="n">
         <f aca="false">IF($L26,S26/S$38*LN(S26/S$38),0)</f>
-        <v>-0.138517954144884</v>
+        <v>-0.128901701846125</v>
       </c>
       <c r="AE26" s="15" t="n">
         <f aca="false">IF($L26,T26/T$38*LN(T26/T$38),0)</f>
-        <v>-0.160615136516689</v>
+        <v>-0.150090651492677</v>
       </c>
       <c r="AF26" s="15" t="n">
         <f aca="false">IF($L26,U26/U$38*LN(U26/U$38),0)</f>
-        <v>-0.153381119683532</v>
+        <v>-0.139092089914752</v>
       </c>
       <c r="AG26" s="15" t="n">
         <f aca="false">IF($L26,V26/V$38*LN(V26/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH26" s="15" t="n">
         <f aca="false">IF($L26,W26/W$38*LN(W26/W$38),0)</f>
-        <v>-0.0151791599387182</v>
+        <v>-0.0182840694338036</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8481,7 +8499,7 @@
       </c>
       <c r="R27" s="15" t="n">
         <f aca="false">IF($L27,IF(F$37&gt;F$36,(F27-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.411130845509107</v>
+        <v>0.45287309396769</v>
       </c>
       <c r="S27" s="15" t="n">
         <f aca="false">IF($L27,IF(G$37&gt;G$36,(G27-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8501,47 +8519,47 @@
       </c>
       <c r="W27" s="15" t="n">
         <f aca="false">IF($L27,IF(K$37&gt;K$36,(K27-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.727764056455896</v>
+        <v>0.730571519771223</v>
       </c>
       <c r="Y27" s="15" t="n">
         <f aca="false">IF($L27,N27/N$38*LN(N27/N$38),0)</f>
-        <v>-0.206321529720728</v>
+        <v>-0.19178474122662</v>
       </c>
       <c r="Z27" s="15" t="n">
         <f aca="false">IF($L27,O27/O$38*LN(O27/O$38),0)</f>
-        <v>-0.183061470689136</v>
+        <v>-0.1669954657952</v>
       </c>
       <c r="AA27" s="15" t="n">
         <f aca="false">IF($L27,P27/P$38*LN(P27/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB27" s="15" t="n">
         <f aca="false">IF($L27,Q27/Q$38*LN(Q27/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC27" s="15" t="n">
         <f aca="false">IF($L27,R27/R$38*LN(R27/R$38),0)</f>
-        <v>-0.10075935723099</v>
+        <v>-0.10321973827193</v>
       </c>
       <c r="AD27" s="15" t="n">
         <f aca="false">IF($L27,S27/S$38*LN(S27/S$38),0)</f>
-        <v>-0.162362678844133</v>
+        <v>-0.151501290177294</v>
       </c>
       <c r="AE27" s="15" t="n">
         <f aca="false">IF($L27,T27/T$38*LN(T27/T$38),0)</f>
-        <v>-0.136133585435043</v>
+        <v>-0.126868867168146</v>
       </c>
       <c r="AF27" s="15" t="n">
         <f aca="false">IF($L27,U27/U$38*LN(U27/U$38),0)</f>
-        <v>-0.181187278314701</v>
+        <v>-0.165043830279324</v>
       </c>
       <c r="AG27" s="15" t="n">
         <f aca="false">IF($L27,V27/V$38*LN(V27/V$38),0)</f>
-        <v>-0.221717559796532</v>
+        <v>-0.208811759142595</v>
       </c>
       <c r="AH27" s="15" t="n">
         <f aca="false">IF($L27,W27/W$38*LN(W27/W$38),0)</f>
-        <v>-0.171235046367665</v>
+        <v>-0.164902628869542</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8611,7 +8629,7 @@
       </c>
       <c r="R28" s="15" t="n">
         <f aca="false">IF($L28,IF(F$37&gt;F$36,(F28-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>1E-006</v>
+        <v>0.0708863185039925</v>
       </c>
       <c r="S28" s="15" t="n">
         <f aca="false">IF($L28,IF(G$37&gt;G$36,(G28-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8631,47 +8649,47 @@
       </c>
       <c r="W28" s="15" t="n">
         <f aca="false">IF($L28,IF(K$37&gt;K$36,(K28-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>1E-006</v>
+        <v>0.0103135728594298</v>
       </c>
       <c r="Y28" s="15" t="n">
         <f aca="false">IF($L28,N28/N$38*LN(N28/N$38),0)</f>
-        <v>-0.0691592871981136</v>
+        <v>-0.063135707384182</v>
       </c>
       <c r="Z28" s="15" t="n">
         <f aca="false">IF($L28,O28/O$38*LN(O28/O$38),0)</f>
-        <v>-0.128890762152608</v>
+        <v>-0.116590022076656</v>
       </c>
       <c r="AA28" s="15" t="n">
         <f aca="false">IF($L28,P28/P$38*LN(P28/P$38),0)</f>
-        <v>-0.00182936571991556</v>
+        <v>-0.00171395061312096</v>
       </c>
       <c r="AB28" s="15" t="n">
         <f aca="false">IF($L28,Q28/Q$38*LN(Q28/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC28" s="15" t="n">
         <f aca="false">IF($L28,R28/R$38*LN(R28/R$38),0)</f>
-        <v>-1.13332177722042E-006</v>
+        <v>-0.0246372693326108</v>
       </c>
       <c r="AD28" s="15" t="n">
         <f aca="false">IF($L28,S28/S$38*LN(S28/S$38),0)</f>
-        <v>-0.0902076009996619</v>
+        <v>-0.0834971257047719</v>
       </c>
       <c r="AE28" s="15" t="n">
         <f aca="false">IF($L28,T28/T$38*LN(T28/T$38),0)</f>
-        <v>-0.113619053727737</v>
+        <v>-0.105629280875255</v>
       </c>
       <c r="AF28" s="15" t="n">
         <f aca="false">IF($L28,U28/U$38*LN(U28/U$38),0)</f>
-        <v>-0.132714884762519</v>
+        <v>-0.119968672693054</v>
       </c>
       <c r="AG28" s="15" t="n">
         <f aca="false">IF($L28,V28/V$38*LN(V28/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH28" s="15" t="n">
         <f aca="false">IF($L28,W28/W$38*LN(W28/W$38),0)</f>
-        <v>-1.37311140322936E-006</v>
+        <v>-0.00580845483350431</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8741,7 +8759,7 @@
       </c>
       <c r="R29" s="15" t="n">
         <f aca="false">IF($L29,IF(F$37&gt;F$36,(F29-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.148162262523336</v>
+        <v>0.208545122743408</v>
       </c>
       <c r="S29" s="15" t="n">
         <f aca="false">IF($L29,IF(G$37&gt;G$36,(G29-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8761,47 +8779,47 @@
       </c>
       <c r="W29" s="15" t="n">
         <f aca="false">IF($L29,IF(K$37&gt;K$36,(K29-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.645401076581761</v>
+        <v>0.64905791412796</v>
       </c>
       <c r="Y29" s="15" t="n">
         <f aca="false">IF($L29,N29/N$38*LN(N29/N$38),0)</f>
-        <v>-0.182027599853022</v>
+        <v>-0.168613041500426</v>
       </c>
       <c r="Z29" s="15" t="n">
         <f aca="false">IF($L29,O29/O$38*LN(O29/O$38),0)</f>
-        <v>-0.152861131746382</v>
+        <v>-0.138776995839543</v>
       </c>
       <c r="AA29" s="15" t="n">
         <f aca="false">IF($L29,P29/P$38*LN(P29/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB29" s="15" t="n">
         <f aca="false">IF($L29,Q29/Q$38*LN(Q29/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC29" s="15" t="n">
         <f aca="false">IF($L29,R29/R$38*LN(R29/R$38),0)</f>
-        <v>-0.0467019793100824</v>
+        <v>-0.0579646255149078</v>
       </c>
       <c r="AD29" s="15" t="n">
         <f aca="false">IF($L29,S29/S$38*LN(S29/S$38),0)</f>
-        <v>-0.115107351130745</v>
+        <v>-0.106838966249081</v>
       </c>
       <c r="AE29" s="15" t="n">
         <f aca="false">IF($L29,T29/T$38*LN(T29/T$38),0)</f>
-        <v>-0.0884008882821394</v>
+        <v>-0.0819601632813974</v>
       </c>
       <c r="AF29" s="15" t="n">
         <f aca="false">IF($L29,U29/U$38*LN(U29/U$38),0)</f>
-        <v>-0.150477571694026</v>
+        <v>-0.13639728611465</v>
       </c>
       <c r="AG29" s="15" t="n">
         <f aca="false">IF($L29,V29/V$38*LN(V29/V$38),0)</f>
-        <v>-0.200969157176953</v>
+        <v>-0.188758341609597</v>
       </c>
       <c r="AH29" s="15" t="n">
         <f aca="false">IF($L29,W29/W$38*LN(W29/W$38),0)</f>
-        <v>-0.158390300871128</v>
+        <v>-0.15258597255427</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8871,7 +8889,7 @@
       </c>
       <c r="R30" s="15" t="n">
         <f aca="false">IF($L30,IF(F$37&gt;F$36,(F30-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.38552117041083</v>
+        <v>0.429078768845537</v>
       </c>
       <c r="S30" s="15" t="n">
         <f aca="false">IF($L30,IF(G$37&gt;G$36,(G30-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -8891,47 +8909,47 @@
       </c>
       <c r="W30" s="15" t="n">
         <f aca="false">IF($L30,IF(K$37&gt;K$36,(K30-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.0402823443696825</v>
+        <v>0.0501795129304242</v>
       </c>
       <c r="Y30" s="15" t="n">
         <f aca="false">IF($L30,N30/N$38*LN(N30/N$38),0)</f>
-        <v>-0.120146287649744</v>
+        <v>-0.110399315948798</v>
       </c>
       <c r="Z30" s="15" t="n">
         <f aca="false">IF($L30,O30/O$38*LN(O30/O$38),0)</f>
-        <v>-0.21025484740918</v>
+        <v>-0.192702478240757</v>
       </c>
       <c r="AA30" s="15" t="n">
         <f aca="false">IF($L30,P30/P$38*LN(P30/P$38),0)</f>
-        <v>-0.00107343975360688</v>
+        <v>-0.00100513456879798</v>
       </c>
       <c r="AB30" s="15" t="n">
         <f aca="false">IF($L30,Q30/Q$38*LN(Q30/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC30" s="15" t="n">
         <f aca="false">IF($L30,R30/R$38*LN(R30/R$38),0)</f>
-        <v>-0.0961867357357948</v>
+        <v>-0.0992904388602162</v>
       </c>
       <c r="AD30" s="15" t="n">
         <f aca="false">IF($L30,S30/S$38*LN(S30/S$38),0)</f>
-        <v>-0.214548893669526</v>
+        <v>-0.20150358079595</v>
       </c>
       <c r="AE30" s="15" t="n">
         <f aca="false">IF($L30,T30/T$38*LN(T30/T$38),0)</f>
-        <v>-0.235182542062742</v>
+        <v>-0.221853020698887</v>
       </c>
       <c r="AF30" s="15" t="n">
         <f aca="false">IF($L30,U30/U$38*LN(U30/U$38),0)</f>
-        <v>-0.215598640996701</v>
+        <v>-0.197577970312385</v>
       </c>
       <c r="AG30" s="15" t="n">
         <f aca="false">IF($L30,V30/V$38*LN(V30/V$38),0)</f>
-        <v>-2.11132670698034E-006</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH30" s="15" t="n">
         <f aca="false">IF($L30,W30/W$38*LN(W30/W$38),0)</f>
-        <v>-0.0193053513243625</v>
+        <v>-0.0219717027747913</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9001,7 +9019,7 @@
       </c>
       <c r="R31" s="15" t="n">
         <f aca="false">IF($L31,IF(F$37&gt;F$36,(F31-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0.493889545582799</v>
+        <v>0.529765417227681</v>
       </c>
       <c r="S31" s="15" t="n">
         <f aca="false">IF($L31,IF(G$37&gt;G$36,(G31-G$36)/(G$37-G$36),0)+0.000001,0)</f>
@@ -9021,47 +9039,47 @@
       </c>
       <c r="W31" s="15" t="n">
         <f aca="false">IF($L31,IF(K$37&gt;K$36,(K31-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0.75143828750257</v>
+        <v>0.754001608585338</v>
       </c>
       <c r="Y31" s="15" t="n">
         <f aca="false">IF($L31,N31/N$38*LN(N31/N$38),0)</f>
-        <v>-0.260240138413684</v>
+        <v>-0.244122741683137</v>
       </c>
       <c r="Z31" s="15" t="n">
         <f aca="false">IF($L31,O31/O$38*LN(O31/O$38),0)</f>
-        <v>-0.247882651316478</v>
+        <v>-0.228871660602992</v>
       </c>
       <c r="AA31" s="15" t="n">
         <f aca="false">IF($L31,P31/P$38*LN(P31/P$38),0)</f>
-        <v>-0.19653551219816</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB31" s="15" t="n">
         <f aca="false">IF($L31,Q31/Q$38*LN(Q31/Q$38),0)</f>
-        <v>-1.86009737402904E-006</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC31" s="15" t="n">
         <f aca="false">IF($L31,R31/R$38*LN(R31/R$38),0)</f>
-        <v>-0.114817657223762</v>
+        <v>-0.115385657605004</v>
       </c>
       <c r="AD31" s="15" t="n">
         <f aca="false">IF($L31,S31/S$38*LN(S31/S$38),0)</f>
-        <v>-0.237672467009974</v>
+        <v>-0.223961007790005</v>
       </c>
       <c r="AE31" s="15" t="n">
         <f aca="false">IF($L31,T31/T$38*LN(T31/T$38),0)</f>
-        <v>-0.211425206934694</v>
+        <v>-0.198788976001303</v>
       </c>
       <c r="AF31" s="15" t="n">
         <f aca="false">IF($L31,U31/U$38*LN(U31/U$38),0)</f>
-        <v>-0.246909108738231</v>
+        <v>-0.227694087276758</v>
       </c>
       <c r="AG31" s="15" t="n">
         <f aca="false">IF($L31,V31/V$38*LN(V31/V$38),0)</f>
-        <v>-0.26869526100873</v>
+        <v>-0.254894999150571</v>
       </c>
       <c r="AH31" s="15" t="n">
         <f aca="false">IF($L31,W31/W$38*LN(W31/W$38),0)</f>
-        <v>-0.174777551269777</v>
+        <v>-0.168305835152753</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9111,87 +9129,87 @@
       </c>
       <c r="L32" s="26" t="b">
         <f aca="false">Показатели!B17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="15" t="n">
         <f aca="false">IF($L32,IF(B$37&gt;B$36,(B32-B$36)/(B$37-B$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.238651850528896</v>
       </c>
       <c r="O32" s="15" t="n">
         <f aca="false">IF($L32,IF(C$37&gt;C$36,(C32-C$36)/(C$37-C$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.617850620966365</v>
       </c>
       <c r="P32" s="15" t="n">
         <f aca="false">IF($L32,IF(D$37&gt;D$36,(D32-D$36)/(D$37-D$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.00331853678253479</v>
       </c>
       <c r="Q32" s="15" t="n">
         <f aca="false">IF($L32,IF(E$37&gt;E$36,(E32-E$36)/(E$37-E$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1E-006</v>
       </c>
       <c r="R32" s="15" t="n">
         <f aca="false">IF($L32,IF(F$37&gt;F$36,(F32-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1E-006</v>
       </c>
       <c r="S32" s="15" t="n">
         <f aca="false">IF($L32,IF(G$37&gt;G$36,(G32-G$36)/(G$37-G$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.461665023964451</v>
       </c>
       <c r="T32" s="15" t="n">
         <f aca="false">IF($L32,IF(H$37&gt;H$36,(H32-H$36)/(H$37-H$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.583374792282352</v>
       </c>
       <c r="U32" s="15" t="n">
         <f aca="false">IF($L32,IF(I$37&gt;I$36,(I32-I$36)/(I$37-I$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.649426236700996</v>
       </c>
       <c r="V32" s="15" t="n">
         <f aca="false">IF($L32,IF(J$37&gt;J$36,(J32-J$36)/(J$37-J$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1E-006</v>
       </c>
       <c r="W32" s="15" t="n">
         <f aca="false">IF($L32,IF(K$37&gt;K$36,(K32-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1E-006</v>
       </c>
       <c r="Y32" s="15" t="n">
         <f aca="false">IF($L32,N32/N$38*LN(N32/N$38),0)</f>
-        <v>0</v>
+        <v>-0.0962485045858442</v>
       </c>
       <c r="Z32" s="15" t="n">
         <f aca="false">IF($L32,O32/O$38*LN(O32/O$38),0)</f>
-        <v>0</v>
+        <v>-0.170842967479588</v>
       </c>
       <c r="AA32" s="15" t="n">
         <f aca="false">IF($L32,P32/P$38*LN(P32/P$38),0)</f>
-        <v>0</v>
+        <v>-0.00196790858908701</v>
       </c>
       <c r="AB32" s="15" t="n">
         <f aca="false">IF($L32,Q32/Q$38*LN(Q32/Q$38),0)</f>
-        <v>0</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC32" s="15" t="n">
         <f aca="false">IF($L32,R32/R$38*LN(R32/R$38),0)</f>
-        <v>0</v>
+        <v>-1.06807539089615E-006</v>
       </c>
       <c r="AD32" s="15" t="n">
         <f aca="false">IF($L32,S32/S$38*LN(S32/S$38),0)</f>
-        <v>0</v>
+        <v>-0.137383918993705</v>
       </c>
       <c r="AE32" s="15" t="n">
         <f aca="false">IF($L32,T32/T$38*LN(T32/T$38),0)</f>
-        <v>0</v>
+        <v>-0.158883031448698</v>
       </c>
       <c r="AF32" s="15" t="n">
         <f aca="false">IF($L32,U32/U$38*LN(U32/U$38),0)</f>
-        <v>0</v>
+        <v>-0.175356160909203</v>
       </c>
       <c r="AG32" s="15" t="n">
         <f aca="false">IF($L32,V32/V$38*LN(V32/V$38),0)</f>
-        <v>0</v>
+        <v>-1.91847778857353E-006</v>
       </c>
       <c r="AH32" s="15" t="n">
         <f aca="false">IF($L32,W32/W$38*LN(W32/W$38),0)</f>
-        <v>0</v>
+        <v>-1.29519221249204E-006</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9241,101 +9259,101 @@
       </c>
       <c r="L33" s="26" t="b">
         <f aca="false">Показатели!B17</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="15" t="n">
         <f aca="false">IF($L33,IF(B$37&gt;B$36,(B33-B$36)/(B$37-B$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.780604601693902</v>
       </c>
       <c r="O33" s="15" t="n">
         <f aca="false">IF($L33,IF(C$37&gt;C$36,(C33-C$36)/(C$37-C$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.738720424767097</v>
       </c>
       <c r="P33" s="15" t="n">
         <f aca="false">IF($L33,IF(D$37&gt;D$36,(D33-D$36)/(D$37-D$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1.000001</v>
       </c>
       <c r="Q33" s="15" t="n">
         <f aca="false">IF($L33,IF(E$37&gt;E$36,(E33-E$36)/(E$37-E$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>1E-006</v>
       </c>
       <c r="R33" s="15" t="n">
         <f aca="false">IF($L33,IF(F$37&gt;F$36,(F33-F$36)/(F$37-F$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.13668451077109</v>
       </c>
       <c r="S33" s="15" t="n">
         <f aca="false">IF($L33,IF(G$37&gt;G$36,(G33-G$36)/(G$37-G$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.586587851345229</v>
       </c>
       <c r="T33" s="15" t="n">
         <f aca="false">IF($L33,IF(H$37&gt;H$36,(H33-H$36)/(H$37-H$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.458115429621646</v>
       </c>
       <c r="U33" s="15" t="n">
         <f aca="false">IF($L33,IF(I$37&gt;I$36,(I33-I$36)/(I$37-I$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.735232758721987</v>
       </c>
       <c r="V33" s="15" t="n">
         <f aca="false">IF($L33,IF(J$37&gt;J$36,(J33-J$36)/(J$37-J$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.806964640877978</v>
       </c>
       <c r="W33" s="15" t="n">
         <f aca="false">IF($L33,IF(K$37&gt;K$36,(K33-K$36)/(K$37-K$36),0)+0.000001,0)</f>
-        <v>0</v>
+        <v>0.615925864680842</v>
       </c>
       <c r="Y33" s="15" t="n">
         <f aca="false">IF($L33,N33/N$38*LN(N33/N$38),0)</f>
-        <v>0</v>
+        <v>-0.212043863741188</v>
       </c>
       <c r="Z33" s="15" t="n">
         <f aca="false">IF($L33,O33/O$38*LN(O33/O$38),0)</f>
-        <v>0</v>
+        <v>-0.19120593349076</v>
       </c>
       <c r="AA33" s="15" t="n">
         <f aca="false">IF($L33,P33/P$38*LN(P33/P$38),0)</f>
-        <v>0</v>
+        <v>-0.187782600686778</v>
       </c>
       <c r="AB33" s="15" t="n">
         <f aca="false">IF($L33,Q33/Q$38*LN(Q33/Q$38),0)</f>
-        <v>0</v>
+        <v>-1.8600969677424E-006</v>
       </c>
       <c r="AC33" s="15" t="n">
         <f aca="false">IF($L33,R33/R$38*LN(R33/R$38),0)</f>
-        <v>0</v>
+        <v>-0.0417164335339342</v>
       </c>
       <c r="AD33" s="15" t="n">
         <f aca="false">IF($L33,S33/S$38*LN(S33/S$38),0)</f>
-        <v>0</v>
+        <v>-0.161177946732336</v>
       </c>
       <c r="AE33" s="15" t="n">
         <f aca="false">IF($L33,T33/T$38*LN(T33/T$38),0)</f>
-        <v>0</v>
+        <v>-0.135144171475691</v>
       </c>
       <c r="AF33" s="15" t="n">
         <f aca="false">IF($L33,U33/U$38*LN(U33/U$38),0)</f>
-        <v>0</v>
+        <v>-0.189579594058475</v>
       </c>
       <c r="AG33" s="15" t="n">
         <f aca="false">IF($L33,V33/V$38*LN(V33/V$38),0)</f>
-        <v>0</v>
+        <v>-0.226531711431799</v>
       </c>
       <c r="AH33" s="15" t="n">
         <f aca="false">IF($L33,W33/W$38*LN(W33/W$38),0)</f>
-        <v>0</v>
+        <v>-0.147353284708008</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B35" s="6" t="n">
         <f aca="false">COUNTIF(L2:L33,TRUE())</f>
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B36" s="11" t="n">
         <f aca="false">_xlfn.MINIFS(B2:B33,$L$2:$L$33,TRUE())</f>
@@ -9355,7 +9373,7 @@
       </c>
       <c r="F36" s="11" t="n">
         <f aca="false">_xlfn.MINIFS(F2:F33,$L$2:$L$33,TRUE())</f>
-        <v>2.66384952782565</v>
+        <v>-1.61322054741009</v>
       </c>
       <c r="G36" s="11" t="n">
         <f aca="false">_xlfn.MINIFS(G2:G33,$L$2:$L$33,TRUE())</f>
@@ -9375,12 +9393,12 @@
       </c>
       <c r="K36" s="11" t="n">
         <f aca="false">_xlfn.MINIFS(K2:K33,$L$2:$L$33,TRUE())</f>
-        <v>0.150457897905598</v>
+        <v>0.141605643562715</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B37" s="11" t="n">
         <f aca="false">_xlfn.MAXIFS(B2:B33,$L$2:$L$33,TRUE())</f>
@@ -9425,177 +9443,217 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B38" s="15" t="n">
         <f aca="false">SUM(N2:N33)</f>
-        <v>7.98165395235434</v>
+        <v>9.00091040457714</v>
       </c>
       <c r="C38" s="15" t="n">
         <f aca="false">SUM(O2:O33)</f>
-        <v>8.75061130168779</v>
+        <v>10.1071823474212</v>
       </c>
       <c r="D38" s="15" t="n">
         <f aca="false">SUM(P2:P33)</f>
-        <v>13.0833425669005</v>
+        <v>14.086662103683</v>
       </c>
       <c r="E38" s="15" t="n">
         <f aca="false">SUM(Q2:Q33)</f>
-        <v>8.58304490705125</v>
+        <v>8.58304690705125</v>
       </c>
       <c r="F38" s="15" t="n">
         <f aca="false">SUM(R2:R33)</f>
-        <v>14.5530712863663</v>
+        <v>15.5011778279141</v>
       </c>
       <c r="G38" s="15" t="n">
         <f aca="false">SUM(S2:S33)</f>
-        <v>9.45008474815539</v>
+        <v>10.4983376234651</v>
       </c>
       <c r="H38" s="15" t="n">
         <f aca="false">SUM(T2:T33)</f>
-        <v>9.63058328484819</v>
+        <v>10.6720735067522</v>
       </c>
       <c r="I38" s="15" t="n">
         <f aca="false">SUM(U2:U33)</f>
-        <v>8.81464184100326</v>
+        <v>10.1993008364262</v>
       </c>
       <c r="J38" s="15" t="n">
         <f aca="false">SUM(V2:V33)</f>
-        <v>7.4977063772418</v>
+        <v>8.30467201811978</v>
       </c>
       <c r="K38" s="15" t="n">
         <f aca="false">SUM(W2:W33)</f>
-        <v>11.8627783189306</v>
+        <v>12.6244965803543</v>
       </c>
       <c r="N38" s="27" t="n">
         <f aca="false">SUM(N2:N33)</f>
-        <v>7.98165395235434</v>
+        <v>9.00091040457714</v>
       </c>
       <c r="O38" s="27" t="n">
         <f aca="false">SUM(O2:O33)</f>
-        <v>8.75061130168779</v>
+        <v>10.1071823474212</v>
       </c>
       <c r="P38" s="27" t="n">
         <f aca="false">SUM(P2:P33)</f>
-        <v>13.0833425669005</v>
+        <v>14.086662103683</v>
       </c>
       <c r="Q38" s="27" t="n">
         <f aca="false">SUM(Q2:Q33)</f>
-        <v>8.58304490705125</v>
+        <v>8.58304690705125</v>
       </c>
       <c r="R38" s="27" t="n">
         <f aca="false">SUM(R2:R33)</f>
-        <v>14.5530712863663</v>
+        <v>15.5011778279141</v>
       </c>
       <c r="S38" s="27" t="n">
         <f aca="false">SUM(S2:S33)</f>
-        <v>9.45008474815539</v>
+        <v>10.4983376234651</v>
       </c>
       <c r="T38" s="27" t="n">
         <f aca="false">SUM(T2:T33)</f>
-        <v>9.63058328484819</v>
+        <v>10.6720735067522</v>
       </c>
       <c r="U38" s="27" t="n">
         <f aca="false">SUM(U2:U33)</f>
-        <v>8.81464184100326</v>
+        <v>10.1993008364262</v>
       </c>
       <c r="V38" s="27" t="n">
         <f aca="false">SUM(V2:V33)</f>
-        <v>7.4977063772418</v>
+        <v>8.30467201811978</v>
       </c>
       <c r="W38" s="27" t="n">
         <f aca="false">SUM(W2:W33)</f>
-        <v>11.8627783189306</v>
+        <v>12.6244965803543</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B39" s="15" t="n">
         <f aca="false">-SUM(Y2:Y33)/LN($B$35)</f>
-        <v>0.877730836271301</v>
+        <v>0.885528247921904</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">-SUM(Z2:Z33)/LN($B$35)</f>
-        <v>0.907897014999739</v>
+        <v>0.914656727688447</v>
       </c>
       <c r="D39" s="15" t="n">
         <f aca="false">-SUM(AA2:AA33)/LN($B$35)</f>
-        <v>0.796652284905945</v>
+        <v>0.800994496566408</v>
       </c>
       <c r="E39" s="15" t="n">
         <f aca="false">-SUM(AB2:AB33)/LN($B$35)</f>
-        <v>0.754181444169665</v>
+        <v>0.737409521362722</v>
       </c>
       <c r="F39" s="15" t="n">
         <f aca="false">-SUM(AC2:AC33)/LN($B$35)</f>
-        <v>0.955667321658371</v>
+        <v>0.953366172677368</v>
       </c>
       <c r="G39" s="15" t="n">
         <f aca="false">-SUM(AD2:AD33)/LN($B$35)</f>
-        <v>0.894087944922895</v>
+        <v>0.904930234570162</v>
       </c>
       <c r="H39" s="15" t="n">
         <f aca="false">-SUM(AE2:AE33)/LN($B$35)</f>
-        <v>0.896819071610945</v>
+        <v>0.907346623364332</v>
       </c>
       <c r="I39" s="15" t="n">
         <f aca="false">-SUM(AF2:AF33)/LN($B$35)</f>
-        <v>0.907025990155231</v>
+        <v>0.913814062565955</v>
       </c>
       <c r="J39" s="15" t="n">
         <f aca="false">-SUM(AG2:AG33)/LN($B$35)</f>
-        <v>0.770262148138611</v>
+        <v>0.775628690570356</v>
       </c>
       <c r="K39" s="15" t="n">
         <f aca="false">-SUM(AH2:AH33)/LN($B$35)</f>
-        <v>0.869517615649953</v>
+        <v>0.874482533735455</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B40" s="22" t="n">
         <f aca="false">(1-B39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0892372518366141</v>
+        <v>0.085949904613759</v>
       </c>
       <c r="C40" s="22" t="n">
         <f aca="false">(1-C39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0672206876756696</v>
+        <v>0.0640790935880819</v>
       </c>
       <c r="D40" s="22" t="n">
         <f aca="false">(1-D39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.148411837530127</v>
+        <v>0.149421177951929</v>
       </c>
       <c r="E40" s="22" t="n">
         <f aca="false">(1-E39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.179408868955857</v>
+        <v>0.197163284230661</v>
       </c>
       <c r="F40" s="22" t="n">
         <f aca="false">(1-F39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0323558799383114</v>
+        <v>0.0350145161351267</v>
       </c>
       <c r="G40" s="22" t="n">
         <f aca="false">(1-G39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0772991361290431</v>
+        <v>0.0713821280971779</v>
       </c>
       <c r="H40" s="22" t="n">
         <f aca="false">(1-H39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0753058433590029</v>
+        <v>0.0695678081221763</v>
       </c>
       <c r="I40" s="22" t="n">
         <f aca="false">(1-I39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0678563987661437</v>
+        <v>0.0647117997848923</v>
       </c>
       <c r="J40" s="22" t="n">
         <f aca="false">(1-J39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.167672485177433</v>
+        <v>0.168466825163867</v>
       </c>
       <c r="K40" s="22" t="n">
         <f aca="false">(1-K39)/(10-SUM($B$39:$K$39))</f>
-        <v>0.0952316106317977</v>
+        <v>0.0942434623123292</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>0.08595</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>0.064079</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>0.149421</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>0.197163</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>0.035015</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>0.071382</v>
+      </c>
+      <c r="H41" s="16" t="n">
+        <v>0.069568</v>
+      </c>
+      <c r="I41" s="16" t="n">
+        <v>0.064712</v>
+      </c>
+      <c r="J41" s="16" t="n">
+        <v>0.168467</v>
+      </c>
+      <c r="K41" s="16" t="n">
+        <v>0.094244</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -9627,42 +9685,42 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C2" s="10" t="n">
         <v>0.08</v>
@@ -9671,27 +9729,27 @@
         <v>3.6</v>
       </c>
       <c r="E2" s="29" t="n">
-        <v>0.023</v>
+        <v>-0.0593</v>
       </c>
       <c r="F2" s="29" t="n">
-        <v>-0.1145</v>
+        <v>-0.1776</v>
       </c>
       <c r="G2" s="29" t="n">
-        <v>0.1527</v>
+        <v>0.0619</v>
       </c>
       <c r="H2" s="29" t="n">
-        <v>0.606</v>
+        <v>0.212</v>
       </c>
       <c r="I2" s="29" t="n">
-        <v>0.162</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>0.08</v>
@@ -9700,27 +9758,27 @@
         <v>4.5</v>
       </c>
       <c r="E3" s="29" t="n">
-        <v>-0.0096</v>
+        <v>-0.0946</v>
       </c>
       <c r="F3" s="29" t="n">
-        <v>-0.1425</v>
+        <v>-0.2167</v>
       </c>
       <c r="G3" s="29" t="n">
-        <v>0.1201</v>
+        <v>0.0297</v>
       </c>
       <c r="H3" s="29" t="n">
-        <v>0.457</v>
+        <v>0.113</v>
       </c>
       <c r="I3" s="29" t="n">
-        <v>0.102</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C4" s="10" t="n">
         <v>0.08</v>
@@ -9729,27 +9787,27 @@
         <v>5.4</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>-0.0334</v>
+        <v>-0.1196</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-0.1713</v>
+        <v>-0.2456</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>0.1006</v>
+        <v>0.0041</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>0.341</v>
+        <v>0.057</v>
       </c>
       <c r="I4" s="29" t="n">
-        <v>0.049</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>0.11</v>
@@ -9758,27 +9816,27 @@
         <v>3.6</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>-0.0079</v>
+        <v>-0.0934</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-0.1401</v>
+        <v>-0.2166</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>0.123</v>
+        <v>0.0328</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>0.458</v>
+        <v>0.12</v>
       </c>
       <c r="I5" s="29" t="n">
-        <v>0.1</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>0.11</v>
@@ -9787,27 +9845,27 @@
         <v>4.5</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.0332</v>
+        <v>-0.1196</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-0.1711</v>
+        <v>-0.2455</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>0.1015</v>
+        <v>0.004</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>0.337</v>
+        <v>0.061</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>0.05</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0.11</v>
@@ -9816,27 +9874,27 @@
         <v>5.4</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.0593</v>
+        <v>-0.1449</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-0.1981</v>
+        <v>-0.2726</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>0.0786</v>
+        <v>-0.0161</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>0.237</v>
+        <v>0.035</v>
       </c>
       <c r="I7" s="29" t="n">
-        <v>0.053</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0.14</v>
@@ -9845,27 +9903,27 @@
         <v>3.6</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>-0.0237</v>
+        <v>-0.1105</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-0.1622</v>
+        <v>-0.2367</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>0.1102</v>
+        <v>0.0146</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>0.387</v>
+        <v>0.075</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>0.058</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>0.14</v>
@@ -9874,27 +9932,27 @@
         <v>4.5</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.0498</v>
+        <v>-0.1357</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-0.1905</v>
+        <v>-0.2654</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>0.0893</v>
+        <v>-0.0069</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>0.278</v>
+        <v>0.044</v>
       </c>
       <c r="I9" s="29" t="n">
-        <v>0.062</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>0.08</v>
@@ -9903,27 +9961,27 @@
         <v>1.8</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>0.0061</v>
+        <v>-0.0745</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>-0.1282</v>
+        <v>-0.1911</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>0.1393</v>
+        <v>0.0476</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>0.531</v>
+        <v>0.161</v>
       </c>
       <c r="I10" s="29" t="n">
-        <v>0.169</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>0.08</v>
@@ -9932,27 +9990,27 @@
         <v>2.7</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>-0.0331</v>
+        <v>-0.117</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>-0.1666</v>
+        <v>-0.239</v>
       </c>
       <c r="G11" s="29" t="n">
-        <v>0.0982</v>
+        <v>0.0045</v>
       </c>
       <c r="H11" s="29" t="n">
-        <v>0.336</v>
+        <v>0.062</v>
       </c>
       <c r="I11" s="29" t="n">
-        <v>0.085</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>0.08</v>
@@ -9961,27 +10019,27 @@
         <v>3.6</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>-0.0523</v>
+        <v>-0.1368</v>
       </c>
       <c r="F12" s="29" t="n">
-        <v>-0.1886</v>
+        <v>-0.2596</v>
       </c>
       <c r="G12" s="29" t="n">
-        <v>0.0814</v>
+        <v>-0.0121</v>
       </c>
       <c r="H12" s="29" t="n">
-        <v>0.256</v>
+        <v>0.036</v>
       </c>
       <c r="I12" s="29" t="n">
-        <v>0.047</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>0.12</v>
@@ -9990,27 +10048,27 @@
         <v>1.8</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>-0.0352</v>
+        <v>-0.1193</v>
       </c>
       <c r="F13" s="29" t="n">
-        <v>-0.1689</v>
+        <v>-0.2401</v>
       </c>
       <c r="G13" s="29" t="n">
-        <v>0.0976</v>
+        <v>0.0035</v>
       </c>
       <c r="H13" s="29" t="n">
-        <v>0.325</v>
+        <v>0.057</v>
       </c>
       <c r="I13" s="29" t="n">
-        <v>0.074</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>0.12</v>
@@ -10019,27 +10077,27 @@
         <v>2.7</v>
       </c>
       <c r="E14" s="29" t="n">
-        <v>-0.0631</v>
+        <v>-0.1472</v>
       </c>
       <c r="F14" s="29" t="n">
-        <v>-0.198</v>
+        <v>-0.2713</v>
       </c>
       <c r="G14" s="29" t="n">
-        <v>0.0699</v>
+        <v>-0.021</v>
       </c>
       <c r="H14" s="29" t="n">
-        <v>0.219</v>
+        <v>0.033</v>
       </c>
       <c r="I14" s="29" t="n">
-        <v>0.049</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>0.12</v>
@@ -10048,27 +10106,27 @@
         <v>3.6</v>
       </c>
       <c r="E15" s="29" t="n">
-        <v>-0.0995</v>
+        <v>-0.1827</v>
       </c>
       <c r="F15" s="29" t="n">
-        <v>-0.2409</v>
+        <v>-0.309</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>0.0345</v>
+        <v>-0.0523</v>
       </c>
       <c r="H15" s="29" t="n">
-        <v>0.116</v>
+        <v>0.009</v>
       </c>
       <c r="I15" s="29" t="n">
-        <v>0.046</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>0.16</v>
@@ -10077,27 +10135,27 @@
         <v>1.8</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>-0.0563</v>
+        <v>-0.1406</v>
       </c>
       <c r="F16" s="29" t="n">
-        <v>-0.1915</v>
+        <v>-0.265</v>
       </c>
       <c r="G16" s="29" t="n">
-        <v>0.0781</v>
+        <v>-0.0148</v>
       </c>
       <c r="H16" s="29" t="n">
-        <v>0.244</v>
+        <v>0.036</v>
       </c>
       <c r="I16" s="29" t="n">
-        <v>0.052</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>0.16</v>
@@ -10106,27 +10164,27 @@
         <v>2.7</v>
       </c>
       <c r="E17" s="29" t="n">
-        <v>-0.1374</v>
+        <v>-0.22</v>
       </c>
       <c r="F17" s="29" t="n">
-        <v>-0.288</v>
+        <v>-0.3579</v>
       </c>
       <c r="G17" s="29" t="n">
-        <v>0.0045</v>
+        <v>-0.0847</v>
       </c>
       <c r="H17" s="29" t="n">
-        <v>0.058</v>
+        <v>0.003</v>
       </c>
       <c r="I17" s="29" t="n">
-        <v>0.048</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>0.08</v>
@@ -10135,27 +10193,27 @@
         <v>3.6</v>
       </c>
       <c r="E18" s="29" t="n">
-        <v>0.2184</v>
+        <v>0.1636</v>
       </c>
       <c r="F18" s="29" t="n">
-        <v>0.1365</v>
+        <v>0.0945</v>
       </c>
       <c r="G18" s="29" t="n">
-        <v>0.3014</v>
+        <v>0.2432</v>
       </c>
       <c r="H18" s="29" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="29" t="n">
-        <v>0.162</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C19" s="10" t="n">
         <v>0.08</v>
@@ -10164,27 +10222,27 @@
         <v>4.5</v>
       </c>
       <c r="E19" s="29" t="n">
-        <v>0.1967</v>
+        <v>0.1516</v>
       </c>
       <c r="F19" s="29" t="n">
-        <v>0.1168</v>
+        <v>0.0819</v>
       </c>
       <c r="G19" s="29" t="n">
-        <v>0.2811</v>
+        <v>0.2313</v>
       </c>
       <c r="H19" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I19" s="29" t="n">
-        <v>0.102</v>
+        <v>0.284</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C20" s="10" t="n">
         <v>0.08</v>
@@ -10193,27 +10251,27 @@
         <v>5.4</v>
       </c>
       <c r="E20" s="29" t="n">
-        <v>0.1753</v>
+        <v>0.1396</v>
       </c>
       <c r="F20" s="29" t="n">
-        <v>0.0944</v>
+        <v>0.0684</v>
       </c>
       <c r="G20" s="29" t="n">
-        <v>0.2617</v>
+        <v>0.2195</v>
       </c>
       <c r="H20" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I20" s="29" t="n">
-        <v>0.049</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C21" s="10" t="n">
         <v>0.11</v>
@@ -10222,27 +10280,27 @@
         <v>3.6</v>
       </c>
       <c r="E21" s="29" t="n">
-        <v>0.1985</v>
+        <v>0.1539</v>
       </c>
       <c r="F21" s="29" t="n">
-        <v>0.1176</v>
+        <v>0.0834</v>
       </c>
       <c r="G21" s="29" t="n">
-        <v>0.2801</v>
+        <v>0.2337</v>
       </c>
       <c r="H21" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I21" s="29" t="n">
-        <v>0.1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C22" s="10" t="n">
         <v>0.11</v>
@@ -10251,27 +10309,27 @@
         <v>4.5</v>
       </c>
       <c r="E22" s="29" t="n">
-        <v>0.1758</v>
+        <v>0.1396</v>
       </c>
       <c r="F22" s="29" t="n">
-        <v>0.095</v>
+        <v>0.0668</v>
       </c>
       <c r="G22" s="29" t="n">
-        <v>0.2635</v>
+        <v>0.2195</v>
       </c>
       <c r="H22" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I22" s="29" t="n">
-        <v>0.05</v>
+        <v>0.282</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>0.11</v>
@@ -10280,27 +10338,27 @@
         <v>5.4</v>
       </c>
       <c r="E23" s="29" t="n">
-        <v>0.152</v>
+        <v>0.1162</v>
       </c>
       <c r="F23" s="29" t="n">
-        <v>0.0638</v>
+        <v>0.0396</v>
       </c>
       <c r="G23" s="29" t="n">
-        <v>0.2417</v>
+        <v>0.196</v>
       </c>
       <c r="H23" s="29" t="n">
-        <v>0.998</v>
+        <v>0.991</v>
       </c>
       <c r="I23" s="29" t="n">
-        <v>0.053</v>
+        <v>0.285</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C24" s="10" t="n">
         <v>0.14</v>
@@ -10309,27 +10367,27 @@
         <v>3.6</v>
       </c>
       <c r="E24" s="29" t="n">
-        <v>0.1848</v>
+        <v>0.1472</v>
       </c>
       <c r="F24" s="29" t="n">
-        <v>0.1044</v>
+        <v>0.075</v>
       </c>
       <c r="G24" s="29" t="n">
-        <v>0.2717</v>
+        <v>0.2268</v>
       </c>
       <c r="H24" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I24" s="29" t="n">
-        <v>0.058</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>0.14</v>
@@ -10338,27 +10396,27 @@
         <v>4.5</v>
       </c>
       <c r="E25" s="29" t="n">
-        <v>0.1614</v>
+        <v>0.124</v>
       </c>
       <c r="F25" s="29" t="n">
-        <v>0.0705</v>
+        <v>0.0439</v>
       </c>
       <c r="G25" s="29" t="n">
-        <v>0.2525</v>
+        <v>0.2061</v>
       </c>
       <c r="H25" s="29" t="n">
-        <v>0.998</v>
+        <v>0.994</v>
       </c>
       <c r="I25" s="29" t="n">
-        <v>0.062</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C26" s="10" t="n">
         <v>0.08</v>
@@ -10367,27 +10425,27 @@
         <v>1.8</v>
       </c>
       <c r="E26" s="29" t="n">
-        <v>0.178</v>
+        <v>0.1217</v>
       </c>
       <c r="F26" s="29" t="n">
-        <v>0.0898</v>
+        <v>0.0502</v>
       </c>
       <c r="G26" s="29" t="n">
-        <v>0.2668</v>
+        <v>0.207</v>
       </c>
       <c r="H26" s="29" t="n">
         <v>0.999</v>
       </c>
       <c r="I26" s="29" t="n">
-        <v>0.169</v>
+        <v>0.224</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>0.08</v>
@@ -10396,27 +10454,27 @@
         <v>2.7</v>
       </c>
       <c r="E27" s="29" t="n">
-        <v>0.174</v>
+        <v>0.1329</v>
       </c>
       <c r="F27" s="29" t="n">
-        <v>0.0917</v>
+        <v>0.0633</v>
       </c>
       <c r="G27" s="29" t="n">
-        <v>0.2601</v>
+        <v>0.2136</v>
       </c>
       <c r="H27" s="29" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="I27" s="29" t="n">
-        <v>0.085</v>
+        <v>0.264</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C28" s="10" t="n">
         <v>0.08</v>
@@ -10425,27 +10483,27 @@
         <v>3.6</v>
       </c>
       <c r="E28" s="29" t="n">
-        <v>0.1566</v>
+        <v>0.1218</v>
       </c>
       <c r="F28" s="29" t="n">
-        <v>0.0741</v>
+        <v>0.0522</v>
       </c>
       <c r="G28" s="29" t="n">
-        <v>0.2453</v>
+        <v>0.2026</v>
       </c>
       <c r="H28" s="29" t="n">
-        <v>0.999</v>
+        <v>0.998</v>
       </c>
       <c r="I28" s="29" t="n">
-        <v>0.047</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C29" s="10" t="n">
         <v>0.12</v>
@@ -10454,27 +10512,27 @@
         <v>1.8</v>
       </c>
       <c r="E29" s="29" t="n">
-        <v>0.0999</v>
+        <v>0.0369</v>
       </c>
       <c r="F29" s="29" t="n">
-        <v>0.0025</v>
+        <v>-0.0479</v>
       </c>
       <c r="G29" s="29" t="n">
-        <v>0.2036</v>
+        <v>0.1311</v>
       </c>
       <c r="H29" s="29" t="n">
-        <v>0.955</v>
+        <v>0.733</v>
       </c>
       <c r="I29" s="29" t="n">
-        <v>0.074</v>
+        <v>0.102</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>0.12</v>
@@ -10483,27 +10541,27 @@
         <v>2.7</v>
       </c>
       <c r="E30" s="29" t="n">
-        <v>0.1203</v>
+        <v>0.0589</v>
       </c>
       <c r="F30" s="29" t="n">
-        <v>0.0345</v>
+        <v>-0.0176</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>0.212</v>
+        <v>0.1495</v>
       </c>
       <c r="H30" s="29" t="n">
-        <v>0.993</v>
+        <v>0.884</v>
       </c>
       <c r="I30" s="29" t="n">
-        <v>0.049</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>0.12</v>
@@ -10512,27 +10570,27 @@
         <v>3.6</v>
       </c>
       <c r="E31" s="29" t="n">
-        <v>0.0969</v>
+        <v>0.0353</v>
       </c>
       <c r="F31" s="29" t="n">
-        <v>0.0021</v>
+        <v>-0.05</v>
       </c>
       <c r="G31" s="29" t="n">
-        <v>0.1938</v>
+        <v>0.1264</v>
       </c>
       <c r="H31" s="29" t="n">
-        <v>0.954</v>
+        <v>0.744</v>
       </c>
       <c r="I31" s="29" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>0.16</v>
@@ -10541,27 +10599,27 @@
         <v>1.8</v>
       </c>
       <c r="E32" s="29" t="n">
-        <v>0.0654</v>
+        <v>-0.0024</v>
       </c>
       <c r="F32" s="29" t="n">
-        <v>-0.0352</v>
+        <v>-0.092</v>
       </c>
       <c r="G32" s="29" t="n">
-        <v>0.1748</v>
+        <v>0.0971</v>
       </c>
       <c r="H32" s="29" t="n">
-        <v>0.85</v>
+        <v>0.489</v>
       </c>
       <c r="I32" s="29" t="n">
-        <v>0.052</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C33" s="10" t="n">
         <v>0.16</v>
@@ -10570,19 +10628,19 @@
         <v>2.7</v>
       </c>
       <c r="E33" s="29" t="n">
-        <v>0.0288</v>
+        <v>-0.0362</v>
       </c>
       <c r="F33" s="29" t="n">
-        <v>-0.0961</v>
+        <v>-0.1457</v>
       </c>
       <c r="G33" s="29" t="n">
-        <v>0.1474</v>
+        <v>0.0729</v>
       </c>
       <c r="H33" s="29" t="n">
-        <v>0.639</v>
+        <v>0.308</v>
       </c>
       <c r="I33" s="29" t="n">
-        <v>0.048</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10590,98 +10648,98 @@
         <v>36</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B37" s="29" t="n">
-        <v>-0.1544</v>
+        <v>-0.1368</v>
       </c>
       <c r="C37" s="29" t="n">
-        <v>-0.2241</v>
+        <v>-0.1683</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B38" s="29" t="n">
-        <v>-0.0669</v>
+        <v>-0.0983</v>
       </c>
       <c r="C38" s="29" t="n">
-        <v>-0.1162</v>
+        <v>-0.1442</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B39" s="29" t="n">
-        <v>0.1121</v>
+        <v>0.1482</v>
       </c>
       <c r="C39" s="29" t="n">
-        <v>0.1471</v>
+        <v>0.2132</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B40" s="29" t="n">
-        <v>-0.0135</v>
+        <v>0.0279</v>
       </c>
       <c r="C40" s="29" t="n">
-        <v>0.0005</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B41" s="29" t="n">
-        <v>0.0391</v>
+        <v>0.0642</v>
       </c>
       <c r="C41" s="29" t="n">
-        <v>0.0813</v>
+        <v>0.1247</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B42" s="29" t="n">
-        <v>-0.0216</v>
+        <v>-0.0326</v>
       </c>
       <c r="C42" s="29" t="n">
-        <v>-0.0086</v>
+        <v>-0.0663</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="29" t="n">
-        <v>0.0213</v>
+        <v>0.0219</v>
       </c>
       <c r="C43" s="29" t="n">
-        <v>0.0389</v>
+        <v>0.0513</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B44" s="29" t="n">
-        <v>0.0913</v>
+        <v>0.083</v>
       </c>
       <c r="C44" s="29" t="n">
-        <v>0.1415</v>
+        <v>0.1065</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10689,10 +10747,10 @@
         <v>73</v>
       </c>
       <c r="B45" s="29" t="n">
-        <v>0.0651</v>
+        <v>0.036</v>
       </c>
       <c r="C45" s="29" t="n">
-        <v>0.1085</v>
+        <v>0.0848</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10700,10 +10758,10 @@
         <v>77</v>
       </c>
       <c r="B46" s="29" t="n">
-        <v>0.0287</v>
+        <v>0.0233</v>
       </c>
       <c r="C46" s="29" t="n">
-        <v>0.0314</v>
+        <v>0.0003</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10711,32 +10769,32 @@
         <v>85</v>
       </c>
       <c r="B47" s="29" t="n">
-        <v>0.1925</v>
+        <v>0.3334</v>
       </c>
       <c r="C47" s="29" t="n">
-        <v>0.2042</v>
+        <v>0.3892</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B48" s="29" t="n">
-        <v>0.025</v>
+        <v>0.003</v>
       </c>
       <c r="C48" s="29" t="n">
-        <v>0.0079</v>
+        <v>-0.0177</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" s="29" t="n">
-        <v>0.0174</v>
+        <v>0.037</v>
       </c>
       <c r="C49" s="29" t="n">
-        <v>0.0092</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10744,21 +10802,21 @@
         <v>83</v>
       </c>
       <c r="B50" s="29" t="n">
-        <v>0.0042</v>
+        <v>0.0359</v>
       </c>
       <c r="C50" s="29" t="n">
-        <v>0.0018</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B51" s="29" t="n">
-        <v>-0.0672</v>
+        <v>-0.0383</v>
       </c>
       <c r="C51" s="29" t="n">
-        <v>-0.1007</v>
+        <v>-0.1184</v>
       </c>
     </row>
   </sheetData>
@@ -11103,10 +11161,10 @@
         <v>75</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>1.2</v>
@@ -11114,73 +11172,73 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0.22</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0.096</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>35.9</v>
       </c>
       <c r="D19" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="C20" s="7" t="n">
         <v>22</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>48</v>
@@ -11190,16 +11248,16 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="C21" s="7" t="n">
         <v>0.15</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>76</v>
@@ -11209,10 +11267,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>3.5</v>
@@ -11221,17 +11279,17 @@
         <v>66</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="C23" s="7" t="n">
         <v>0.92</v>
@@ -11251,10 +11309,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="C24" s="7" t="n">
         <v>0.95</v>
@@ -11274,29 +11332,29 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="C25" s="7" t="n">
         <v>8</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="C26" s="7" t="n">
         <v>0.92</v>
@@ -11312,54 +11370,54 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="C27" s="7" t="n">
         <v>300</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="C28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>15.4</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>60</v>
@@ -11369,10 +11427,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="C30" s="7" t="n">
         <v>6.3</v>
@@ -11388,67 +11446,67 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="C31" s="7" t="n">
         <v>452.12</v>
       </c>
       <c r="D31" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="F31" s="6"/>
       <c r="G31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="C32" s="7" t="n">
         <v>13300</v>
       </c>
       <c r="D32" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>133</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>134</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="C33" s="7" t="n">
         <v>5050</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="C34" s="7" t="n">
         <v>1.467</v>
@@ -11457,7 +11515,7 @@
         <v>75</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>1.3</v>
@@ -11468,19 +11526,19 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>142</v>
       </c>
       <c r="C35" s="7" t="n">
         <v>45.59</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>39.3</v>
@@ -11491,19 +11549,19 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="C36" s="7" t="n">
         <v>345</v>
       </c>
       <c r="D36" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>148</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>300</v>
@@ -11514,48 +11572,48 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="C37" s="7" t="n">
         <v>365262</v>
       </c>
       <c r="D37" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>166</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>1.15</v>
@@ -11571,16 +11629,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>157</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>158</v>
       </c>
       <c r="C40" s="7" t="n">
         <v>600</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>76</v>
@@ -11594,16 +11652,16 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>76</v>
@@ -11613,10 +11671,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>0.05</v>
@@ -11636,16 +11694,16 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>76</v>
@@ -11655,10 +11713,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>0.007</v>
@@ -11667,17 +11725,17 @@
         <v>75</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>170</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>171</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>2</v>
@@ -11686,17 +11744,17 @@
         <v>75</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>172</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>173</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>0.6</v>
@@ -11716,19 +11774,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>174</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>200</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>100</v>
@@ -11739,16 +11797,16 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>3000</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>76</v>
@@ -11758,16 +11816,16 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="C49" s="7" t="n">
         <v>10</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49" s="6" t="s">
         <v>76</v>
@@ -11777,19 +11835,19 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="C50" s="7" t="n">
         <v>0.606</v>
       </c>
       <c r="D50" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>0.45</v>
@@ -11800,29 +11858,29 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="C51" s="7" t="n">
         <v>2.68</v>
       </c>
       <c r="D51" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>190</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="6"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="C52" s="7" t="n">
         <v>2.5</v>
@@ -11831,7 +11889,7 @@
         <v>75</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>2.1</v>
@@ -11842,10 +11900,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="C53" s="7" t="n">
         <v>1.15</v>
@@ -11854,17 +11912,17 @@
         <v>75</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="6"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>198</v>
       </c>
       <c r="C54" s="7" t="n">
         <v>0.16</v>
@@ -11873,36 +11931,36 @@
         <v>75</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="6"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="C55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="C55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="6" t="s">
+      <c r="E55" s="6" t="s">
         <v>202</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>203</v>
       </c>
       <c r="F55" s="6"/>
       <c r="G55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>205</v>
       </c>
       <c r="C56" s="7" t="n">
         <v>0.5</v>
@@ -11911,22 +11969,22 @@
         <v>75</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F56" s="6"/>
       <c r="G56" s="6"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="C59" s="8" t="n">
         <f aca="false">E_bat_kWh*(SOC_max-SOC_min)/100</f>
@@ -11935,10 +11993,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="C60" s="8" t="n">
         <f aca="false">T_shift_h*tau_svc</f>
@@ -11947,10 +12005,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>212</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>213</v>
       </c>
       <c r="C61" s="8" t="n">
         <f aca="false">l_charge_km/v_transp_kmh</f>
@@ -11959,10 +12017,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>215</v>
       </c>
       <c r="C62" s="8" t="n">
         <f aca="false">P_transp_kW*t_tr</f>
@@ -11971,10 +12029,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="C63" s="8" t="n">
         <f aca="false">E_use/(eta_ch*eta_bat*P_ch_ac)</f>
@@ -11983,10 +12041,10 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="C64" s="8" t="n">
         <f aca="false">k_pto_D*P_e_nom_D</f>
@@ -11995,10 +12053,10 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>220</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="C65" s="8" t="n">
         <f aca="false">wage_month/h_month*k_soc</f>
@@ -12007,10 +12065,10 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>222</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>223</v>
       </c>
       <c r="C66" s="8" t="n">
         <f aca="false">price_ET_usd*usd_kzt*k_landed</f>
@@ -12019,10 +12077,10 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="C67" s="8" t="n">
         <f aca="false">price_D_usd*usd_kzt*k_landed</f>
@@ -12031,10 +12089,10 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="C68" s="8" t="n">
         <f aca="false">T_year_h*life_y</f>
@@ -12043,10 +12101,10 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="C69" s="8" t="n">
         <f aca="false">ASAE_RF1*price_D*(T_life/1000)^ASAE_RF2/T_life</f>
@@ -12055,10 +12113,10 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="C70" s="8" t="n">
         <f aca="false">IF(r_disc=0,1/life_y,r_disc*(1+r_disc)^life_y/((1+r_disc)^life_y-1))</f>
@@ -12067,10 +12125,10 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="C71" s="8" t="n">
         <f aca="false">IF(r_disc=0,1/life_y,r_disc/((1+r_disc)^life_y-1))</f>
@@ -12079,10 +12137,10 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="C72" s="8" t="n">
         <f aca="false">bat_usd_kWh*E_bat_kWh*usd_kzt</f>
@@ -12091,10 +12149,10 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>236</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="C73" s="8" t="n">
         <f aca="false">k_D*(sfc_a*(eta_ep*(turn_P-P_aux)+P_hyd_idle_D)+sfc_b*P_pto_nom)</f>
@@ -12103,10 +12161,10 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="C74" s="8" t="n">
         <f aca="false">k_D*(sfc_a*(eta_ep*(P_transp_kW-P_aux)*m_D/m_ET+P_hyd_idle_D)+sfc_b*P_pto_nom)</f>
@@ -12141,103 +12199,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="9" t="s">
         <v>266</v>
-      </c>
-      <c r="AB1" s="9" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>0</v>
@@ -12246,7 +12304,7 @@
         <v>4.5</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>80</v>
@@ -12287,17 +12345,17 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>0</v>
@@ -12306,7 +12364,7 @@
         <v>4.5</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>80</v>
@@ -12347,17 +12405,17 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0</v>
@@ -12366,7 +12424,7 @@
         <v>4.5</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>80</v>
@@ -12407,17 +12465,17 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>0</v>
@@ -12426,7 +12484,7 @@
         <v>4.5</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>80</v>
@@ -12467,10 +12525,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>1</v>
@@ -12479,7 +12537,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.11</v>
@@ -12488,7 +12546,7 @@
         <v>5.4</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>67</v>
@@ -12556,10 +12614,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
@@ -12568,7 +12626,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0.08</v>
@@ -12577,7 +12635,7 @@
         <v>5.4</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>66</v>
@@ -12645,10 +12703,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>3</v>
@@ -12657,7 +12715,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.14</v>
@@ -12666,7 +12724,7 @@
         <v>4.5</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>80</v>
@@ -12734,10 +12792,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>4</v>
@@ -12746,7 +12804,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.11</v>
@@ -12755,7 +12813,7 @@
         <v>4.5</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>79</v>
@@ -12823,10 +12881,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>5</v>
@@ -12835,7 +12893,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.11</v>
@@ -12844,7 +12902,7 @@
         <v>3.6</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>100</v>
@@ -12912,10 +12970,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>6</v>
@@ -12924,7 +12982,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>0.08</v>
@@ -12933,7 +12991,7 @@
         <v>4.5</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>80</v>
@@ -13001,10 +13059,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>7</v>
@@ -13013,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.08</v>
@@ -13022,7 +13080,7 @@
         <v>3.6</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>100</v>
@@ -13090,10 +13148,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>8</v>
@@ -13102,7 +13160,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0.14</v>
@@ -13111,7 +13169,7 @@
         <v>3.6</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>100</v>
@@ -13179,10 +13237,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>9</v>
@@ -13191,7 +13249,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0.08</v>
@@ -13200,7 +13258,7 @@
         <v>5.4</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>67</v>
@@ -13268,10 +13326,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>10</v>
@@ -13280,7 +13338,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>0.08</v>
@@ -13289,7 +13347,7 @@
         <v>4.5</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>80</v>
@@ -13357,10 +13415,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>11</v>
@@ -13369,7 +13427,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0.08</v>
@@ -13378,7 +13436,7 @@
         <v>3.6</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>100</v>
@@ -13446,10 +13504,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>12</v>
@@ -13458,7 +13516,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>0.14</v>
@@ -13467,7 +13525,7 @@
         <v>3.6</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>100</v>
@@ -13535,10 +13593,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>13</v>
@@ -13547,7 +13605,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>0.11</v>
@@ -13556,7 +13614,7 @@
         <v>3.6</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>100</v>
@@ -13624,10 +13682,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>14</v>
@@ -13636,7 +13694,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>0.14</v>
@@ -13645,7 +13703,7 @@
         <v>4.5</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>81</v>
@@ -13713,10 +13771,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>15</v>
@@ -13725,7 +13783,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>0.11</v>
@@ -13734,7 +13792,7 @@
         <v>4.5</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>80</v>
@@ -13802,10 +13860,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>16</v>
@@ -13814,7 +13872,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>0.11</v>
@@ -13823,7 +13881,7 @@
         <v>5.4</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>67</v>
@@ -13891,10 +13949,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>17</v>
@@ -13903,7 +13961,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>0.14</v>
@@ -13912,7 +13970,7 @@
         <v>4.5</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>79</v>
@@ -13980,10 +14038,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>18</v>
@@ -13992,7 +14050,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>0.08</v>
@@ -14001,7 +14059,7 @@
         <v>3.6</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>100</v>
@@ -14069,10 +14127,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>19</v>
@@ -14081,7 +14139,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>0.11</v>
@@ -14090,7 +14148,7 @@
         <v>5.4</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>67</v>
@@ -14158,10 +14216,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>20</v>
@@ -14170,7 +14228,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>0.11</v>
@@ -14179,7 +14237,7 @@
         <v>3.6</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>101</v>
@@ -14247,10 +14305,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>21</v>
@@ -14259,7 +14317,7 @@
         <v>3</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>0.11</v>
@@ -14268,7 +14326,7 @@
         <v>4.5</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>79</v>
@@ -14336,10 +14394,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>22</v>
@@ -14348,7 +14406,7 @@
         <v>3</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>0.08</v>
@@ -14357,7 +14415,7 @@
         <v>4.5</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>80</v>
@@ -14425,10 +14483,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>23</v>
@@ -14437,7 +14495,7 @@
         <v>3</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0.14</v>
@@ -14446,7 +14504,7 @@
         <v>3.6</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>100</v>
@@ -14514,10 +14572,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>24</v>
@@ -14526,7 +14584,7 @@
         <v>3</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0.08</v>
@@ -14535,7 +14593,7 @@
         <v>5.4</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>66</v>
@@ -14603,17 +14661,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>0</v>
@@ -14622,7 +14680,7 @@
         <v>2.7</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>133</v>
@@ -14663,17 +14721,17 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>0</v>
@@ -14682,7 +14740,7 @@
         <v>2.7</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>133</v>
@@ -14723,17 +14781,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>0</v>
@@ -14742,7 +14800,7 @@
         <v>2.7</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>133</v>
@@ -14783,17 +14841,17 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>0</v>
@@ -14802,7 +14860,7 @@
         <v>2.7</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>133</v>
@@ -14843,17 +14901,17 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>0</v>
@@ -14862,7 +14920,7 @@
         <v>2.7</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>133</v>
@@ -14903,17 +14961,17 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>0</v>
@@ -14922,7 +14980,7 @@
         <v>2.7</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>133</v>
@@ -14963,17 +15021,17 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>0</v>
@@ -14982,7 +15040,7 @@
         <v>2.7</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>133</v>
@@ -15023,17 +15081,17 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>0</v>
@@ -15042,7 +15100,7 @@
         <v>2.7</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>133</v>
@@ -15083,10 +15141,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C38" s="6" t="n">
         <v>1</v>
@@ -15095,7 +15153,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>0.12</v>
@@ -15104,7 +15162,7 @@
         <v>2.7</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>134</v>
@@ -15160,10 +15218,10 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>2</v>
@@ -15172,7 +15230,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>0.08</v>
@@ -15181,7 +15239,7 @@
         <v>2.7</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>134</v>
@@ -15237,10 +15295,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>3</v>
@@ -15249,7 +15307,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>0.16</v>
@@ -15258,7 +15316,7 @@
         <v>1.8</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>200</v>
@@ -15314,10 +15372,10 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C41" s="6" t="n">
         <v>4</v>
@@ -15326,7 +15384,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>0.08</v>
@@ -15335,7 +15393,7 @@
         <v>3.6</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>100</v>
@@ -15391,10 +15449,10 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C42" s="6" t="n">
         <v>5</v>
@@ -15403,7 +15461,7 @@
         <v>1</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>0.12</v>
@@ -15412,7 +15470,7 @@
         <v>1.8</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>201</v>
@@ -15468,10 +15526,10 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>6</v>
@@ -15480,7 +15538,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>0.08</v>
@@ -15489,7 +15547,7 @@
         <v>1.8</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>201</v>
@@ -15545,10 +15603,10 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C44" s="6" t="n">
         <v>7</v>
@@ -15557,7 +15615,7 @@
         <v>1</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>0.12</v>
@@ -15566,7 +15624,7 @@
         <v>3.6</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>100</v>
@@ -15622,10 +15680,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>8</v>
@@ -15634,7 +15692,7 @@
         <v>1</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>0.16</v>
@@ -15643,7 +15701,7 @@
         <v>2.7</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>134</v>
@@ -15699,10 +15757,10 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>9</v>
@@ -15711,7 +15769,7 @@
         <v>2</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>0.12</v>
@@ -15720,7 +15778,7 @@
         <v>1.8</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>201</v>
@@ -15776,10 +15834,10 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C47" s="6" t="n">
         <v>10</v>
@@ -15788,7 +15846,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>0.08</v>
@@ -15797,7 +15855,7 @@
         <v>3.6</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>100</v>
@@ -15853,10 +15911,10 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C48" s="6" t="n">
         <v>11</v>
@@ -15865,7 +15923,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>0.08</v>
@@ -15874,7 +15932,7 @@
         <v>1.8</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>201</v>
@@ -15930,10 +15988,10 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>12</v>
@@ -15942,7 +16000,7 @@
         <v>2</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>0.16</v>
@@ -15951,7 +16009,7 @@
         <v>2.7</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>133</v>
@@ -16007,10 +16065,10 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C50" s="6" t="n">
         <v>13</v>
@@ -16019,7 +16077,7 @@
         <v>2</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>0.16</v>
@@ -16028,7 +16086,7 @@
         <v>1.8</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>200</v>
@@ -16084,10 +16142,10 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C51" s="6" t="n">
         <v>14</v>
@@ -16096,7 +16154,7 @@
         <v>2</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>0.12</v>
@@ -16105,7 +16163,7 @@
         <v>3.6</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>100</v>
@@ -16161,10 +16219,10 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>15</v>
@@ -16173,7 +16231,7 @@
         <v>2</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>0.08</v>
@@ -16182,7 +16240,7 @@
         <v>2.7</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>134</v>
@@ -16238,10 +16296,10 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>273</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>274</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>16</v>
@@ -16250,7 +16308,7 @@
         <v>2</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0.12</v>
@@ -16259,7 +16317,7 @@
         <v>2.7</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I53" s="6" t="n">
         <v>134</v>
@@ -16315,10 +16373,10 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>18</v>
@@ -16327,7 +16385,7 @@
         <v>3</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>0.08</v>
@@ -16336,7 +16394,7 @@
         <v>3.6</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>100</v>
@@ -16392,10 +16450,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C55" s="6" t="n">
         <v>19</v>
@@ -16404,7 +16462,7 @@
         <v>3</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>0.12</v>
@@ -16413,7 +16471,7 @@
         <v>3.6</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>100</v>
@@ -16469,10 +16527,10 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>20</v>
@@ -16481,7 +16539,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>0.16</v>
@@ -16490,7 +16548,7 @@
         <v>2.7</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>134</v>
@@ -16546,10 +16604,10 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C57" s="6" t="n">
         <v>21</v>
@@ -16558,7 +16616,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>0.12</v>
@@ -16567,7 +16625,7 @@
         <v>2.7</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>134</v>
@@ -16623,10 +16681,10 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>22</v>
@@ -16635,7 +16693,7 @@
         <v>3</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>0.08</v>
@@ -16644,7 +16702,7 @@
         <v>2.7</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I58" s="6" t="n">
         <v>134</v>
@@ -16700,10 +16758,10 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>23</v>
@@ -16712,7 +16770,7 @@
         <v>3</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>0.08</v>
@@ -16721,7 +16779,7 @@
         <v>1.8</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I59" s="6" t="n">
         <v>201</v>
@@ -16777,10 +16835,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C60" s="6" t="n">
         <v>24</v>
@@ -16789,7 +16847,7 @@
         <v>3</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>0.16</v>
@@ -16798,7 +16856,7 @@
         <v>1.8</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I60" s="6" t="n">
         <v>200</v>
@@ -16854,10 +16912,10 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C61" s="6" t="n">
         <v>25</v>
@@ -16866,7 +16924,7 @@
         <v>3</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>0.12</v>
@@ -16875,7 +16933,7 @@
         <v>1.8</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I61" s="6" t="n">
         <v>201</v>
@@ -16956,10 +17014,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>280</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>37</v>
@@ -16968,15 +17026,15 @@
         <v>38</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>282</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>283</v>
       </c>
       <c r="C2" s="15" t="n">
         <f aca="false">AVERAGE(Проходы!W2:W5)/(m_ET*g)</f>
@@ -16986,51 +17044,51 @@
         <v>75</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>285</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>286</v>
       </c>
       <c r="C3" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!Y6:Y29,Проходы!V6:V29),1,2)*1000</f>
         <v>34579.4225774855</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="C4" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!Y6:Y29,Проходы!V6:V29),1,1)*1000</f>
         <v>1989.17591054482</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="C5" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!Y6:Y29,Проходы!V6:V29,TRUE(),TRUE()),3,1)</f>
@@ -17040,15 +17098,15 @@
         <v>75</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>0.821404</v>
@@ -17057,15 +17115,15 @@
         <v>75</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>6.745697</v>
@@ -17074,33 +17132,33 @@
         <v>75</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="C8" s="15" t="n">
         <f aca="false">AVERAGE(Проходы!AB30:AB37)</f>
         <v>2.05875785793399</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>0.9812</v>
@@ -17109,69 +17167,69 @@
         <v>66</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>308</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>309</v>
       </c>
       <c r="C10" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!AA38:AA61,Проходы!M38:N61),1,3)</f>
         <v>125.550648318433</v>
       </c>
       <c r="D10" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>312</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>313</v>
       </c>
       <c r="C11" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!AA38:AA61,Проходы!M38:N61),1,2)</f>
         <v>-10.2737530004209</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>315</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="C12" s="15" t="n">
         <f aca="false">INDEX(LINEST(Проходы!AA38:AA61,Проходы!M38:N61),1,1)</f>
         <v>-28.2256677671611</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>318</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">AVERAGE(Проходы!T38:T61)</f>
@@ -17181,15 +17239,15 @@
         <v>75</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>322</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>0</v>
@@ -17198,15 +17256,15 @@
         <v>75</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>0.032418</v>
@@ -17215,21 +17273,21 @@
         <v>75</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>327</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>328</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>32.194</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>60</v>
@@ -17237,10 +17295,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>330</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>331</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>2.9974</v>
@@ -17277,45 +17335,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="L1" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>0.08</v>
@@ -17362,7 +17420,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>0.08</v>
@@ -17409,7 +17467,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>0.08</v>
@@ -17456,7 +17514,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>0.11</v>
@@ -17503,7 +17561,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>0.11</v>
@@ -17550,7 +17608,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>0.11</v>
@@ -17597,7 +17655,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B8" s="6" t="n">
         <v>0.14</v>
@@ -17644,7 +17702,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>0.14</v>
@@ -17691,7 +17749,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>0.08</v>
@@ -17738,7 +17796,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>0.08</v>
@@ -17785,7 +17843,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B12" s="6" t="n">
         <v>0.08</v>
@@ -17832,7 +17890,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B13" s="6" t="n">
         <v>0.12</v>
@@ -17879,7 +17937,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>0.12</v>
@@ -17926,7 +17984,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B15" s="6" t="n">
         <v>0.12</v>
@@ -17973,7 +18031,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>0.16</v>
@@ -18020,7 +18078,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B17" s="6" t="n">
         <v>0.16</v>
@@ -18090,67 +18148,67 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>351</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19545,84 +19603,87 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="2" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>375</v>
       </c>
     </row>
@@ -19664,23 +19725,23 @@
         <v>2.11239488770896</v>
       </c>
       <c r="J2" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I2,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I2,T_av-2*t_tr,IF(S_task&gt;0,S_task*D2-(0),1000000000)))</f>
         <v>2.11239488770896</v>
       </c>
       <c r="K2" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J2)-t_tr&gt;0.000001,T_av-(t_tr+J2)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J2)-t_tr&gt;0.000001,T_av-(t_tr+J2)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D2-(J2),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="L2" s="12" t="n">
-        <f aca="false">IF(K2,MAX(0,MIN(I2,T_av-(t_tr+J2+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K2,MAX(0,MIN(I2,T_av-(t_tr+J2+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D2-(J2),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="M2" s="19" t="b">
-        <f aca="false">AND(K2,L2&gt;0,T_av-(t_tr+J2+2*t_tr+t_ch+L2)-t_tr&gt;0.000001,T_av-(t_tr+J2+2*t_tr+t_ch+L2)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K2,L2&gt;0,T_av-(t_tr+J2+2*t_tr+t_ch+L2)-t_tr&gt;0.000001,T_av-(t_tr+J2+2*t_tr+t_ch+L2)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D2-(J2+L2),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N2" s="12" t="n">
-        <f aca="false">IF(M2,MAX(0,MIN(I2,T_av-((t_tr+J2+2*t_tr+t_ch+L2)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M2,MAX(0,MIN(I2,T_av-((t_tr+J2+2*t_tr+t_ch+L2)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D2-(J2+L2),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O2" s="14" t="n">
@@ -19708,11 +19769,11 @@
         <v>7.51524643464724</v>
       </c>
       <c r="U2" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S2+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D2&lt;T_av-2*t_tr-Y2*t_refuel_h),MAX(0,(S_task*D2*S2+2*t_tr*Q_tr)/tank_D-1),Y2)</f>
         <v>0</v>
       </c>
       <c r="V2" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U2*t_refuel_h)/D2</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D2&lt;T_av-2*t_tr-Y2*t_refuel_h),S_task,(T_av-2*t_tr-Y2*t_refuel_h)/D2)</f>
         <v>2.8207156997683</v>
       </c>
       <c r="W2" s="12" t="n">
@@ -19722,6 +19783,10 @@
       <c r="X2" s="11" t="n">
         <f aca="false">T2/D2</f>
         <v>2.93194921621186</v>
+      </c>
+      <c r="Y2" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S2+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19762,23 +19827,23 @@
         <v>1.70278044608037</v>
       </c>
       <c r="J3" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I3,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I3,T_av-2*t_tr,IF(S_task&gt;0,S_task*D3-(0),1000000000)))</f>
         <v>1.70278044608037</v>
       </c>
       <c r="K3" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J3)-t_tr&gt;0.000001,T_av-(t_tr+J3)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J3)-t_tr&gt;0.000001,T_av-(t_tr+J3)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D3-(J3),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L3" s="12" t="n">
-        <f aca="false">IF(K3,MAX(0,MIN(I3,T_av-(t_tr+J3+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K3,MAX(0,MIN(I3,T_av-(t_tr+J3+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D3-(J3),1000000000))),0)</f>
         <v>0.206894135630823</v>
       </c>
       <c r="M3" s="19" t="b">
-        <f aca="false">AND(K3,L3&gt;0,T_av-(t_tr+J3+2*t_tr+t_ch+L3)-t_tr&gt;0.000001,T_av-(t_tr+J3+2*t_tr+t_ch+L3)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K3,L3&gt;0,T_av-(t_tr+J3+2*t_tr+t_ch+L3)-t_tr&gt;0.000001,T_av-(t_tr+J3+2*t_tr+t_ch+L3)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D3-(J3+L3),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N3" s="12" t="n">
-        <f aca="false">IF(M3,MAX(0,MIN(I3,T_av-((t_tr+J3+2*t_tr+t_ch+L3)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M3,MAX(0,MIN(I3,T_av-((t_tr+J3+2*t_tr+t_ch+L3)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D3-(J3+L3),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O3" s="14" t="n">
@@ -19806,11 +19871,11 @@
         <v>6.7658882552001</v>
       </c>
       <c r="U3" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S3+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D3&lt;T_av-2*t_tr-Y3*t_refuel_h),MAX(0,(S_task*D3*S3+2*t_tr*Q_tr)/tank_D-1),Y3)</f>
         <v>0.0843279358780533</v>
       </c>
       <c r="V3" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U3*t_refuel_h)/D3</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D3&lt;T_av-2*t_tr-Y3*t_refuel_h),S_task,(T_av-2*t_tr-Y3*t_refuel_h)/D3)</f>
         <v>3.43646625603563</v>
       </c>
       <c r="W3" s="12" t="n">
@@ -19820,6 +19885,10 @@
       <c r="X3" s="11" t="n">
         <f aca="false">T3/D3</f>
         <v>3.22144910568908</v>
+      </c>
+      <c r="Y3" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S3+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.0843279358780533</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19860,23 +19929,23 @@
         <v>1.42057276129</v>
       </c>
       <c r="J4" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I4,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I4,T_av-2*t_tr,IF(S_task&gt;0,S_task*D4-(0),1000000000)))</f>
         <v>1.42057276129</v>
       </c>
       <c r="K4" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J4)-t_tr&gt;0.000001,T_av-(t_tr+J4)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J4)-t_tr&gt;0.000001,T_av-(t_tr+J4)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D4-(J4),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L4" s="12" t="n">
-        <f aca="false">IF(K4,MAX(0,MIN(I4,T_av-(t_tr+J4+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K4,MAX(0,MIN(I4,T_av-(t_tr+J4+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D4-(J4),1000000000))),0)</f>
         <v>0.489101820421197</v>
       </c>
       <c r="M4" s="19" t="b">
-        <f aca="false">AND(K4,L4&gt;0,T_av-(t_tr+J4+2*t_tr+t_ch+L4)-t_tr&gt;0.000001,T_av-(t_tr+J4+2*t_tr+t_ch+L4)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K4,L4&gt;0,T_av-(t_tr+J4+2*t_tr+t_ch+L4)-t_tr&gt;0.000001,T_av-(t_tr+J4+2*t_tr+t_ch+L4)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D4-(J4+L4),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N4" s="12" t="n">
-        <f aca="false">IF(M4,MAX(0,MIN(I4,T_av-((t_tr+J4+2*t_tr+t_ch+L4)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M4,MAX(0,MIN(I4,T_av-((t_tr+J4+2*t_tr+t_ch+L4)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D4-(J4+L4),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O4" s="14" t="n">
@@ -19904,11 +19973,11 @@
         <v>6.13630240407866</v>
       </c>
       <c r="U4" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S4+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D4&lt;T_av-2*t_tr-Y4*t_refuel_h),MAX(0,(S_task*D4*S4+2*t_tr*Q_tr)/tank_D-1),Y4)</f>
         <v>0.193968051029966</v>
       </c>
       <c r="V4" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U4*t_refuel_h)/D4</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D4&lt;T_av-2*t_tr-Y4*t_refuel_h),S_task,(T_av-2*t_tr-Y4*t_refuel_h)/D4)</f>
         <v>4.0192859947148</v>
       </c>
       <c r="W4" s="12" t="n">
@@ -19918,6 +19987,10 @@
       <c r="X4" s="11" t="n">
         <f aca="false">T4/D4</f>
         <v>3.42500147104832</v>
+      </c>
+      <c r="Y4" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S4+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.193968051029966</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19958,23 +20031,23 @@
         <v>1.66452950288524</v>
       </c>
       <c r="J5" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I5,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I5,T_av-2*t_tr,IF(S_task&gt;0,S_task*D5-(0),1000000000)))</f>
         <v>1.66452950288524</v>
       </c>
       <c r="K5" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J5)-t_tr&gt;0.000001,T_av-(t_tr+J5)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J5)-t_tr&gt;0.000001,T_av-(t_tr+J5)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D5-(J5),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L5" s="12" t="n">
-        <f aca="false">IF(K5,MAX(0,MIN(I5,T_av-(t_tr+J5+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K5,MAX(0,MIN(I5,T_av-(t_tr+J5+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D5-(J5),1000000000))),0)</f>
         <v>0.245145078825958</v>
       </c>
       <c r="M5" s="19" t="b">
-        <f aca="false">AND(K5,L5&gt;0,T_av-(t_tr+J5+2*t_tr+t_ch+L5)-t_tr&gt;0.000001,T_av-(t_tr+J5+2*t_tr+t_ch+L5)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K5,L5&gt;0,T_av-(t_tr+J5+2*t_tr+t_ch+L5)-t_tr&gt;0.000001,T_av-(t_tr+J5+2*t_tr+t_ch+L5)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D5-(J5+L5),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N5" s="12" t="n">
-        <f aca="false">IF(M5,MAX(0,MIN(I5,T_av-((t_tr+J5+2*t_tr+t_ch+L5)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M5,MAX(0,MIN(I5,T_av-((t_tr+J5+2*t_tr+t_ch+L5)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D5-(J5+L5),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O5" s="14" t="n">
@@ -20002,11 +20075,11 @@
         <v>6.63332867459959</v>
       </c>
       <c r="U5" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S5+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D5&lt;T_av-2*t_tr-Y5*t_refuel_h),MAX(0,(S_task*D5*S5+2*t_tr*Q_tr)/tank_D-1),Y5)</f>
         <v>0.105683000121053</v>
       </c>
       <c r="V5" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U5*t_refuel_h)/D5</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D5&lt;T_av-2*t_tr-Y5*t_refuel_h),S_task,(T_av-2*t_tr-Y5*t_refuel_h)/D5)</f>
         <v>2.81453112833609</v>
       </c>
       <c r="W5" s="12" t="n">
@@ -20016,6 +20089,10 @@
       <c r="X5" s="11" t="n">
         <f aca="false">T5/D5</f>
         <v>2.58788357474279</v>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S5+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.105683000121053</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20056,23 +20133,23 @@
         <v>1.33507701895421</v>
       </c>
       <c r="J6" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I6,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I6,T_av-2*t_tr,IF(S_task&gt;0,S_task*D6-(0),1000000000)))</f>
         <v>1.33507701895421</v>
       </c>
       <c r="K6" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J6)-t_tr&gt;0.000001,T_av-(t_tr+J6)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J6)-t_tr&gt;0.000001,T_av-(t_tr+J6)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D6-(J6),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L6" s="12" t="n">
-        <f aca="false">IF(K6,MAX(0,MIN(I6,T_av-(t_tr+J6+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K6,MAX(0,MIN(I6,T_av-(t_tr+J6+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D6-(J6),1000000000))),0)</f>
         <v>0.574597562756988</v>
       </c>
       <c r="M6" s="19" t="b">
-        <f aca="false">AND(K6,L6&gt;0,T_av-(t_tr+J6+2*t_tr+t_ch+L6)-t_tr&gt;0.000001,T_av-(t_tr+J6+2*t_tr+t_ch+L6)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K6,L6&gt;0,T_av-(t_tr+J6+2*t_tr+t_ch+L6)-t_tr&gt;0.000001,T_av-(t_tr+J6+2*t_tr+t_ch+L6)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D6-(J6+L6),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <f aca="false">IF(M6,MAX(0,MIN(I6,T_av-((t_tr+J6+2*t_tr+t_ch+L6)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M6,MAX(0,MIN(I6,T_av-((t_tr+J6+2*t_tr+t_ch+L6)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D6-(J6+L6),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O6" s="14" t="n">
@@ -20100,11 +20177,11 @@
         <v>5.87051055379391</v>
       </c>
       <c r="U6" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S6+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D6&lt;T_av-2*t_tr-Y6*t_refuel_h),MAX(0,(S_task*D6*S6+2*t_tr*Q_tr)/tank_D-1),Y6)</f>
         <v>0.247314452820456</v>
       </c>
       <c r="V6" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U6*t_refuel_h)/D6</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D6&lt;T_av-2*t_tr-Y6*t_refuel_h),S_task,(T_av-2*t_tr-Y6*t_refuel_h)/D6)</f>
         <v>3.42482581616789</v>
       </c>
       <c r="W6" s="12" t="n">
@@ -20114,6 +20191,10 @@
       <c r="X6" s="11" t="n">
         <f aca="false">T6/D6</f>
         <v>2.79513202999218</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S6+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.247314452820456</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20154,23 +20235,23 @@
         <v>1.10762154109937</v>
       </c>
       <c r="J7" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I7,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I7,T_av-2*t_tr,IF(S_task&gt;0,S_task*D7-(0),1000000000)))</f>
         <v>1.10762154109937</v>
       </c>
       <c r="K7" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J7)-t_tr&gt;0.000001,T_av-(t_tr+J7)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J7)-t_tr&gt;0.000001,T_av-(t_tr+J7)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D7-(J7),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L7" s="12" t="n">
-        <f aca="false">IF(K7,MAX(0,MIN(I7,T_av-(t_tr+J7+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K7,MAX(0,MIN(I7,T_av-(t_tr+J7+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D7-(J7),1000000000))),0)</f>
         <v>0.802053040611822</v>
       </c>
       <c r="M7" s="19" t="b">
-        <f aca="false">AND(K7,L7&gt;0,T_av-(t_tr+J7+2*t_tr+t_ch+L7)-t_tr&gt;0.000001,T_av-(t_tr+J7+2*t_tr+t_ch+L7)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K7,L7&gt;0,T_av-(t_tr+J7+2*t_tr+t_ch+L7)-t_tr&gt;0.000001,T_av-(t_tr+J7+2*t_tr+t_ch+L7)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D7-(J7+L7),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <f aca="false">IF(M7,MAX(0,MIN(I7,T_av-((t_tr+J7+2*t_tr+t_ch+L7)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M7,MAX(0,MIN(I7,T_av-((t_tr+J7+2*t_tr+t_ch+L7)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D7-(J7+L7),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O7" s="14" t="n">
@@ -20198,11 +20279,11 @@
         <v>5.24075699973565</v>
       </c>
       <c r="U7" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S7+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D7&lt;T_av-2*t_tr-Y7*t_refuel_h),MAX(0,(S_task*D7*S7+2*t_tr*Q_tr)/tank_D-1),Y7)</f>
         <v>0.39530937996856</v>
       </c>
       <c r="V7" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U7*t_refuel_h)/D7</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D7&lt;T_av-2*t_tr-Y7*t_refuel_h),S_task,(T_av-2*t_tr-Y7*t_refuel_h)/D7)</f>
         <v>4.0024290757825</v>
       </c>
       <c r="W7" s="12" t="n">
@@ -20212,6 +20293,10 @@
       <c r="X7" s="11" t="n">
         <f aca="false">T7/D7</f>
         <v>2.92514925952325</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S7+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.39530937996856</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20252,23 +20337,23 @@
         <v>1.34426913507301</v>
       </c>
       <c r="J8" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I8,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I8,T_av-2*t_tr,IF(S_task&gt;0,S_task*D8-(0),1000000000)))</f>
         <v>1.34426913507301</v>
       </c>
       <c r="K8" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J8)-t_tr&gt;0.000001,T_av-(t_tr+J8)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J8)-t_tr&gt;0.000001,T_av-(t_tr+J8)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D8-(J8),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L8" s="12" t="n">
-        <f aca="false">IF(K8,MAX(0,MIN(I8,T_av-(t_tr+J8+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K8,MAX(0,MIN(I8,T_av-(t_tr+J8+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D8-(J8),1000000000))),0)</f>
         <v>0.565405446638186</v>
       </c>
       <c r="M8" s="19" t="b">
-        <f aca="false">AND(K8,L8&gt;0,T_av-(t_tr+J8+2*t_tr+t_ch+L8)-t_tr&gt;0.000001,T_av-(t_tr+J8+2*t_tr+t_ch+L8)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K8,L8&gt;0,T_av-(t_tr+J8+2*t_tr+t_ch+L8)-t_tr&gt;0.000001,T_av-(t_tr+J8+2*t_tr+t_ch+L8)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D8-(J8+L8),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <f aca="false">IF(M8,MAX(0,MIN(I8,T_av-((t_tr+J8+2*t_tr+t_ch+L8)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M8,MAX(0,MIN(I8,T_av-((t_tr+J8+2*t_tr+t_ch+L8)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D8-(J8+L8),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O8" s="14" t="n">
@@ -20296,11 +20381,11 @@
         <v>5.82530017470435</v>
       </c>
       <c r="U8" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S8+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D8&lt;T_av-2*t_tr-Y8*t_refuel_h),MAX(0,(S_task*D8*S8+2*t_tr*Q_tr)/tank_D-1),Y8)</f>
         <v>0.256872959864435</v>
       </c>
       <c r="V8" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U8*t_refuel_h)/D8</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D8&lt;T_av-2*t_tr-Y8*t_refuel_h),S_task,(T_av-2*t_tr-Y8*t_refuel_h)/D8)</f>
         <v>2.80568348865141</v>
       </c>
       <c r="W8" s="12" t="n">
@@ -20310,6 +20395,10 @@
       <c r="X8" s="11" t="n">
         <f aca="false">T8/D8</f>
         <v>2.27264460719244</v>
+      </c>
+      <c r="Y8" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S8+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.256872959864435</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20350,23 +20439,23 @@
         <v>1.07240749936394</v>
       </c>
       <c r="J9" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I9,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I9,T_av-2*t_tr,IF(S_task&gt;0,S_task*D9-(0),1000000000)))</f>
         <v>1.07240749936394</v>
       </c>
       <c r="K9" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J9)-t_tr&gt;0.000001,T_av-(t_tr+J9)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J9)-t_tr&gt;0.000001,T_av-(t_tr+J9)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D9-(J9),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L9" s="12" t="n">
-        <f aca="false">IF(K9,MAX(0,MIN(I9,T_av-(t_tr+J9+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K9,MAX(0,MIN(I9,T_av-(t_tr+J9+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D9-(J9),1000000000))),0)</f>
         <v>0.837267082347256</v>
       </c>
       <c r="M9" s="19" t="b">
-        <f aca="false">AND(K9,L9&gt;0,T_av-(t_tr+J9+2*t_tr+t_ch+L9)-t_tr&gt;0.000001,T_av-(t_tr+J9+2*t_tr+t_ch+L9)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K9,L9&gt;0,T_av-(t_tr+J9+2*t_tr+t_ch+L9)-t_tr&gt;0.000001,T_av-(t_tr+J9+2*t_tr+t_ch+L9)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D9-(J9+L9),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <f aca="false">IF(M9,MAX(0,MIN(I9,T_av-((t_tr+J9+2*t_tr+t_ch+L9)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M9,MAX(0,MIN(I9,T_av-((t_tr+J9+2*t_tr+t_ch+L9)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D9-(J9+L9),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O9" s="14" t="n">
@@ -20394,11 +20483,11 @@
         <v>5.0651794403029</v>
       </c>
       <c r="U9" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S9+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D9&lt;T_av-2*t_tr-Y9*t_refuel_h),MAX(0,(S_task*D9*S9+2*t_tr*Q_tr)/tank_D-1),Y9)</f>
         <v>0.443131216193827</v>
       </c>
       <c r="V9" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U9*t_refuel_h)/D9</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D9&lt;T_av-2*t_tr-Y9*t_refuel_h),S_task,(T_av-2*t_tr-Y9*t_refuel_h)/D9)</f>
         <v>3.41084065161621</v>
       </c>
       <c r="W9" s="12" t="n">
@@ -20408,6 +20497,10 @@
       <c r="X9" s="11" t="n">
         <f aca="false">T9/D9</f>
         <v>2.41168892577814</v>
+      </c>
+      <c r="Y9" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S9+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.443131216193827</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20448,23 +20541,23 @@
         <v>2.09024355285488</v>
       </c>
       <c r="J10" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I10,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I10,T_av-2*t_tr,IF(S_task&gt;0,S_task*D10-(0),1000000000)))</f>
         <v>2.09024355285488</v>
       </c>
       <c r="K10" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J10)-t_tr&gt;0.000001,T_av-(t_tr+J10)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J10)-t_tr&gt;0.000001,T_av-(t_tr+J10)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D10-(J10),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="L10" s="12" t="n">
-        <f aca="false">IF(K10,MAX(0,MIN(I10,T_av-(t_tr+J10+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K10,MAX(0,MIN(I10,T_av-(t_tr+J10+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D10-(J10),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="M10" s="19" t="b">
-        <f aca="false">AND(K10,L10&gt;0,T_av-(t_tr+J10+2*t_tr+t_ch+L10)-t_tr&gt;0.000001,T_av-(t_tr+J10+2*t_tr+t_ch+L10)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K10,L10&gt;0,T_av-(t_tr+J10+2*t_tr+t_ch+L10)-t_tr&gt;0.000001,T_av-(t_tr+J10+2*t_tr+t_ch+L10)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D10-(J10+L10),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <f aca="false">IF(M10,MAX(0,MIN(I10,T_av-((t_tr+J10+2*t_tr+t_ch+L10)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M10,MAX(0,MIN(I10,T_av-((t_tr+J10+2*t_tr+t_ch+L10)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D10-(J10+L10),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O10" s="14" t="n">
@@ -20492,11 +20585,11 @@
         <v>7.43372448745445</v>
       </c>
       <c r="U10" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S10+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D10&lt;T_av-2*t_tr-Y10*t_refuel_h),MAX(0,(S_task*D10*S10+2*t_tr*Q_tr)/tank_D-1),Y10)</f>
         <v>0</v>
       </c>
       <c r="V10" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U10*t_refuel_h)/D10</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D10&lt;T_av-2*t_tr-Y10*t_refuel_h),S_task,(T_av-2*t_tr-Y10*t_refuel_h)/D10)</f>
         <v>1.54393672269514</v>
       </c>
       <c r="W10" s="12" t="n">
@@ -20506,6 +20599,10 @@
       <c r="X10" s="11" t="n">
         <f aca="false">T10/D10</f>
         <v>1.5874127337595</v>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S10+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20546,23 +20643,23 @@
         <v>1.60900518211438</v>
       </c>
       <c r="J11" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I11,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I11,T_av-2*t_tr,IF(S_task&gt;0,S_task*D11-(0),1000000000)))</f>
         <v>1.60900518211438</v>
       </c>
       <c r="K11" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J11)-t_tr&gt;0.000001,T_av-(t_tr+J11)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J11)-t_tr&gt;0.000001,T_av-(t_tr+J11)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D11-(J11),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L11" s="12" t="n">
-        <f aca="false">IF(K11,MAX(0,MIN(I11,T_av-(t_tr+J11+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K11,MAX(0,MIN(I11,T_av-(t_tr+J11+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D11-(J11),1000000000))),0)</f>
         <v>0.300669399596819</v>
       </c>
       <c r="M11" s="19" t="b">
-        <f aca="false">AND(K11,L11&gt;0,T_av-(t_tr+J11+2*t_tr+t_ch+L11)-t_tr&gt;0.000001,T_av-(t_tr+J11+2*t_tr+t_ch+L11)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K11,L11&gt;0,T_av-(t_tr+J11+2*t_tr+t_ch+L11)-t_tr&gt;0.000001,T_av-(t_tr+J11+2*t_tr+t_ch+L11)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D11-(J11+L11),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <f aca="false">IF(M11,MAX(0,MIN(I11,T_av-((t_tr+J11+2*t_tr+t_ch+L11)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M11,MAX(0,MIN(I11,T_av-((t_tr+J11+2*t_tr+t_ch+L11)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D11-(J11+L11),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O11" s="14" t="n">
@@ -20590,11 +20687,11 @@
         <v>6.53614108394619</v>
       </c>
       <c r="U11" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S11+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D11&lt;T_av-2*t_tr-Y11*t_refuel_h),MAX(0,(S_task*D11*S11+2*t_tr*Q_tr)/tank_D-1),Y11)</f>
         <v>0.12189005040192</v>
       </c>
       <c r="V11" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U11*t_refuel_h)/D11</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D11&lt;T_av-2*t_tr-Y11*t_refuel_h),S_task,(T_av-2*t_tr-Y11*t_refuel_h)/D11)</f>
         <v>2.25269036346385</v>
       </c>
       <c r="W11" s="12" t="n">
@@ -20604,6 +20701,10 @@
       <c r="X11" s="11" t="n">
         <f aca="false">T11/D11</f>
         <v>2.04162724686769</v>
+      </c>
+      <c r="Y11" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S11+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.12189005040192</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20644,23 +20745,23 @@
         <v>1.36998760581607</v>
       </c>
       <c r="J12" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I12,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I12,T_av-2*t_tr,IF(S_task&gt;0,S_task*D12-(0),1000000000)))</f>
         <v>1.36998760581607</v>
       </c>
       <c r="K12" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J12)-t_tr&gt;0.000001,T_av-(t_tr+J12)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J12)-t_tr&gt;0.000001,T_av-(t_tr+J12)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D12-(J12),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L12" s="12" t="n">
-        <f aca="false">IF(K12,MAX(0,MIN(I12,T_av-(t_tr+J12+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K12,MAX(0,MIN(I12,T_av-(t_tr+J12+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D12-(J12),1000000000))),0)</f>
         <v>0.539686975895129</v>
       </c>
       <c r="M12" s="19" t="b">
-        <f aca="false">AND(K12,L12&gt;0,T_av-(t_tr+J12+2*t_tr+t_ch+L12)-t_tr&gt;0.000001,T_av-(t_tr+J12+2*t_tr+t_ch+L12)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K12,L12&gt;0,T_av-(t_tr+J12+2*t_tr+t_ch+L12)-t_tr&gt;0.000001,T_av-(t_tr+J12+2*t_tr+t_ch+L12)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D12-(J12+L12),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <f aca="false">IF(M12,MAX(0,MIN(I12,T_av-((t_tr+J12+2*t_tr+t_ch+L12)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M12,MAX(0,MIN(I12,T_av-((t_tr+J12+2*t_tr+t_ch+L12)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D12-(J12+L12),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O12" s="14" t="n">
@@ -20688,11 +20789,11 @@
         <v>5.99162627407306</v>
       </c>
       <c r="U12" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S12+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D12&lt;T_av-2*t_tr-Y12*t_refuel_h),MAX(0,(S_task*D12*S12+2*t_tr*Q_tr)/tank_D-1),Y12)</f>
         <v>0.222418656347106</v>
       </c>
       <c r="V12" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U12*t_refuel_h)/D12</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D12&lt;T_av-2*t_tr-Y12*t_refuel_h),S_task,(T_av-2*t_tr-Y12*t_refuel_h)/D12)</f>
         <v>2.92468724503303</v>
       </c>
       <c r="W12" s="12" t="n">
@@ -20702,6 +20803,10 @@
       <c r="X12" s="11" t="n">
         <f aca="false">T12/D12</f>
         <v>2.43493123596411</v>
+      </c>
+      <c r="Y12" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S12+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.222418656347106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20742,23 +20847,23 @@
         <v>1.56693156616922</v>
       </c>
       <c r="J13" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I13,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I13,T_av-2*t_tr,IF(S_task&gt;0,S_task*D13-(0),1000000000)))</f>
         <v>1.56693156616922</v>
       </c>
       <c r="K13" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J13)-t_tr&gt;0.000001,T_av-(t_tr+J13)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J13)-t_tr&gt;0.000001,T_av-(t_tr+J13)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D13-(J13),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L13" s="12" t="n">
-        <f aca="false">IF(K13,MAX(0,MIN(I13,T_av-(t_tr+J13+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K13,MAX(0,MIN(I13,T_av-(t_tr+J13+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D13-(J13),1000000000))),0)</f>
         <v>0.342743015541977</v>
       </c>
       <c r="M13" s="19" t="b">
-        <f aca="false">AND(K13,L13&gt;0,T_av-(t_tr+J13+2*t_tr+t_ch+L13)-t_tr&gt;0.000001,T_av-(t_tr+J13+2*t_tr+t_ch+L13)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K13,L13&gt;0,T_av-(t_tr+J13+2*t_tr+t_ch+L13)-t_tr&gt;0.000001,T_av-(t_tr+J13+2*t_tr+t_ch+L13)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D13-(J13+L13),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <f aca="false">IF(M13,MAX(0,MIN(I13,T_av-((t_tr+J13+2*t_tr+t_ch+L13)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M13,MAX(0,MIN(I13,T_av-((t_tr+J13+2*t_tr+t_ch+L13)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D13-(J13+L13),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O13" s="14" t="n">
@@ -20786,11 +20891,11 @@
         <v>6.42274307329686</v>
       </c>
       <c r="U13" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S13+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D13&lt;T_av-2*t_tr-Y13*t_refuel_h),MAX(0,(S_task*D13*S13+2*t_tr*Q_tr)/tank_D-1),Y13)</f>
         <v>0.141420379733841</v>
       </c>
       <c r="V13" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U13*t_refuel_h)/D13</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D13&lt;T_av-2*t_tr-Y13*t_refuel_h),S_task,(T_av-2*t_tr-Y13*t_refuel_h)/D13)</f>
         <v>1.53940684311765</v>
       </c>
       <c r="W13" s="12" t="n">
@@ -20800,6 +20905,10 @@
       <c r="X13" s="11" t="n">
         <f aca="false">T13/D13</f>
         <v>1.3715256944784</v>
+      </c>
+      <c r="Y13" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S13+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.141420379733841</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20840,23 +20949,23 @@
         <v>1.19917401208893</v>
       </c>
       <c r="J14" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I14,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I14,T_av-2*t_tr,IF(S_task&gt;0,S_task*D14-(0),1000000000)))</f>
         <v>1.19917401208893</v>
       </c>
       <c r="K14" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J14)-t_tr&gt;0.000001,T_av-(t_tr+J14)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J14)-t_tr&gt;0.000001,T_av-(t_tr+J14)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D14-(J14),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L14" s="12" t="n">
-        <f aca="false">IF(K14,MAX(0,MIN(I14,T_av-(t_tr+J14+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K14,MAX(0,MIN(I14,T_av-(t_tr+J14+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D14-(J14),1000000000))),0)</f>
         <v>0.710500569622265</v>
       </c>
       <c r="M14" s="19" t="b">
-        <f aca="false">AND(K14,L14&gt;0,T_av-(t_tr+J14+2*t_tr+t_ch+L14)-t_tr&gt;0.000001,T_av-(t_tr+J14+2*t_tr+t_ch+L14)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K14,L14&gt;0,T_av-(t_tr+J14+2*t_tr+t_ch+L14)-t_tr&gt;0.000001,T_av-(t_tr+J14+2*t_tr+t_ch+L14)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D14-(J14+L14),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <f aca="false">IF(M14,MAX(0,MIN(I14,T_av-((t_tr+J14+2*t_tr+t_ch+L14)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M14,MAX(0,MIN(I14,T_av-((t_tr+J14+2*t_tr+t_ch+L14)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D14-(J14+L14),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O14" s="14" t="n">
@@ -20884,11 +20993,11 @@
         <v>5.52044606059915</v>
       </c>
       <c r="U14" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S14+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D14&lt;T_av-2*t_tr-Y14*t_refuel_h),MAX(0,(S_task*D14*S14+2*t_tr*Q_tr)/tank_D-1),Y14)</f>
         <v>0.325413208983113</v>
       </c>
       <c r="V14" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U14*t_refuel_h)/D14</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D14&lt;T_av-2*t_tr-Y14*t_refuel_h),S_task,(T_av-2*t_tr-Y14*t_refuel_h)/D14)</f>
         <v>2.24315449771543</v>
       </c>
       <c r="W14" s="12" t="n">
@@ -20898,6 +21007,10 @@
       <c r="X14" s="11" t="n">
         <f aca="false">T14/D14</f>
         <v>1.72436502630968</v>
+      </c>
+      <c r="Y14" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S14+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.325413208983113</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20938,23 +21051,23 @@
         <v>1.02191462454598</v>
       </c>
       <c r="J15" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I15,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I15,T_av-2*t_tr,IF(S_task&gt;0,S_task*D15-(0),1000000000)))</f>
         <v>1.02191462454598</v>
       </c>
       <c r="K15" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J15)-t_tr&gt;0.000001,T_av-(t_tr+J15)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J15)-t_tr&gt;0.000001,T_av-(t_tr+J15)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D15-(J15),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L15" s="12" t="n">
-        <f aca="false">IF(K15,MAX(0,MIN(I15,T_av-(t_tr+J15+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K15,MAX(0,MIN(I15,T_av-(t_tr+J15+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D15-(J15),1000000000))),0)</f>
         <v>0.887759957165217</v>
       </c>
       <c r="M15" s="19" t="b">
-        <f aca="false">AND(K15,L15&gt;0,T_av-(t_tr+J15+2*t_tr+t_ch+L15)-t_tr&gt;0.000001,T_av-(t_tr+J15+2*t_tr+t_ch+L15)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K15,L15&gt;0,T_av-(t_tr+J15+2*t_tr+t_ch+L15)-t_tr&gt;0.000001,T_av-(t_tr+J15+2*t_tr+t_ch+L15)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D15-(J15+L15),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <f aca="false">IF(M15,MAX(0,MIN(I15,T_av-((t_tr+J15+2*t_tr+t_ch+L15)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M15,MAX(0,MIN(I15,T_av-((t_tr+J15+2*t_tr+t_ch+L15)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D15-(J15+L15),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O15" s="14" t="n">
@@ -20982,11 +21095,11 @@
         <v>5.00378946246266</v>
       </c>
       <c r="U15" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S15+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D15&lt;T_av-2*t_tr-Y15*t_refuel_h),MAX(0,(S_task*D15*S15+2*t_tr*Q_tr)/tank_D-1),Y15)</f>
         <v>0.460643779222216</v>
       </c>
       <c r="V15" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U15*t_refuel_h)/D15</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D15&lt;T_av-2*t_tr-Y15*t_refuel_h),S_task,(T_av-2*t_tr-Y15*t_refuel_h)/D15)</f>
         <v>2.91016543326575</v>
       </c>
       <c r="W15" s="12" t="n">
@@ -20996,6 +21109,10 @@
       <c r="X15" s="11" t="n">
         <f aca="false">T15/D15</f>
         <v>2.03348518465854</v>
+      </c>
+      <c r="Y15" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S15+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.460643779222216</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21036,23 +21153,23 @@
         <v>1.25879711358138</v>
       </c>
       <c r="J16" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I16,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I16,T_av-2*t_tr,IF(S_task&gt;0,S_task*D16-(0),1000000000)))</f>
         <v>1.25879711358138</v>
       </c>
       <c r="K16" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J16)-t_tr&gt;0.000001,T_av-(t_tr+J16)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J16)-t_tr&gt;0.000001,T_av-(t_tr+J16)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D16-(J16),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L16" s="12" t="n">
-        <f aca="false">IF(K16,MAX(0,MIN(I16,T_av-(t_tr+J16+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K16,MAX(0,MIN(I16,T_av-(t_tr+J16+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D16-(J16),1000000000))),0)</f>
         <v>0.650877468129815</v>
       </c>
       <c r="M16" s="19" t="b">
-        <f aca="false">AND(K16,L16&gt;0,T_av-(t_tr+J16+2*t_tr+t_ch+L16)-t_tr&gt;0.000001,T_av-(t_tr+J16+2*t_tr+t_ch+L16)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K16,L16&gt;0,T_av-(t_tr+J16+2*t_tr+t_ch+L16)-t_tr&gt;0.000001,T_av-(t_tr+J16+2*t_tr+t_ch+L16)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D16-(J16+L16),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <f aca="false">IF(M16,MAX(0,MIN(I16,T_av-((t_tr+J16+2*t_tr+t_ch+L16)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M16,MAX(0,MIN(I16,T_av-((t_tr+J16+2*t_tr+t_ch+L16)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D16-(J16+L16),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O16" s="14" t="n">
@@ -21080,11 +21197,11 @@
         <v>5.66893785751517</v>
       </c>
       <c r="U16" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S16+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D16&lt;T_av-2*t_tr-Y16*t_refuel_h),MAX(0,(S_task*D16*S16+2*t_tr*Q_tr)/tank_D-1),Y16)</f>
         <v>0.291107002761894</v>
       </c>
       <c r="V16" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U16*t_refuel_h)/D16</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D16&lt;T_av-2*t_tr-Y16*t_refuel_h),S_task,(T_av-2*t_tr-Y16*t_refuel_h)/D16)</f>
         <v>1.53461218496475</v>
       </c>
       <c r="W16" s="12" t="n">
@@ -21094,6 +21211,10 @@
       <c r="X16" s="11" t="n">
         <f aca="false">T16/D16</f>
         <v>1.21055658668786</v>
+      </c>
+      <c r="Y16" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S16+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.291107002761894</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21134,23 +21255,23 @@
         <v>0.960514453982853</v>
       </c>
       <c r="J17" s="12" t="n">
-        <f aca="false">MAX(0,MIN(I17,T_av-2*t_tr))</f>
+        <f aca="false">MAX(0,MIN(I17,T_av-2*t_tr,IF(S_task&gt;0,S_task*D17-(0),1000000000)))</f>
         <v>0.960514453982853</v>
       </c>
       <c r="K17" s="19" t="b">
-        <f aca="false">AND(T_av-(t_tr+J17)-t_tr&gt;0.000001,T_av-(t_tr+J17)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(T_av-(t_tr+J17)-t_tr&gt;0.000001,T_av-(t_tr+J17)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D17-(J17),1000000000)&gt;0.000001)</f>
         <v>1</v>
       </c>
       <c r="L17" s="12" t="n">
-        <f aca="false">IF(K17,MAX(0,MIN(I17,T_av-(t_tr+J17+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(K17,MAX(0,MIN(I17,T_av-(t_tr+J17+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D17-(J17),1000000000))),0)</f>
         <v>0.949160127728342</v>
       </c>
       <c r="M17" s="19" t="b">
-        <f aca="false">AND(K17,L17&gt;0,T_av-(t_tr+J17+2*t_tr+t_ch+L17)-t_tr&gt;0.000001,T_av-(t_tr+J17+2*t_tr+t_ch+L17)-2*t_tr-t_ch&gt;=0.25)</f>
+        <f aca="false">AND(K17,L17&gt;0,T_av-(t_tr+J17+2*t_tr+t_ch+L17)-t_tr&gt;0.000001,T_av-(t_tr+J17+2*t_tr+t_ch+L17)-2*t_tr-t_ch&gt;=0.25,IF(S_task&gt;0,S_task*D17-(J17+L17),1000000000)&gt;0.000001)</f>
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <f aca="false">IF(M17,MAX(0,MIN(I17,T_av-((t_tr+J17+2*t_tr+t_ch+L17)+2*t_tr+t_ch)-t_tr)),0)</f>
+        <f aca="false">IF(M17,MAX(0,MIN(I17,T_av-((t_tr+J17+2*t_tr+t_ch+L17)+2*t_tr+t_ch)-t_tr,IF(S_task&gt;0,S_task*D17-(J17+L17),1000000000))),0)</f>
         <v>0</v>
       </c>
       <c r="O17" s="14" t="n">
@@ -21178,11 +21299,11 @@
         <v>4.79376181808808</v>
       </c>
       <c r="U17" s="12" t="n">
-        <f aca="false">MAX(0,((T_av-2*t_tr)*S17+2*t_tr*Q_tr)/tank_D-1)</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D17&lt;T_av-2*t_tr-Y17*t_refuel_h),MAX(0,(S_task*D17*S17+2*t_tr*Q_tr)/tank_D-1),Y17)</f>
         <v>0.523950100812087</v>
       </c>
       <c r="V17" s="11" t="n">
-        <f aca="false">(T_av-2*t_tr-U17*t_refuel_h)/D17</f>
+        <f aca="false">IF(AND(S_task&gt;0,S_task*D17&lt;T_av-2*t_tr-Y17*t_refuel_h),S_task,(T_av-2*t_tr-Y17*t_refuel_h)/D17)</f>
         <v>2.2338522583055</v>
       </c>
       <c r="W17" s="12" t="n">
@@ -21192,6 +21313,10 @@
       <c r="X17" s="11" t="n">
         <f aca="false">T17/D17</f>
         <v>1.49737813445326</v>
+      </c>
+      <c r="Y17" s="12" t="n">
+        <f aca="false">MAX(0,((T_av-2*t_tr)*S17+2*t_tr*Q_tr)/tank_D-1)</f>
+        <v>0.523950100812087</v>
       </c>
     </row>
   </sheetData>
@@ -21219,7 +21344,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>376</v>
@@ -22406,7 +22531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
@@ -22982,6 +23107,15 @@
       <c r="E38" s="9" t="s">
         <v>428</v>
       </c>
+      <c r="F38" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G38" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
@@ -22991,16 +23125,28 @@
         <v>402</v>
       </c>
       <c r="C39" s="15" t="n">
-        <f aca="false">$H$3*$E$17</f>
-        <v>0.0525984063679585</v>
-      </c>
-      <c r="D39" s="23" t="n">
-        <f aca="false">Энтропия!B$40</f>
-        <v>0.0892372518366141</v>
-      </c>
-      <c r="E39" s="22" t="n">
-        <f aca="false">(alpha_w*C39+(1-alpha_w)*D39)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.0709178291022863</v>
+        <f aca="false">$H$3</f>
+        <v>0.157795219103876</v>
+      </c>
+      <c r="D39" s="15" t="n">
+        <f aca="false">$E$17</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="E39" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!B$41,Энтропия!B$40)</f>
+        <v>0.085949904613759</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <f aca="false">E39/SUMIF($B$39:$B$48,B39,$E$39:$E$48)</f>
+        <v>0.572888612494277</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <f aca="false">alpha_w*D39+(1-alpha_w)*F39</f>
+        <v>0.453110972913805</v>
+      </c>
+      <c r="H39" s="22" t="n">
+        <f aca="false">C39*G39/SUMIF($B$39:$B$48,B39,$G$39:$G$48)</f>
+        <v>0.0714987452493041</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23011,16 +23157,28 @@
         <v>402</v>
       </c>
       <c r="C40" s="15" t="n">
-        <f aca="false">$H$3*$E$18</f>
-        <v>0.105196812735917</v>
-      </c>
-      <c r="D40" s="23" t="n">
-        <f aca="false">Энтропия!C$40</f>
-        <v>0.0672206876756696</v>
-      </c>
-      <c r="E40" s="22" t="n">
-        <f aca="false">(alpha_w*C40+(1-alpha_w)*D40)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.0862087502057934</v>
+        <f aca="false">$H$3</f>
+        <v>0.157795219103876</v>
+      </c>
+      <c r="D40" s="15" t="n">
+        <f aca="false">$E$18</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E40" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!C$41,Энтропия!C$40)</f>
+        <v>0.0640790935880819</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <f aca="false">E40/SUMIF($B$39:$B$48,B40,$E$39:$E$48)</f>
+        <v>0.427111387505723</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <f aca="false">alpha_w*D40+(1-alpha_w)*F40</f>
+        <v>0.546889027086195</v>
+      </c>
+      <c r="H40" s="22" t="n">
+        <f aca="false">C40*G40/SUMIF($B$39:$B$48,B40,$G$39:$G$48)</f>
+        <v>0.0862964738545715</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23031,16 +23189,28 @@
         <v>403</v>
       </c>
       <c r="C41" s="15" t="n">
-        <f aca="false">$H$4*$F$21</f>
-        <v>0.160775452522787</v>
-      </c>
-      <c r="D41" s="23" t="n">
-        <f aca="false">Энтропия!D$40</f>
-        <v>0.148411837530127</v>
-      </c>
-      <c r="E41" s="22" t="n">
-        <f aca="false">(alpha_w*C41+(1-alpha_w)*D41)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.154593645026457</v>
+        <f aca="false">$H$4</f>
+        <v>0.297944991396023</v>
+      </c>
+      <c r="D41" s="15" t="n">
+        <f aca="false">$F$21</f>
+        <v>0.539614550221075</v>
+      </c>
+      <c r="E41" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!D$41,Энтропия!D$40)</f>
+        <v>0.149421177951929</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <f aca="false">E41/SUMIF($B$39:$B$48,B41,$E$39:$E$48)</f>
+        <v>0.391565980104701</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <f aca="false">alpha_w*D41+(1-alpha_w)*F41</f>
+        <v>0.465590265162888</v>
+      </c>
+      <c r="H41" s="22" t="n">
+        <f aca="false">C41*G41/SUMIF($B$39:$B$48,B41,$G$39:$G$48)</f>
+        <v>0.138720287548029</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23051,16 +23221,28 @@
         <v>403</v>
       </c>
       <c r="C42" s="15" t="n">
-        <f aca="false">$H$4*$F$22</f>
-        <v>0.0486913976001771</v>
-      </c>
-      <c r="D42" s="23" t="n">
-        <f aca="false">Энтропия!E$40</f>
-        <v>0.179408868955857</v>
-      </c>
-      <c r="E42" s="22" t="n">
-        <f aca="false">(alpha_w*C42+(1-alpha_w)*D42)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.114050133278017</v>
+        <f aca="false">$H$4</f>
+        <v>0.297944991396023</v>
+      </c>
+      <c r="D42" s="15" t="n">
+        <f aca="false">$F$22</f>
+        <v>0.163424118566428</v>
+      </c>
+      <c r="E42" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!E$41,Энтропия!E$40)</f>
+        <v>0.197163284230661</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <f aca="false">E42/SUMIF($B$39:$B$48,B42,$E$39:$E$48)</f>
+        <v>0.516676656472869</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <f aca="false">alpha_w*D42+(1-alpha_w)*F42</f>
+        <v>0.340050387519649</v>
+      </c>
+      <c r="H42" s="22" t="n">
+        <f aca="false">C42*G42/SUMIF($B$39:$B$48,B42,$G$39:$G$48)</f>
+        <v>0.101316309783756</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23071,16 +23253,28 @@
         <v>403</v>
       </c>
       <c r="C43" s="15" t="n">
-        <f aca="false">$H$4*$F$23</f>
-        <v>0.0884781412730592</v>
-      </c>
-      <c r="D43" s="23" t="n">
-        <f aca="false">Энтропия!F$40</f>
-        <v>0.0323558799383114</v>
-      </c>
-      <c r="E43" s="22" t="n">
-        <f aca="false">(alpha_w*C43+(1-alpha_w)*D43)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.0604170106056853</v>
+        <f aca="false">$H$4</f>
+        <v>0.297944991396023</v>
+      </c>
+      <c r="D43" s="15" t="n">
+        <f aca="false">$F$23</f>
+        <v>0.296961331212497</v>
+      </c>
+      <c r="E43" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!F$41,Энтропия!F$40)</f>
+        <v>0.0350145161351267</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <f aca="false">E43/SUMIF($B$39:$B$48,B43,$E$39:$E$48)</f>
+        <v>0.0917573634224298</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <f aca="false">alpha_w*D43+(1-alpha_w)*F43</f>
+        <v>0.194359347317464</v>
+      </c>
+      <c r="H43" s="22" t="n">
+        <f aca="false">C43*G43/SUMIF($B$39:$B$48,B43,$G$39:$G$48)</f>
+        <v>0.0579083940642384</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23091,16 +23285,28 @@
         <v>404</v>
       </c>
       <c r="C44" s="15" t="n">
-        <f aca="false">$H$5*$E$26</f>
-        <v>0.0993149971320078</v>
-      </c>
-      <c r="D44" s="23" t="n">
-        <f aca="false">Энтропия!G$40</f>
-        <v>0.0772991361290431</v>
-      </c>
-      <c r="E44" s="22" t="n">
-        <f aca="false">(alpha_w*C44+(1-alpha_w)*D44)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.0883070666305255</v>
+        <f aca="false">$H$5</f>
+        <v>0.297944991396023</v>
+      </c>
+      <c r="D44" s="15" t="n">
+        <f aca="false">$E$26</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="E44" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!G$41,Энтропия!G$40)</f>
+        <v>0.0713821280971779</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <f aca="false">E44/SUMIF($B$39:$B$48,B44,$E$39:$E$48)</f>
+        <v>0.50643604397301</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <f aca="false">alpha_w*D44+(1-alpha_w)*F44</f>
+        <v>0.419884688653172</v>
+      </c>
+      <c r="H44" s="22" t="n">
+        <f aca="false">C44*G44/SUMIF($B$39:$B$48,B44,$G$39:$G$48)</f>
+        <v>0.125102539948091</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23111,16 +23317,28 @@
         <v>404</v>
       </c>
       <c r="C45" s="15" t="n">
-        <f aca="false">$H$5*$E$27</f>
-        <v>0.198629994264016</v>
-      </c>
-      <c r="D45" s="23" t="n">
-        <f aca="false">Энтропия!H$40</f>
-        <v>0.0753058433590029</v>
-      </c>
-      <c r="E45" s="22" t="n">
-        <f aca="false">(alpha_w*C45+(1-alpha_w)*D45)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.136967918811509</v>
+        <f aca="false">$H$5</f>
+        <v>0.297944991396023</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <f aca="false">$E$27</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E45" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!H$41,Энтропия!H$40)</f>
+        <v>0.0695678081221763</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <f aca="false">E45/SUMIF($B$39:$B$48,B45,$E$39:$E$48)</f>
+        <v>0.49356395602699</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <f aca="false">alpha_w*D45+(1-alpha_w)*F45</f>
+        <v>0.580115311346828</v>
+      </c>
+      <c r="H45" s="22" t="n">
+        <f aca="false">C45*G45/SUMIF($B$39:$B$48,B45,$G$39:$G$48)</f>
+        <v>0.172842451447932</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23131,16 +23349,28 @@
         <v>405</v>
       </c>
       <c r="C46" s="15" t="n">
-        <f aca="false">$H$6*$E$30</f>
-        <v>0.0590130526668012</v>
-      </c>
-      <c r="D46" s="23" t="n">
-        <f aca="false">Энтропия!I$40</f>
-        <v>0.0678563987661437</v>
-      </c>
-      <c r="E46" s="22" t="n">
-        <f aca="false">(alpha_w*C46+(1-alpha_w)*D46)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.0634347257164725</v>
+        <f aca="false">$H$6</f>
+        <v>0.0885195790002019</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <f aca="false">$E$30</f>
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E46" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!I$41,Энтропия!I$40)</f>
+        <v>0.0647117997848923</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <f aca="false">E46/SUMIF($B$39:$B$48,B46,$E$39:$E$48)</f>
+        <v>0.277520290717525</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <f aca="false">alpha_w*D46+(1-alpha_w)*F46</f>
+        <v>0.472093478692096</v>
+      </c>
+      <c r="H46" s="22" t="n">
+        <f aca="false">C46*G46/SUMIF($B$39:$B$48,B46,$G$39:$G$48)</f>
+        <v>0.0417895159825651</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23151,16 +23381,28 @@
         <v>405</v>
       </c>
       <c r="C47" s="15" t="n">
-        <f aca="false">$H$6*$E$31</f>
-        <v>0.0295065263334006</v>
-      </c>
-      <c r="D47" s="23" t="n">
-        <f aca="false">Энтропия!J$40</f>
-        <v>0.167672485177433</v>
-      </c>
-      <c r="E47" s="22" t="n">
-        <f aca="false">(alpha_w*C47+(1-alpha_w)*D47)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.098589505755417</v>
+        <f aca="false">$H$6</f>
+        <v>0.0885195790002019</v>
+      </c>
+      <c r="D47" s="15" t="n">
+        <f aca="false">$E$31</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="E47" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!J$41,Энтропия!J$40)</f>
+        <v>0.168466825163867</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <f aca="false">E47/SUMIF($B$39:$B$48,B47,$E$39:$E$48)</f>
+        <v>0.722479709282475</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <f aca="false">alpha_w*D47+(1-alpha_w)*F47</f>
+        <v>0.527906521307904</v>
+      </c>
+      <c r="H47" s="22" t="n">
+        <f aca="false">C47*G47/SUMIF($B$39:$B$48,B47,$G$39:$G$48)</f>
+        <v>0.0467300630176368</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23171,16 +23413,37 @@
         <v>406</v>
       </c>
       <c r="C48" s="15" t="n">
-        <f aca="false">$H$7*$D$34</f>
+        <f aca="false">$H$7</f>
         <v>0.157795219103876</v>
       </c>
-      <c r="D48" s="23" t="n">
-        <f aca="false">Энтропия!K$40</f>
-        <v>0.0952316106317977</v>
-      </c>
-      <c r="E48" s="22" t="n">
-        <f aca="false">(alpha_w*C48+(1-alpha_w)*D48)/(alpha_w*SUM($C$39:$C$48)+(1-alpha_w)*SUM($D$39:$D$48))</f>
-        <v>0.126513414867837</v>
+      <c r="D48" s="15" t="n">
+        <f aca="false">$D$34</f>
+        <v>1</v>
+      </c>
+      <c r="E48" s="23" t="n">
+        <f aca="false">IF(S_task&gt;0,Энтропия!K$41,Энтропия!K$40)</f>
+        <v>0.0942434623123292</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <f aca="false">E48/SUMIF($B$39:$B$48,B48,$E$39:$E$48)</f>
+        <v>1</v>
+      </c>
+      <c r="G48" s="15" t="n">
+        <f aca="false">alpha_w*D48+(1-alpha_w)*F48</f>
+        <v>1</v>
+      </c>
+      <c r="H48" s="22" t="n">
+        <f aca="false">C48*G48/SUMIF($B$39:$B$48,B48,$G$39:$G$48)</f>
+        <v>0.157795219103876</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G49" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <f aca="false">SUM(H39:H48)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
